--- a/Gantt chart for maison quest.xlsx
+++ b/Gantt chart for maison quest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/naomik/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{639EB0ED-A087-324C-B206-2BA1152E49D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50422181-AA6E-D341-AF5A-54073D8B215C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="660" windowWidth="25740" windowHeight="17060" xr2:uid="{60D461F6-DC51-7E42-A4C3-72038E3E6CD3}"/>
+    <workbookView xWindow="3660" yWindow="660" windowWidth="25740" windowHeight="17060" xr2:uid="{60D461F6-DC51-7E42-A4C3-72038E3E6CD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Gantt Chart" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="124">
   <si>
     <t>Project start: 01 Mar 2026 | Platform: MaisonQuest (Cameroon Real Estate Marketplace) | Owner: Mel-smith Koge | Status: Active Testing</t>
   </si>
@@ -291,9 +291,6 @@
   </si>
   <si>
     <t>Testing</t>
-  </si>
-  <si>
-    <t>In progress</t>
   </si>
   <si>
     <t>Not started</t>
@@ -440,7 +437,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -558,13 +555,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color theme="9" tint="-0.249977111117893"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
@@ -609,7 +599,7 @@
       <name val="Aptos Narrow (Body)"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -727,6 +717,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED973"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -934,7 +930,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -947,12 +943,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -962,9 +952,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="11" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -973,16 +960,12 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -995,18 +978,33 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1016,15 +1014,6 @@
     <xf numFmtId="0" fontId="10" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1034,32 +1023,38 @@
     <xf numFmtId="0" fontId="11" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1129,6 +1124,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFC000"/>
+      <color rgb="FFFEF3C9"/>
+      <color rgb="FF8ED973"/>
       <color rgb="FFF2F6FA"/>
       <color rgb="FFDAE8F8"/>
       <color rgb="FFD4D4D4"/>
@@ -1136,8 +1134,6 @@
       <color rgb="FFFEF3C8"/>
       <color rgb="FFB4740E"/>
       <color rgb="FFFEE2E2"/>
-      <color rgb="FF215C99"/>
-      <color rgb="FFDBE9F9"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1686,190 +1682,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2322" ht="46" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-      <c r="AA1" s="12"/>
-      <c r="AB1" s="12"/>
-      <c r="AC1" s="12"/>
-      <c r="AD1" s="12"/>
-      <c r="AE1" s="12"/>
-      <c r="AF1" s="12"/>
-      <c r="AG1" s="12"/>
-      <c r="AH1" s="12"/>
-      <c r="AI1" s="12"/>
-      <c r="AJ1" s="12"/>
+      <c r="A1" s="75" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="75"/>
+      <c r="W1" s="75"/>
+      <c r="X1" s="75"/>
+      <c r="Y1" s="75"/>
+      <c r="Z1" s="75"/>
+      <c r="AA1" s="75"/>
+      <c r="AB1" s="75"/>
+      <c r="AC1" s="75"/>
+      <c r="AD1" s="75"/>
+      <c r="AE1" s="75"/>
+      <c r="AF1" s="75"/>
+      <c r="AG1" s="75"/>
+      <c r="AH1" s="75"/>
+      <c r="AI1" s="75"/>
+      <c r="AJ1" s="75"/>
     </row>
     <row r="2" spans="1:2322" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="13"/>
-      <c r="AB2" s="13"/>
-      <c r="AC2" s="13"/>
-      <c r="AD2" s="13"/>
-      <c r="AE2" s="13"/>
-      <c r="AF2" s="13"/>
-      <c r="AG2" s="13"/>
-      <c r="AH2" s="13"/>
-      <c r="AI2" s="13"/>
-      <c r="AJ2" s="13"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
+      <c r="W2" s="76"/>
+      <c r="X2" s="76"/>
+      <c r="Y2" s="76"/>
+      <c r="Z2" s="76"/>
+      <c r="AA2" s="76"/>
+      <c r="AB2" s="76"/>
+      <c r="AC2" s="76"/>
+      <c r="AD2" s="76"/>
+      <c r="AE2" s="76"/>
+      <c r="AF2" s="76"/>
+      <c r="AG2" s="76"/>
+      <c r="AH2" s="76"/>
+      <c r="AI2" s="76"/>
+      <c r="AJ2" s="76"/>
     </row>
     <row r="3" spans="1:2322" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14"/>
-      <c r="B3" s="15" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="15" t="s">
+      <c r="O3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="Q3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="R3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="S3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="15" t="s">
+      <c r="T3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="15" t="s">
+      <c r="U3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="15" t="s">
+      <c r="V3" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="15" t="s">
+      <c r="W3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="X3" s="15" t="s">
+      <c r="X3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="Y3" s="15" t="s">
+      <c r="Y3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="Z3" s="15" t="s">
+      <c r="Z3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="AA3" s="15" t="s">
+      <c r="AA3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="AB3" s="15" t="s">
+      <c r="AB3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="AC3" s="15" t="s">
+      <c r="AC3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="AD3" s="15" t="s">
+      <c r="AD3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="AE3" s="15" t="s">
+      <c r="AE3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="AF3" s="15" t="s">
+      <c r="AF3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AG3" s="15" t="s">
+      <c r="AG3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AH3" s="15" t="s">
+      <c r="AH3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AI3" s="15" t="s">
+      <c r="AI3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AJ3" s="16" t="s">
+      <c r="AJ3" s="14" t="s">
         <v>34</v>
       </c>
       <c r="AK3"/>
@@ -3768,490 +3764,490 @@
       <c r="BVF3" s="10"/>
     </row>
     <row r="4" spans="1:2322" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="18"/>
-      <c r="U4" s="18"/>
-      <c r="V4" s="18"/>
-      <c r="W4" s="18"/>
-      <c r="X4" s="18"/>
-      <c r="Y4" s="18"/>
-      <c r="Z4" s="18"/>
-      <c r="AA4" s="18"/>
-      <c r="AB4" s="18"/>
-      <c r="AC4" s="18"/>
-      <c r="AD4" s="18"/>
-      <c r="AE4" s="18"/>
-      <c r="AF4" s="18"/>
-      <c r="AG4" s="18"/>
-      <c r="AH4" s="18"/>
-      <c r="AI4" s="18"/>
-      <c r="AJ4" s="18"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AC4" s="15"/>
+      <c r="AD4" s="15"/>
+      <c r="AE4" s="15"/>
+      <c r="AF4" s="15"/>
+      <c r="AG4" s="15"/>
+      <c r="AH4" s="15"/>
+      <c r="AI4" s="15"/>
+      <c r="AJ4" s="15"/>
     </row>
     <row r="5" spans="1:2322" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="17">
         <v>46082</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="17">
         <v>46088</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="25" t="s">
+      <c r="I5" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="71"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21"/>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21"/>
-      <c r="V5" s="21"/>
-      <c r="W5" s="21"/>
-      <c r="X5" s="21"/>
-      <c r="Y5" s="21"/>
-      <c r="Z5" s="21"/>
-      <c r="AA5" s="21"/>
-      <c r="AB5" s="21"/>
-      <c r="AC5" s="21"/>
-      <c r="AD5" s="21"/>
-      <c r="AE5" s="21"/>
-      <c r="AF5" s="21"/>
-      <c r="AG5" s="21"/>
-      <c r="AH5" s="21"/>
-      <c r="AI5" s="21"/>
-      <c r="AJ5" s="21"/>
-      <c r="AK5" s="21"/>
-      <c r="AL5" s="21"/>
-      <c r="AM5" s="21"/>
-      <c r="AN5" s="21"/>
-      <c r="AO5" s="21"/>
-      <c r="AP5" s="21"/>
-      <c r="AQ5" s="21"/>
-      <c r="AR5" s="21"/>
-      <c r="AS5" s="21"/>
-      <c r="AT5" s="21"/>
-      <c r="AU5" s="21"/>
-      <c r="AV5" s="21"/>
-      <c r="AW5" s="21"/>
-      <c r="AX5" s="21"/>
-      <c r="AY5" s="21"/>
-      <c r="AZ5" s="21"/>
-      <c r="BA5" s="21"/>
-      <c r="BB5" s="21"/>
-      <c r="BC5" s="21"/>
-      <c r="BD5" s="21"/>
-      <c r="BE5" s="21"/>
-      <c r="BF5" s="21"/>
-      <c r="BG5" s="21"/>
-      <c r="BH5" s="21"/>
-      <c r="BI5" s="21"/>
-      <c r="BJ5" s="21"/>
-      <c r="BK5" s="21"/>
-      <c r="BL5" s="21"/>
-      <c r="BM5" s="21"/>
-      <c r="BN5" s="21"/>
-      <c r="BO5" s="21"/>
-      <c r="BP5" s="21"/>
-      <c r="BQ5" s="21"/>
-      <c r="BR5" s="21"/>
-      <c r="BS5" s="21"/>
-      <c r="BT5" s="21"/>
-      <c r="BU5" s="21"/>
-      <c r="BV5" s="21"/>
-      <c r="BW5" s="21"/>
-      <c r="BX5" s="21"/>
-      <c r="BY5" s="21"/>
-      <c r="BZ5" s="21"/>
-      <c r="CA5" s="21"/>
-      <c r="CB5" s="21"/>
-      <c r="CC5" s="21"/>
-      <c r="CD5" s="21"/>
-      <c r="CE5" s="21"/>
-      <c r="CF5" s="21"/>
-      <c r="CG5" s="21"/>
-      <c r="CH5" s="21"/>
-      <c r="CI5" s="21"/>
-      <c r="CJ5" s="21"/>
-      <c r="CK5" s="21"/>
-      <c r="CL5" s="21"/>
-      <c r="CM5" s="21"/>
-      <c r="CN5" s="21"/>
-      <c r="CO5" s="21"/>
-      <c r="CP5" s="21"/>
-      <c r="CQ5" s="21"/>
-      <c r="CR5" s="21"/>
-      <c r="CS5" s="21"/>
-      <c r="CT5" s="21"/>
-      <c r="CU5" s="21"/>
-      <c r="CV5" s="21"/>
-      <c r="CW5" s="21"/>
-      <c r="CX5" s="21"/>
-      <c r="CY5" s="21"/>
-      <c r="CZ5" s="21"/>
-      <c r="DA5" s="21"/>
-      <c r="DB5" s="21"/>
-      <c r="DC5" s="21"/>
-      <c r="DD5" s="21"/>
-      <c r="DE5" s="21"/>
-      <c r="DF5" s="21"/>
-      <c r="DG5" s="21"/>
-      <c r="DH5" s="21"/>
-      <c r="DI5" s="21"/>
-      <c r="DJ5" s="21"/>
-      <c r="DK5" s="21"/>
-      <c r="DL5" s="21"/>
-      <c r="DM5" s="21"/>
-      <c r="DN5" s="21"/>
-      <c r="DO5" s="21"/>
-      <c r="DP5" s="21"/>
-      <c r="DQ5" s="21"/>
-      <c r="DR5" s="21"/>
-      <c r="DS5" s="21"/>
-      <c r="DT5" s="21"/>
-      <c r="DU5" s="21"/>
-      <c r="DV5" s="21"/>
-      <c r="DW5" s="21"/>
-      <c r="DX5" s="21"/>
-      <c r="DY5" s="21"/>
-      <c r="DZ5" s="21"/>
-      <c r="EA5" s="21"/>
-      <c r="EB5" s="21"/>
-      <c r="EC5" s="21"/>
-      <c r="ED5" s="21"/>
-      <c r="EE5" s="21"/>
-      <c r="EF5" s="21"/>
-      <c r="EG5" s="21"/>
-      <c r="EH5" s="21"/>
-      <c r="EI5" s="21"/>
-      <c r="EJ5" s="21"/>
-      <c r="EK5" s="21"/>
-      <c r="EL5" s="21"/>
-      <c r="EM5" s="21"/>
-      <c r="EN5" s="21"/>
-      <c r="EO5" s="21"/>
-      <c r="EP5" s="21"/>
-      <c r="EQ5" s="21"/>
-      <c r="ER5" s="21"/>
-      <c r="ES5" s="21"/>
-      <c r="ET5" s="21"/>
-      <c r="EU5" s="21"/>
-      <c r="EV5" s="21"/>
-      <c r="EW5" s="21"/>
-      <c r="EX5" s="21"/>
-      <c r="EY5" s="21"/>
-      <c r="EZ5" s="21"/>
-      <c r="FA5" s="21"/>
-      <c r="FB5" s="21"/>
-      <c r="FC5" s="21"/>
-      <c r="FD5" s="21"/>
-      <c r="FE5" s="21"/>
-      <c r="FF5" s="21"/>
-      <c r="FG5" s="21"/>
-      <c r="FH5" s="21"/>
-      <c r="FI5" s="21"/>
-      <c r="FJ5" s="21"/>
-      <c r="FK5" s="21"/>
-      <c r="FL5" s="21"/>
-      <c r="FM5" s="21"/>
-      <c r="FN5" s="21"/>
-      <c r="FO5" s="21"/>
-      <c r="FP5" s="21"/>
-      <c r="FQ5" s="21"/>
-      <c r="FR5" s="21"/>
-      <c r="FS5" s="21"/>
-      <c r="FT5" s="21"/>
-      <c r="FU5" s="21"/>
-      <c r="FV5" s="21"/>
-      <c r="FW5" s="21"/>
-      <c r="FX5" s="21"/>
-      <c r="FY5" s="21"/>
-      <c r="FZ5" s="21"/>
-      <c r="GA5" s="21"/>
-      <c r="GB5" s="21"/>
-      <c r="GC5" s="21"/>
-      <c r="GD5" s="21"/>
-      <c r="GE5" s="21"/>
-      <c r="GF5" s="21"/>
-      <c r="GG5" s="21"/>
-      <c r="GH5" s="21"/>
-      <c r="GI5" s="21"/>
-      <c r="GJ5" s="21"/>
-      <c r="GK5" s="21"/>
-      <c r="GL5" s="21"/>
-      <c r="GM5" s="21"/>
-      <c r="GN5" s="21"/>
-      <c r="GO5" s="21"/>
-      <c r="GP5" s="21"/>
-      <c r="GQ5" s="21"/>
-      <c r="GR5" s="21"/>
-      <c r="GS5" s="21"/>
-      <c r="GT5" s="21"/>
-      <c r="GU5" s="21"/>
-      <c r="GV5" s="21"/>
-      <c r="GW5" s="21"/>
-      <c r="GX5" s="21"/>
-      <c r="GY5" s="21"/>
-      <c r="GZ5" s="21"/>
-      <c r="HA5" s="21"/>
-      <c r="HB5" s="21"/>
-      <c r="HC5" s="21"/>
-      <c r="HD5" s="21"/>
-      <c r="HE5" s="21"/>
-      <c r="HF5" s="21"/>
-      <c r="HG5" s="21"/>
-      <c r="HH5" s="21"/>
-      <c r="HI5" s="21"/>
-      <c r="HJ5" s="21"/>
-      <c r="HK5" s="21"/>
-      <c r="HL5" s="21"/>
-      <c r="HM5" s="21"/>
-      <c r="HN5" s="21"/>
-      <c r="HO5" s="21"/>
-      <c r="HP5" s="21"/>
-      <c r="HQ5" s="21"/>
-      <c r="HR5" s="21"/>
-      <c r="HS5" s="21"/>
-      <c r="HT5" s="21"/>
-      <c r="HU5" s="21"/>
-      <c r="HV5" s="21"/>
-      <c r="HW5" s="21"/>
-      <c r="HX5" s="21"/>
-      <c r="HY5" s="21"/>
-      <c r="HZ5" s="21"/>
-      <c r="IA5" s="21"/>
-      <c r="IB5" s="21"/>
-      <c r="IC5" s="21"/>
-      <c r="ID5" s="21"/>
-      <c r="IE5" s="21"/>
-      <c r="IF5" s="21"/>
-      <c r="IG5" s="21"/>
-      <c r="IH5" s="21"/>
-      <c r="II5" s="21"/>
-      <c r="IJ5" s="21"/>
-      <c r="IK5" s="21"/>
-      <c r="IL5" s="21"/>
-      <c r="IM5" s="21"/>
-      <c r="IN5" s="21"/>
-      <c r="IO5" s="21"/>
-      <c r="IP5" s="21"/>
-      <c r="IQ5" s="21"/>
-      <c r="IR5" s="21"/>
-      <c r="IS5" s="21"/>
-      <c r="IT5" s="21"/>
-      <c r="IU5" s="21"/>
-      <c r="IV5" s="21"/>
-      <c r="IW5" s="21"/>
-      <c r="IX5" s="21"/>
-      <c r="IY5" s="21"/>
-      <c r="IZ5" s="21"/>
-      <c r="JA5" s="21"/>
-      <c r="JB5" s="21"/>
-      <c r="JC5" s="21"/>
-      <c r="JD5" s="21"/>
-      <c r="JE5" s="21"/>
-      <c r="JF5" s="21"/>
-      <c r="JG5" s="21"/>
-      <c r="JH5" s="21"/>
-      <c r="JI5" s="21"/>
-      <c r="JJ5" s="21"/>
-      <c r="JK5" s="21"/>
-      <c r="JL5" s="21"/>
-      <c r="JM5" s="21"/>
-      <c r="JN5" s="21"/>
-      <c r="JO5" s="21"/>
-      <c r="JP5" s="21"/>
-      <c r="JQ5" s="21"/>
-      <c r="JR5" s="21"/>
-      <c r="JS5" s="21"/>
-      <c r="JT5" s="21"/>
-      <c r="JU5" s="21"/>
-      <c r="JV5" s="21"/>
-      <c r="JW5" s="21"/>
-      <c r="JX5" s="21"/>
-      <c r="JY5" s="21"/>
-      <c r="JZ5" s="21"/>
-      <c r="KA5" s="21"/>
-      <c r="KB5" s="21"/>
-      <c r="KC5" s="21"/>
-      <c r="KD5" s="21"/>
-      <c r="KE5" s="21"/>
-      <c r="KF5" s="21"/>
-      <c r="KG5" s="21"/>
-      <c r="KH5" s="21"/>
-      <c r="KI5" s="21"/>
-      <c r="KJ5" s="21"/>
-      <c r="KK5" s="21"/>
-      <c r="KL5" s="21"/>
-      <c r="KM5" s="21"/>
-      <c r="KN5" s="21"/>
-      <c r="KO5" s="21"/>
-      <c r="KP5" s="21"/>
-      <c r="KQ5" s="21"/>
-      <c r="KR5" s="21"/>
-      <c r="KS5" s="21"/>
-      <c r="KT5" s="21"/>
-      <c r="KU5" s="21"/>
-      <c r="KV5" s="21"/>
-      <c r="KW5" s="21"/>
-      <c r="KX5" s="21"/>
-      <c r="KY5" s="21"/>
-      <c r="KZ5" s="21"/>
-      <c r="LA5" s="21"/>
-      <c r="LB5" s="21"/>
-      <c r="LC5" s="21"/>
-      <c r="LD5" s="21"/>
-      <c r="LE5" s="21"/>
-      <c r="LF5" s="21"/>
-      <c r="LG5" s="21"/>
-      <c r="LH5" s="21"/>
-      <c r="LI5" s="21"/>
-      <c r="LJ5" s="21"/>
-      <c r="LK5" s="21"/>
-      <c r="LL5" s="21"/>
-      <c r="LM5" s="21"/>
-      <c r="LN5" s="21"/>
-      <c r="LO5" s="21"/>
-      <c r="LP5" s="21"/>
-      <c r="LQ5" s="21"/>
-      <c r="LR5" s="21"/>
-      <c r="LS5" s="21"/>
-      <c r="LT5" s="21"/>
-      <c r="LU5" s="21"/>
-      <c r="LV5" s="21"/>
-      <c r="LW5" s="21"/>
-      <c r="LX5" s="21"/>
-      <c r="LY5" s="21"/>
-      <c r="LZ5" s="21"/>
-      <c r="MA5" s="21"/>
-      <c r="MB5" s="21"/>
-      <c r="MC5" s="21"/>
-      <c r="MD5" s="21"/>
-      <c r="ME5" s="21"/>
-      <c r="MF5" s="21"/>
-      <c r="MG5" s="21"/>
-      <c r="MH5" s="21"/>
-      <c r="MI5" s="21"/>
-      <c r="MJ5" s="21"/>
-      <c r="MK5" s="21"/>
-      <c r="ML5" s="21"/>
-      <c r="MM5" s="21"/>
-      <c r="MN5" s="21"/>
-      <c r="MO5" s="21"/>
-      <c r="MP5" s="21"/>
-      <c r="MQ5" s="21"/>
-      <c r="MR5" s="21"/>
-      <c r="MS5" s="21"/>
-      <c r="MT5" s="21"/>
-      <c r="MU5" s="21"/>
-      <c r="MV5" s="21"/>
-      <c r="MW5" s="21"/>
-      <c r="MX5" s="21"/>
-      <c r="MY5" s="21"/>
-      <c r="MZ5" s="21"/>
-      <c r="NA5" s="21"/>
-      <c r="NB5" s="21"/>
-      <c r="NC5" s="21"/>
-      <c r="ND5" s="21"/>
-      <c r="NE5" s="21"/>
-      <c r="NF5" s="21"/>
-      <c r="NG5" s="21"/>
-      <c r="NH5" s="21"/>
-      <c r="NI5" s="21"/>
-      <c r="NJ5" s="21"/>
-      <c r="NK5" s="21"/>
-      <c r="NL5" s="21"/>
-      <c r="NM5" s="21"/>
-      <c r="NN5" s="21"/>
-      <c r="NO5" s="21"/>
-      <c r="NP5" s="21"/>
-      <c r="NQ5" s="21"/>
-      <c r="NR5" s="21"/>
-      <c r="NS5" s="21"/>
-      <c r="NT5" s="21"/>
-      <c r="NU5" s="21"/>
-      <c r="NV5" s="21"/>
-      <c r="NW5" s="21"/>
-      <c r="NX5" s="21"/>
-      <c r="NY5" s="21"/>
-      <c r="NZ5" s="21"/>
-      <c r="OA5" s="21"/>
-      <c r="OB5" s="21"/>
-      <c r="OC5" s="21"/>
-      <c r="OD5" s="21"/>
-      <c r="OE5" s="21"/>
-      <c r="OF5" s="21"/>
-      <c r="OG5" s="21"/>
-      <c r="OH5" s="21"/>
-      <c r="OI5" s="21"/>
-      <c r="OJ5" s="21"/>
-      <c r="OK5" s="21"/>
-      <c r="OL5" s="21"/>
-      <c r="OM5" s="21"/>
-      <c r="ON5" s="21"/>
-      <c r="OO5" s="21"/>
-      <c r="OP5" s="21"/>
-      <c r="OQ5" s="21"/>
-      <c r="OR5" s="21"/>
-      <c r="OS5" s="21"/>
-      <c r="OT5" s="21"/>
-      <c r="OU5" s="21"/>
-      <c r="OV5" s="21"/>
-      <c r="OW5" s="21"/>
-      <c r="OX5" s="21"/>
-      <c r="OY5" s="21"/>
-      <c r="OZ5" s="21"/>
-      <c r="PA5" s="21"/>
-      <c r="PB5" s="21"/>
-      <c r="PC5" s="21"/>
-      <c r="PD5" s="21"/>
-      <c r="PE5" s="21"/>
-      <c r="PF5" s="21"/>
-      <c r="PG5" s="21"/>
-      <c r="PH5" s="21"/>
-      <c r="PI5" s="21"/>
-      <c r="PJ5" s="21"/>
-      <c r="PK5" s="21"/>
-      <c r="PL5" s="21"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="18"/>
+      <c r="U5" s="18"/>
+      <c r="V5" s="18"/>
+      <c r="W5" s="18"/>
+      <c r="X5" s="18"/>
+      <c r="Y5" s="18"/>
+      <c r="Z5" s="18"/>
+      <c r="AA5" s="18"/>
+      <c r="AB5" s="18"/>
+      <c r="AC5" s="18"/>
+      <c r="AD5" s="18"/>
+      <c r="AE5" s="18"/>
+      <c r="AF5" s="18"/>
+      <c r="AG5" s="18"/>
+      <c r="AH5" s="18"/>
+      <c r="AI5" s="18"/>
+      <c r="AJ5" s="18"/>
+      <c r="AK5" s="18"/>
+      <c r="AL5" s="18"/>
+      <c r="AM5" s="18"/>
+      <c r="AN5" s="18"/>
+      <c r="AO5" s="18"/>
+      <c r="AP5" s="18"/>
+      <c r="AQ5" s="18"/>
+      <c r="AR5" s="18"/>
+      <c r="AS5" s="18"/>
+      <c r="AT5" s="18"/>
+      <c r="AU5" s="18"/>
+      <c r="AV5" s="18"/>
+      <c r="AW5" s="18"/>
+      <c r="AX5" s="18"/>
+      <c r="AY5" s="18"/>
+      <c r="AZ5" s="18"/>
+      <c r="BA5" s="18"/>
+      <c r="BB5" s="18"/>
+      <c r="BC5" s="18"/>
+      <c r="BD5" s="18"/>
+      <c r="BE5" s="18"/>
+      <c r="BF5" s="18"/>
+      <c r="BG5" s="18"/>
+      <c r="BH5" s="18"/>
+      <c r="BI5" s="18"/>
+      <c r="BJ5" s="18"/>
+      <c r="BK5" s="18"/>
+      <c r="BL5" s="18"/>
+      <c r="BM5" s="18"/>
+      <c r="BN5" s="18"/>
+      <c r="BO5" s="18"/>
+      <c r="BP5" s="18"/>
+      <c r="BQ5" s="18"/>
+      <c r="BR5" s="18"/>
+      <c r="BS5" s="18"/>
+      <c r="BT5" s="18"/>
+      <c r="BU5" s="18"/>
+      <c r="BV5" s="18"/>
+      <c r="BW5" s="18"/>
+      <c r="BX5" s="18"/>
+      <c r="BY5" s="18"/>
+      <c r="BZ5" s="18"/>
+      <c r="CA5" s="18"/>
+      <c r="CB5" s="18"/>
+      <c r="CC5" s="18"/>
+      <c r="CD5" s="18"/>
+      <c r="CE5" s="18"/>
+      <c r="CF5" s="18"/>
+      <c r="CG5" s="18"/>
+      <c r="CH5" s="18"/>
+      <c r="CI5" s="18"/>
+      <c r="CJ5" s="18"/>
+      <c r="CK5" s="18"/>
+      <c r="CL5" s="18"/>
+      <c r="CM5" s="18"/>
+      <c r="CN5" s="18"/>
+      <c r="CO5" s="18"/>
+      <c r="CP5" s="18"/>
+      <c r="CQ5" s="18"/>
+      <c r="CR5" s="18"/>
+      <c r="CS5" s="18"/>
+      <c r="CT5" s="18"/>
+      <c r="CU5" s="18"/>
+      <c r="CV5" s="18"/>
+      <c r="CW5" s="18"/>
+      <c r="CX5" s="18"/>
+      <c r="CY5" s="18"/>
+      <c r="CZ5" s="18"/>
+      <c r="DA5" s="18"/>
+      <c r="DB5" s="18"/>
+      <c r="DC5" s="18"/>
+      <c r="DD5" s="18"/>
+      <c r="DE5" s="18"/>
+      <c r="DF5" s="18"/>
+      <c r="DG5" s="18"/>
+      <c r="DH5" s="18"/>
+      <c r="DI5" s="18"/>
+      <c r="DJ5" s="18"/>
+      <c r="DK5" s="18"/>
+      <c r="DL5" s="18"/>
+      <c r="DM5" s="18"/>
+      <c r="DN5" s="18"/>
+      <c r="DO5" s="18"/>
+      <c r="DP5" s="18"/>
+      <c r="DQ5" s="18"/>
+      <c r="DR5" s="18"/>
+      <c r="DS5" s="18"/>
+      <c r="DT5" s="18"/>
+      <c r="DU5" s="18"/>
+      <c r="DV5" s="18"/>
+      <c r="DW5" s="18"/>
+      <c r="DX5" s="18"/>
+      <c r="DY5" s="18"/>
+      <c r="DZ5" s="18"/>
+      <c r="EA5" s="18"/>
+      <c r="EB5" s="18"/>
+      <c r="EC5" s="18"/>
+      <c r="ED5" s="18"/>
+      <c r="EE5" s="18"/>
+      <c r="EF5" s="18"/>
+      <c r="EG5" s="18"/>
+      <c r="EH5" s="18"/>
+      <c r="EI5" s="18"/>
+      <c r="EJ5" s="18"/>
+      <c r="EK5" s="18"/>
+      <c r="EL5" s="18"/>
+      <c r="EM5" s="18"/>
+      <c r="EN5" s="18"/>
+      <c r="EO5" s="18"/>
+      <c r="EP5" s="18"/>
+      <c r="EQ5" s="18"/>
+      <c r="ER5" s="18"/>
+      <c r="ES5" s="18"/>
+      <c r="ET5" s="18"/>
+      <c r="EU5" s="18"/>
+      <c r="EV5" s="18"/>
+      <c r="EW5" s="18"/>
+      <c r="EX5" s="18"/>
+      <c r="EY5" s="18"/>
+      <c r="EZ5" s="18"/>
+      <c r="FA5" s="18"/>
+      <c r="FB5" s="18"/>
+      <c r="FC5" s="18"/>
+      <c r="FD5" s="18"/>
+      <c r="FE5" s="18"/>
+      <c r="FF5" s="18"/>
+      <c r="FG5" s="18"/>
+      <c r="FH5" s="18"/>
+      <c r="FI5" s="18"/>
+      <c r="FJ5" s="18"/>
+      <c r="FK5" s="18"/>
+      <c r="FL5" s="18"/>
+      <c r="FM5" s="18"/>
+      <c r="FN5" s="18"/>
+      <c r="FO5" s="18"/>
+      <c r="FP5" s="18"/>
+      <c r="FQ5" s="18"/>
+      <c r="FR5" s="18"/>
+      <c r="FS5" s="18"/>
+      <c r="FT5" s="18"/>
+      <c r="FU5" s="18"/>
+      <c r="FV5" s="18"/>
+      <c r="FW5" s="18"/>
+      <c r="FX5" s="18"/>
+      <c r="FY5" s="18"/>
+      <c r="FZ5" s="18"/>
+      <c r="GA5" s="18"/>
+      <c r="GB5" s="18"/>
+      <c r="GC5" s="18"/>
+      <c r="GD5" s="18"/>
+      <c r="GE5" s="18"/>
+      <c r="GF5" s="18"/>
+      <c r="GG5" s="18"/>
+      <c r="GH5" s="18"/>
+      <c r="GI5" s="18"/>
+      <c r="GJ5" s="18"/>
+      <c r="GK5" s="18"/>
+      <c r="GL5" s="18"/>
+      <c r="GM5" s="18"/>
+      <c r="GN5" s="18"/>
+      <c r="GO5" s="18"/>
+      <c r="GP5" s="18"/>
+      <c r="GQ5" s="18"/>
+      <c r="GR5" s="18"/>
+      <c r="GS5" s="18"/>
+      <c r="GT5" s="18"/>
+      <c r="GU5" s="18"/>
+      <c r="GV5" s="18"/>
+      <c r="GW5" s="18"/>
+      <c r="GX5" s="18"/>
+      <c r="GY5" s="18"/>
+      <c r="GZ5" s="18"/>
+      <c r="HA5" s="18"/>
+      <c r="HB5" s="18"/>
+      <c r="HC5" s="18"/>
+      <c r="HD5" s="18"/>
+      <c r="HE5" s="18"/>
+      <c r="HF5" s="18"/>
+      <c r="HG5" s="18"/>
+      <c r="HH5" s="18"/>
+      <c r="HI5" s="18"/>
+      <c r="HJ5" s="18"/>
+      <c r="HK5" s="18"/>
+      <c r="HL5" s="18"/>
+      <c r="HM5" s="18"/>
+      <c r="HN5" s="18"/>
+      <c r="HO5" s="18"/>
+      <c r="HP5" s="18"/>
+      <c r="HQ5" s="18"/>
+      <c r="HR5" s="18"/>
+      <c r="HS5" s="18"/>
+      <c r="HT5" s="18"/>
+      <c r="HU5" s="18"/>
+      <c r="HV5" s="18"/>
+      <c r="HW5" s="18"/>
+      <c r="HX5" s="18"/>
+      <c r="HY5" s="18"/>
+      <c r="HZ5" s="18"/>
+      <c r="IA5" s="18"/>
+      <c r="IB5" s="18"/>
+      <c r="IC5" s="18"/>
+      <c r="ID5" s="18"/>
+      <c r="IE5" s="18"/>
+      <c r="IF5" s="18"/>
+      <c r="IG5" s="18"/>
+      <c r="IH5" s="18"/>
+      <c r="II5" s="18"/>
+      <c r="IJ5" s="18"/>
+      <c r="IK5" s="18"/>
+      <c r="IL5" s="18"/>
+      <c r="IM5" s="18"/>
+      <c r="IN5" s="18"/>
+      <c r="IO5" s="18"/>
+      <c r="IP5" s="18"/>
+      <c r="IQ5" s="18"/>
+      <c r="IR5" s="18"/>
+      <c r="IS5" s="18"/>
+      <c r="IT5" s="18"/>
+      <c r="IU5" s="18"/>
+      <c r="IV5" s="18"/>
+      <c r="IW5" s="18"/>
+      <c r="IX5" s="18"/>
+      <c r="IY5" s="18"/>
+      <c r="IZ5" s="18"/>
+      <c r="JA5" s="18"/>
+      <c r="JB5" s="18"/>
+      <c r="JC5" s="18"/>
+      <c r="JD5" s="18"/>
+      <c r="JE5" s="18"/>
+      <c r="JF5" s="18"/>
+      <c r="JG5" s="18"/>
+      <c r="JH5" s="18"/>
+      <c r="JI5" s="18"/>
+      <c r="JJ5" s="18"/>
+      <c r="JK5" s="18"/>
+      <c r="JL5" s="18"/>
+      <c r="JM5" s="18"/>
+      <c r="JN5" s="18"/>
+      <c r="JO5" s="18"/>
+      <c r="JP5" s="18"/>
+      <c r="JQ5" s="18"/>
+      <c r="JR5" s="18"/>
+      <c r="JS5" s="18"/>
+      <c r="JT5" s="18"/>
+      <c r="JU5" s="18"/>
+      <c r="JV5" s="18"/>
+      <c r="JW5" s="18"/>
+      <c r="JX5" s="18"/>
+      <c r="JY5" s="18"/>
+      <c r="JZ5" s="18"/>
+      <c r="KA5" s="18"/>
+      <c r="KB5" s="18"/>
+      <c r="KC5" s="18"/>
+      <c r="KD5" s="18"/>
+      <c r="KE5" s="18"/>
+      <c r="KF5" s="18"/>
+      <c r="KG5" s="18"/>
+      <c r="KH5" s="18"/>
+      <c r="KI5" s="18"/>
+      <c r="KJ5" s="18"/>
+      <c r="KK5" s="18"/>
+      <c r="KL5" s="18"/>
+      <c r="KM5" s="18"/>
+      <c r="KN5" s="18"/>
+      <c r="KO5" s="18"/>
+      <c r="KP5" s="18"/>
+      <c r="KQ5" s="18"/>
+      <c r="KR5" s="18"/>
+      <c r="KS5" s="18"/>
+      <c r="KT5" s="18"/>
+      <c r="KU5" s="18"/>
+      <c r="KV5" s="18"/>
+      <c r="KW5" s="18"/>
+      <c r="KX5" s="18"/>
+      <c r="KY5" s="18"/>
+      <c r="KZ5" s="18"/>
+      <c r="LA5" s="18"/>
+      <c r="LB5" s="18"/>
+      <c r="LC5" s="18"/>
+      <c r="LD5" s="18"/>
+      <c r="LE5" s="18"/>
+      <c r="LF5" s="18"/>
+      <c r="LG5" s="18"/>
+      <c r="LH5" s="18"/>
+      <c r="LI5" s="18"/>
+      <c r="LJ5" s="18"/>
+      <c r="LK5" s="18"/>
+      <c r="LL5" s="18"/>
+      <c r="LM5" s="18"/>
+      <c r="LN5" s="18"/>
+      <c r="LO5" s="18"/>
+      <c r="LP5" s="18"/>
+      <c r="LQ5" s="18"/>
+      <c r="LR5" s="18"/>
+      <c r="LS5" s="18"/>
+      <c r="LT5" s="18"/>
+      <c r="LU5" s="18"/>
+      <c r="LV5" s="18"/>
+      <c r="LW5" s="18"/>
+      <c r="LX5" s="18"/>
+      <c r="LY5" s="18"/>
+      <c r="LZ5" s="18"/>
+      <c r="MA5" s="18"/>
+      <c r="MB5" s="18"/>
+      <c r="MC5" s="18"/>
+      <c r="MD5" s="18"/>
+      <c r="ME5" s="18"/>
+      <c r="MF5" s="18"/>
+      <c r="MG5" s="18"/>
+      <c r="MH5" s="18"/>
+      <c r="MI5" s="18"/>
+      <c r="MJ5" s="18"/>
+      <c r="MK5" s="18"/>
+      <c r="ML5" s="18"/>
+      <c r="MM5" s="18"/>
+      <c r="MN5" s="18"/>
+      <c r="MO5" s="18"/>
+      <c r="MP5" s="18"/>
+      <c r="MQ5" s="18"/>
+      <c r="MR5" s="18"/>
+      <c r="MS5" s="18"/>
+      <c r="MT5" s="18"/>
+      <c r="MU5" s="18"/>
+      <c r="MV5" s="18"/>
+      <c r="MW5" s="18"/>
+      <c r="MX5" s="18"/>
+      <c r="MY5" s="18"/>
+      <c r="MZ5" s="18"/>
+      <c r="NA5" s="18"/>
+      <c r="NB5" s="18"/>
+      <c r="NC5" s="18"/>
+      <c r="ND5" s="18"/>
+      <c r="NE5" s="18"/>
+      <c r="NF5" s="18"/>
+      <c r="NG5" s="18"/>
+      <c r="NH5" s="18"/>
+      <c r="NI5" s="18"/>
+      <c r="NJ5" s="18"/>
+      <c r="NK5" s="18"/>
+      <c r="NL5" s="18"/>
+      <c r="NM5" s="18"/>
+      <c r="NN5" s="18"/>
+      <c r="NO5" s="18"/>
+      <c r="NP5" s="18"/>
+      <c r="NQ5" s="18"/>
+      <c r="NR5" s="18"/>
+      <c r="NS5" s="18"/>
+      <c r="NT5" s="18"/>
+      <c r="NU5" s="18"/>
+      <c r="NV5" s="18"/>
+      <c r="NW5" s="18"/>
+      <c r="NX5" s="18"/>
+      <c r="NY5" s="18"/>
+      <c r="NZ5" s="18"/>
+      <c r="OA5" s="18"/>
+      <c r="OB5" s="18"/>
+      <c r="OC5" s="18"/>
+      <c r="OD5" s="18"/>
+      <c r="OE5" s="18"/>
+      <c r="OF5" s="18"/>
+      <c r="OG5" s="18"/>
+      <c r="OH5" s="18"/>
+      <c r="OI5" s="18"/>
+      <c r="OJ5" s="18"/>
+      <c r="OK5" s="18"/>
+      <c r="OL5" s="18"/>
+      <c r="OM5" s="18"/>
+      <c r="ON5" s="18"/>
+      <c r="OO5" s="18"/>
+      <c r="OP5" s="18"/>
+      <c r="OQ5" s="18"/>
+      <c r="OR5" s="18"/>
+      <c r="OS5" s="18"/>
+      <c r="OT5" s="18"/>
+      <c r="OU5" s="18"/>
+      <c r="OV5" s="18"/>
+      <c r="OW5" s="18"/>
+      <c r="OX5" s="18"/>
+      <c r="OY5" s="18"/>
+      <c r="OZ5" s="18"/>
+      <c r="PA5" s="18"/>
+      <c r="PB5" s="18"/>
+      <c r="PC5" s="18"/>
+      <c r="PD5" s="18"/>
+      <c r="PE5" s="18"/>
+      <c r="PF5" s="18"/>
+      <c r="PG5" s="18"/>
+      <c r="PH5" s="18"/>
+      <c r="PI5" s="18"/>
+      <c r="PJ5" s="18"/>
+      <c r="PK5" s="18"/>
+      <c r="PL5" s="18"/>
       <c r="PM5"/>
       <c r="PN5"/>
       <c r="PO5"/>
@@ -6148,2207 +6144,2207 @@
       <c r="CKH5" s="11"/>
     </row>
     <row r="6" spans="1:2322" x14ac:dyDescent="0.2">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23" t="s">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="21">
         <v>46082</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="21">
         <v>46088</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="I6" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="72"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="23"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="23"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="23"/>
-      <c r="AA6" s="23"/>
-      <c r="AB6" s="23"/>
-      <c r="AC6" s="23"/>
-      <c r="AD6" s="23"/>
-      <c r="AE6" s="23"/>
-      <c r="AF6" s="23"/>
-      <c r="AG6" s="23"/>
-      <c r="AH6" s="23"/>
-      <c r="AI6" s="23"/>
-      <c r="AJ6" s="23"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="20"/>
+      <c r="AD6" s="20"/>
+      <c r="AE6" s="20"/>
+      <c r="AF6" s="20"/>
+      <c r="AG6" s="20"/>
+      <c r="AH6" s="20"/>
+      <c r="AI6" s="20"/>
+      <c r="AJ6" s="20"/>
     </row>
     <row r="7" spans="1:2322" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19" t="s">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="C7" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="17">
         <v>46082</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="17">
         <v>46088</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="71"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="19"/>
-      <c r="AB7" s="19"/>
-      <c r="AC7" s="19"/>
-      <c r="AD7" s="19"/>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="19"/>
-      <c r="AG7" s="19"/>
-      <c r="AH7" s="19"/>
-      <c r="AI7" s="19"/>
-      <c r="AJ7" s="22"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="16"/>
+      <c r="U7" s="16"/>
+      <c r="V7" s="16"/>
+      <c r="W7" s="16"/>
+      <c r="X7" s="16"/>
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="16"/>
+      <c r="AA7" s="16"/>
+      <c r="AB7" s="16"/>
+      <c r="AC7" s="16"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="16"/>
+      <c r="AF7" s="16"/>
+      <c r="AG7" s="16"/>
+      <c r="AH7" s="16"/>
+      <c r="AI7" s="16"/>
+      <c r="AJ7" s="19"/>
     </row>
     <row r="8" spans="1:2322" x14ac:dyDescent="0.2">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23" t="s">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="23" t="s">
+      <c r="C8" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="21">
         <v>46089</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="21">
         <v>46096</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="25" t="s">
+      <c r="I8" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="23"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="23"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="23"/>
-      <c r="AC8" s="23"/>
-      <c r="AD8" s="23"/>
-      <c r="AE8" s="23"/>
-      <c r="AF8" s="23"/>
-      <c r="AG8" s="23"/>
-      <c r="AH8" s="23"/>
-      <c r="AI8" s="23"/>
-      <c r="AJ8" s="23"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="20"/>
+      <c r="AD8" s="20"/>
+      <c r="AE8" s="20"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="20"/>
+      <c r="AH8" s="20"/>
+      <c r="AI8" s="20"/>
+      <c r="AJ8" s="20"/>
     </row>
     <row r="9" spans="1:2322" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19" t="s">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" s="19" t="s">
+      <c r="C9" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="17">
         <v>46089</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="17">
         <v>46096</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="H9" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="I9" s="28" t="s">
+      <c r="I9" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="21"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="19"/>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="19"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="19"/>
-      <c r="AG9" s="19"/>
-      <c r="AH9" s="19"/>
-      <c r="AI9" s="19"/>
-      <c r="AJ9" s="22"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="16"/>
+      <c r="AJ9" s="19"/>
     </row>
     <row r="10" spans="1:2322" x14ac:dyDescent="0.2">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" s="23" t="s">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="21">
         <v>46096</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="21">
         <v>46242</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="23"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="23"/>
-      <c r="AC10" s="23"/>
-      <c r="AD10" s="23"/>
-      <c r="AE10" s="23"/>
-      <c r="AF10" s="23"/>
-      <c r="AG10" s="23"/>
-      <c r="AH10" s="23"/>
-      <c r="AI10" s="23"/>
-      <c r="AJ10" s="23"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="20"/>
+      <c r="AE10" s="20"/>
+      <c r="AF10" s="20"/>
+      <c r="AG10" s="20"/>
+      <c r="AH10" s="20"/>
+      <c r="AI10" s="20"/>
+      <c r="AJ10" s="20"/>
     </row>
-    <row r="11" spans="1:2322" s="36" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="33" t="s">
+    <row r="11" spans="1:2322" s="31" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="44"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="43"/>
-      <c r="Y11" s="44"/>
-      <c r="Z11" s="38"/>
-      <c r="AA11" s="38"/>
-      <c r="AB11" s="38"/>
-      <c r="AC11" s="38"/>
-      <c r="AD11" s="43"/>
-      <c r="AE11" s="44"/>
-      <c r="AF11" s="43"/>
-      <c r="AG11" s="38"/>
-      <c r="AH11" s="38"/>
-      <c r="AI11" s="38"/>
-      <c r="AJ11" s="38"/>
-      <c r="AK11" s="45"/>
-      <c r="AL11" s="35"/>
-      <c r="AM11" s="34"/>
-      <c r="AN11" s="34"/>
-      <c r="AO11" s="34"/>
-      <c r="AP11" s="34"/>
-      <c r="AQ11" s="34"/>
-      <c r="AR11" s="34"/>
-      <c r="AS11" s="34"/>
-      <c r="AT11" s="34"/>
-      <c r="AU11" s="34"/>
-      <c r="AV11" s="34"/>
-      <c r="AW11" s="34"/>
-      <c r="AX11" s="34"/>
-      <c r="AY11" s="34"/>
-      <c r="AZ11" s="34"/>
-      <c r="BA11" s="34"/>
-      <c r="BB11" s="34"/>
-      <c r="BC11" s="34"/>
-      <c r="BD11" s="34"/>
-      <c r="BE11" s="34"/>
-      <c r="BF11" s="34"/>
-      <c r="BG11" s="34"/>
-      <c r="BH11" s="34"/>
-      <c r="BI11" s="34"/>
-      <c r="BJ11" s="34"/>
-      <c r="BK11" s="34"/>
-      <c r="BL11" s="34"/>
-      <c r="BM11" s="34"/>
-      <c r="BN11" s="34"/>
-      <c r="BO11" s="34"/>
-      <c r="BP11" s="34"/>
-      <c r="BQ11" s="34"/>
-      <c r="BR11" s="34"/>
-      <c r="BS11" s="34"/>
-      <c r="BT11" s="34"/>
-      <c r="BU11" s="34"/>
-      <c r="BV11" s="34"/>
-      <c r="BW11" s="34"/>
-      <c r="BX11" s="34"/>
-      <c r="BY11" s="34"/>
-      <c r="BZ11" s="34"/>
-      <c r="CA11" s="34"/>
-      <c r="CB11" s="34"/>
-      <c r="CC11" s="34"/>
-      <c r="CD11" s="34"/>
-      <c r="CE11" s="34"/>
-      <c r="CF11" s="34"/>
-      <c r="CG11" s="34"/>
-      <c r="CH11" s="34"/>
-      <c r="CI11" s="34"/>
-      <c r="CJ11" s="34"/>
-      <c r="CK11" s="34"/>
-      <c r="CL11" s="34"/>
-      <c r="CM11" s="34"/>
-      <c r="CN11" s="34"/>
-      <c r="CO11" s="34"/>
-      <c r="CP11" s="34"/>
-      <c r="CQ11" s="34"/>
-      <c r="CR11" s="34"/>
-      <c r="CS11" s="34"/>
-      <c r="CT11" s="34"/>
-      <c r="CU11" s="34"/>
-      <c r="CV11" s="34"/>
-      <c r="CW11" s="34"/>
-      <c r="CX11" s="34"/>
-      <c r="CY11" s="34"/>
-      <c r="CZ11" s="34"/>
-      <c r="DA11" s="34"/>
-      <c r="DB11" s="34"/>
-      <c r="DC11" s="34"/>
-      <c r="DD11" s="34"/>
-      <c r="DE11" s="34"/>
-      <c r="DF11" s="34"/>
-      <c r="DG11" s="34"/>
-      <c r="DH11" s="34"/>
-      <c r="DI11" s="34"/>
-      <c r="DJ11" s="34"/>
-      <c r="DK11" s="34"/>
-      <c r="DL11" s="34"/>
-      <c r="DM11" s="34"/>
-      <c r="DN11" s="34"/>
-      <c r="DO11" s="34"/>
-      <c r="DP11" s="34"/>
-      <c r="DQ11" s="34"/>
-      <c r="DR11" s="34"/>
-      <c r="DS11" s="34"/>
-      <c r="DT11" s="34"/>
-      <c r="DU11" s="34"/>
-      <c r="DV11" s="34"/>
-      <c r="DW11" s="34"/>
-      <c r="DX11" s="34"/>
-      <c r="DY11" s="34"/>
-      <c r="DZ11" s="34"/>
-      <c r="EA11" s="34"/>
-      <c r="EB11" s="34"/>
-      <c r="EC11" s="34"/>
-      <c r="ED11" s="34"/>
-      <c r="EE11" s="34"/>
-      <c r="EF11" s="34"/>
-      <c r="EG11" s="34"/>
-      <c r="EH11" s="34"/>
-      <c r="EI11" s="34"/>
-      <c r="EJ11" s="34"/>
-      <c r="EK11" s="34"/>
-      <c r="EL11" s="34"/>
-      <c r="EM11" s="34"/>
-      <c r="EN11" s="34"/>
-      <c r="EO11" s="34"/>
-      <c r="EP11" s="34"/>
-      <c r="EQ11" s="34"/>
-      <c r="ER11" s="34"/>
-      <c r="ES11" s="34"/>
-      <c r="ET11" s="34"/>
-      <c r="EU11" s="34"/>
-      <c r="EV11" s="34"/>
-      <c r="EW11" s="34"/>
-      <c r="EX11" s="34"/>
-      <c r="EY11" s="34"/>
-      <c r="EZ11" s="34"/>
-      <c r="FA11" s="34"/>
-      <c r="FB11" s="34"/>
-      <c r="FC11" s="34"/>
-      <c r="FD11" s="34"/>
-      <c r="FE11" s="34"/>
-      <c r="FF11" s="34"/>
-      <c r="FG11" s="34"/>
-      <c r="FH11" s="34"/>
-      <c r="FI11" s="34"/>
-      <c r="FJ11" s="34"/>
-      <c r="FK11" s="34"/>
-      <c r="FL11" s="34"/>
-      <c r="FM11" s="34"/>
-      <c r="FN11" s="34"/>
-      <c r="FO11" s="34"/>
-      <c r="FP11" s="34"/>
-      <c r="FQ11" s="34"/>
-      <c r="FR11" s="34"/>
-      <c r="FS11" s="34"/>
-      <c r="FT11" s="34"/>
-      <c r="FU11" s="34"/>
-      <c r="FV11" s="34"/>
-      <c r="FW11" s="34"/>
-      <c r="FX11" s="34"/>
-      <c r="FY11" s="34"/>
-      <c r="FZ11" s="34"/>
-      <c r="GA11" s="34"/>
-      <c r="GB11" s="34"/>
-      <c r="GC11" s="34"/>
-      <c r="GD11" s="34"/>
-      <c r="GE11" s="34"/>
-      <c r="GF11" s="34"/>
-      <c r="GG11" s="34"/>
-      <c r="GH11" s="34"/>
-      <c r="GI11" s="34"/>
-      <c r="GJ11" s="34"/>
-      <c r="GK11" s="34"/>
-      <c r="GL11" s="34"/>
-      <c r="GM11" s="34"/>
-      <c r="GN11" s="34"/>
-      <c r="GO11" s="34"/>
-      <c r="GP11" s="34"/>
-      <c r="GQ11" s="34"/>
-      <c r="GR11" s="34"/>
-      <c r="GS11" s="34"/>
-      <c r="GT11" s="34"/>
-      <c r="GU11" s="34"/>
-      <c r="GV11" s="34"/>
-      <c r="GW11" s="34"/>
-      <c r="GX11" s="34"/>
-      <c r="GY11" s="34"/>
-      <c r="GZ11" s="34"/>
-      <c r="HA11" s="34"/>
-      <c r="HB11" s="34"/>
-      <c r="HC11" s="34"/>
-      <c r="HD11" s="34"/>
-      <c r="HE11" s="34"/>
-      <c r="HF11" s="34"/>
-      <c r="HG11" s="34"/>
-      <c r="HH11" s="34"/>
-      <c r="HI11" s="34"/>
-      <c r="HJ11" s="34"/>
-      <c r="HK11" s="34"/>
-      <c r="HL11" s="34"/>
-      <c r="HM11" s="34"/>
-      <c r="HN11" s="34"/>
-      <c r="HO11" s="34"/>
-      <c r="HP11" s="34"/>
-      <c r="HQ11" s="34"/>
-      <c r="HR11" s="34"/>
-      <c r="HS11" s="34"/>
-      <c r="HT11" s="34"/>
-      <c r="HU11" s="34"/>
-      <c r="HV11" s="34"/>
-      <c r="HW11" s="34"/>
-      <c r="HX11" s="34"/>
-      <c r="HY11" s="34"/>
-      <c r="HZ11" s="34"/>
-      <c r="IA11" s="34"/>
-      <c r="IB11" s="34"/>
-      <c r="IC11" s="34"/>
-      <c r="ID11" s="34"/>
-      <c r="IE11" s="34"/>
-      <c r="IF11" s="34"/>
-      <c r="IG11" s="34"/>
-      <c r="IH11" s="34"/>
-      <c r="II11" s="34"/>
-      <c r="IJ11" s="34"/>
-      <c r="IK11" s="34"/>
-      <c r="IL11" s="34"/>
-      <c r="IM11" s="34"/>
-      <c r="IN11" s="34"/>
-      <c r="IO11" s="34"/>
-      <c r="IP11" s="34"/>
-      <c r="IQ11" s="34"/>
-      <c r="IR11" s="34"/>
-      <c r="IS11" s="34"/>
-      <c r="IT11" s="34"/>
-      <c r="IU11" s="34"/>
-      <c r="IV11" s="34"/>
-      <c r="IW11" s="34"/>
-      <c r="IX11" s="34"/>
-      <c r="IY11" s="34"/>
-      <c r="IZ11" s="34"/>
-      <c r="JA11" s="34"/>
-      <c r="JB11" s="34"/>
-      <c r="JC11" s="34"/>
-      <c r="JD11" s="34"/>
-      <c r="JE11" s="34"/>
-      <c r="JF11" s="34"/>
-      <c r="JG11" s="34"/>
-      <c r="JH11" s="34"/>
-      <c r="JI11" s="34"/>
-      <c r="JJ11" s="34"/>
-      <c r="JK11" s="34"/>
-      <c r="JL11" s="34"/>
-      <c r="JM11" s="34"/>
-      <c r="JN11" s="34"/>
-      <c r="JO11" s="34"/>
-      <c r="JP11" s="34"/>
-      <c r="JQ11" s="34"/>
-      <c r="JR11" s="34"/>
-      <c r="JS11" s="34"/>
-      <c r="JT11" s="34"/>
-      <c r="JU11" s="34"/>
-      <c r="JV11" s="34"/>
-      <c r="JW11" s="34"/>
-      <c r="JX11" s="34"/>
-      <c r="JY11" s="34"/>
-      <c r="JZ11" s="34"/>
-      <c r="KA11" s="34"/>
-      <c r="KB11" s="34"/>
-      <c r="KC11" s="34"/>
-      <c r="KD11" s="34"/>
-      <c r="KE11" s="34"/>
-      <c r="KF11" s="34"/>
-      <c r="KG11" s="34"/>
-      <c r="KH11" s="34"/>
-      <c r="KI11" s="34"/>
-      <c r="KJ11" s="34"/>
-      <c r="KK11" s="34"/>
-      <c r="KL11" s="34"/>
-      <c r="KM11" s="34"/>
-      <c r="KN11" s="34"/>
-      <c r="KO11" s="34"/>
-      <c r="KP11" s="34"/>
-      <c r="KQ11" s="34"/>
-      <c r="KR11" s="34"/>
-      <c r="KS11" s="34"/>
-      <c r="KT11" s="34"/>
-      <c r="KU11" s="34"/>
-      <c r="KV11" s="34"/>
-      <c r="KW11" s="34"/>
-      <c r="KX11" s="34"/>
-      <c r="KY11" s="34"/>
-      <c r="KZ11" s="34"/>
-      <c r="LA11" s="34"/>
-      <c r="LB11" s="34"/>
-      <c r="LC11" s="34"/>
-      <c r="LD11" s="34"/>
-      <c r="LE11" s="34"/>
-      <c r="LF11" s="34"/>
-      <c r="LG11" s="34"/>
-      <c r="LH11" s="34"/>
-      <c r="LI11" s="34"/>
-      <c r="LJ11" s="34"/>
-      <c r="LK11" s="34"/>
-      <c r="LL11" s="34"/>
-      <c r="LM11" s="34"/>
-      <c r="LN11" s="34"/>
-      <c r="LO11" s="34"/>
-      <c r="LP11" s="34"/>
-      <c r="LQ11" s="34"/>
-      <c r="LR11" s="34"/>
-      <c r="LS11" s="34"/>
-      <c r="LT11" s="34"/>
-      <c r="LU11" s="34"/>
-      <c r="LV11" s="34"/>
-      <c r="LW11" s="34"/>
-      <c r="LX11" s="34"/>
-      <c r="LY11" s="34"/>
-      <c r="LZ11" s="34"/>
-      <c r="MA11" s="34"/>
-      <c r="MB11" s="34"/>
-      <c r="MC11" s="34"/>
-      <c r="MD11" s="34"/>
-      <c r="ME11" s="34"/>
-      <c r="MF11" s="34"/>
-      <c r="MG11" s="34"/>
-      <c r="MH11" s="34"/>
-      <c r="MI11" s="34"/>
-      <c r="MJ11" s="34"/>
-      <c r="MK11" s="34"/>
-      <c r="ML11" s="34"/>
-      <c r="MM11" s="34"/>
-      <c r="MN11" s="34"/>
-      <c r="MO11" s="34"/>
-      <c r="MP11" s="34"/>
-      <c r="MQ11" s="34"/>
-      <c r="MR11" s="34"/>
-      <c r="MS11" s="34"/>
-      <c r="MT11" s="34"/>
-      <c r="MU11" s="34"/>
-      <c r="MV11" s="34"/>
-      <c r="MW11" s="34"/>
-      <c r="MX11" s="34"/>
-      <c r="MY11" s="34"/>
-      <c r="MZ11" s="34"/>
-      <c r="NA11" s="34"/>
-      <c r="NB11" s="34"/>
-      <c r="NC11" s="34"/>
-      <c r="ND11" s="34"/>
-      <c r="NE11" s="34"/>
-      <c r="NF11" s="34"/>
-      <c r="NG11" s="34"/>
-      <c r="NH11" s="34"/>
-      <c r="NI11" s="34"/>
-      <c r="NJ11" s="34"/>
-      <c r="NK11" s="34"/>
-      <c r="NL11" s="34"/>
-      <c r="NM11" s="34"/>
-      <c r="NN11" s="34"/>
-      <c r="NO11" s="34"/>
-      <c r="NP11" s="34"/>
-      <c r="NQ11" s="34"/>
-      <c r="NR11" s="34"/>
-      <c r="NS11" s="34"/>
-      <c r="NT11" s="34"/>
-      <c r="NU11" s="34"/>
-      <c r="NV11" s="34"/>
-      <c r="NW11" s="34"/>
-      <c r="NX11" s="34"/>
-      <c r="NY11" s="34"/>
-      <c r="NZ11" s="34"/>
-      <c r="OA11" s="34"/>
-      <c r="OB11" s="34"/>
-      <c r="OC11" s="34"/>
-      <c r="OD11" s="34"/>
-      <c r="OE11" s="34"/>
-      <c r="OF11" s="34"/>
-      <c r="OG11" s="34"/>
-      <c r="OH11" s="34"/>
-      <c r="OI11" s="34"/>
-      <c r="OJ11" s="34"/>
-      <c r="OK11" s="34"/>
-      <c r="OL11" s="34"/>
-      <c r="OM11" s="34"/>
-      <c r="ON11" s="34"/>
-      <c r="OO11" s="34"/>
-      <c r="OP11" s="34"/>
-      <c r="OQ11" s="34"/>
-      <c r="OR11" s="34"/>
-      <c r="OS11" s="34"/>
-      <c r="OT11" s="34"/>
-      <c r="OU11" s="34"/>
-      <c r="OV11" s="34"/>
-      <c r="OW11" s="34"/>
-      <c r="OX11" s="34"/>
-      <c r="OY11" s="34"/>
-      <c r="OZ11" s="34"/>
-      <c r="PA11" s="34"/>
-      <c r="PB11" s="34"/>
-      <c r="PC11" s="34"/>
-      <c r="PD11" s="34"/>
-      <c r="PE11" s="34"/>
-      <c r="PF11" s="34"/>
-      <c r="PG11" s="34"/>
-      <c r="PH11" s="34"/>
-      <c r="PI11" s="34"/>
-      <c r="PJ11" s="34"/>
-      <c r="PK11" s="34"/>
-      <c r="PL11" s="34"/>
-      <c r="PM11" s="34"/>
-      <c r="PN11" s="34"/>
-      <c r="PO11" s="34"/>
-      <c r="PP11" s="34"/>
-      <c r="PQ11" s="34"/>
-      <c r="PR11" s="34"/>
-      <c r="PS11" s="34"/>
-      <c r="PT11" s="34"/>
-      <c r="PU11" s="34"/>
-      <c r="PV11" s="34"/>
-      <c r="PW11" s="34"/>
-      <c r="PX11" s="34"/>
-      <c r="PY11" s="34"/>
-      <c r="PZ11" s="34"/>
-      <c r="QA11" s="34"/>
-      <c r="QB11" s="34"/>
-      <c r="QC11" s="34"/>
-      <c r="QD11" s="34"/>
-      <c r="QE11" s="34"/>
-      <c r="QF11" s="34"/>
-      <c r="QG11" s="34"/>
-      <c r="QH11" s="34"/>
-      <c r="QI11" s="34"/>
-      <c r="QJ11" s="34"/>
-      <c r="QK11" s="34"/>
-      <c r="QL11" s="34"/>
-      <c r="QM11" s="34"/>
-      <c r="QN11" s="34"/>
-      <c r="QO11" s="34"/>
-      <c r="QP11" s="34"/>
-      <c r="QQ11" s="34"/>
-      <c r="QR11" s="34"/>
-      <c r="QS11" s="34"/>
-      <c r="QT11" s="34"/>
-      <c r="QU11" s="34"/>
-      <c r="QV11" s="34"/>
-      <c r="QW11" s="34"/>
-      <c r="QX11" s="34"/>
-      <c r="QY11" s="34"/>
-      <c r="QZ11" s="34"/>
-      <c r="RA11" s="34"/>
-      <c r="RB11" s="34"/>
-      <c r="RC11" s="34"/>
-      <c r="RD11" s="34"/>
-      <c r="RE11" s="34"/>
-      <c r="RF11" s="34"/>
-      <c r="RG11" s="34"/>
-      <c r="RH11" s="34"/>
-      <c r="RI11" s="34"/>
-      <c r="RJ11" s="34"/>
-      <c r="RK11" s="34"/>
-      <c r="RL11" s="34"/>
-      <c r="RM11" s="34"/>
-      <c r="RN11" s="34"/>
-      <c r="RO11" s="34"/>
-      <c r="RP11" s="34"/>
-      <c r="RQ11" s="34"/>
-      <c r="RR11" s="34"/>
-      <c r="RS11" s="34"/>
-      <c r="RT11" s="34"/>
-      <c r="RU11" s="34"/>
-      <c r="RV11" s="34"/>
-      <c r="RW11" s="34"/>
-      <c r="RX11" s="34"/>
-      <c r="RY11" s="34"/>
-      <c r="RZ11" s="34"/>
-      <c r="SA11" s="34"/>
-      <c r="SB11" s="34"/>
-      <c r="SC11" s="34"/>
-      <c r="SD11" s="34"/>
-      <c r="SE11" s="34"/>
-      <c r="SF11" s="34"/>
-      <c r="SG11" s="34"/>
-      <c r="SH11" s="34"/>
-      <c r="SI11" s="34"/>
-      <c r="SJ11" s="34"/>
-      <c r="SK11" s="34"/>
-      <c r="SL11" s="34"/>
-      <c r="SM11" s="34"/>
-      <c r="SN11" s="34"/>
-      <c r="SO11" s="34"/>
-      <c r="SP11" s="34"/>
-      <c r="SQ11" s="34"/>
-      <c r="SR11" s="34"/>
-      <c r="SS11" s="34"/>
-      <c r="ST11" s="34"/>
-      <c r="SU11" s="34"/>
-      <c r="SV11" s="34"/>
-      <c r="SW11" s="34"/>
-      <c r="SX11" s="34"/>
-      <c r="SY11" s="34"/>
-      <c r="SZ11" s="34"/>
-      <c r="TA11" s="34"/>
-      <c r="TB11" s="34"/>
-      <c r="TC11" s="34"/>
-      <c r="TD11" s="34"/>
-      <c r="TE11" s="34"/>
-      <c r="TF11" s="34"/>
-      <c r="TG11" s="34"/>
-      <c r="TH11" s="34"/>
-      <c r="TI11" s="34"/>
-      <c r="TJ11" s="34"/>
-      <c r="TK11" s="34"/>
-      <c r="TL11" s="34"/>
-      <c r="TM11" s="34"/>
-      <c r="TN11" s="34"/>
-      <c r="TO11" s="34"/>
-      <c r="TP11" s="34"/>
-      <c r="TQ11" s="34"/>
-      <c r="TR11" s="34"/>
-      <c r="TS11" s="34"/>
-      <c r="TT11" s="34"/>
-      <c r="TU11" s="34"/>
-      <c r="TV11" s="34"/>
-      <c r="TW11" s="34"/>
-      <c r="TX11" s="34"/>
-      <c r="TY11" s="34"/>
-      <c r="TZ11" s="34"/>
-      <c r="UA11" s="34"/>
-      <c r="UB11" s="34"/>
-      <c r="UC11" s="34"/>
-      <c r="UD11" s="34"/>
-      <c r="UE11" s="34"/>
-      <c r="UF11" s="34"/>
-      <c r="UG11" s="34"/>
-      <c r="UH11" s="34"/>
-      <c r="UI11" s="34"/>
-      <c r="UJ11" s="34"/>
-      <c r="UK11" s="34"/>
-      <c r="UL11" s="34"/>
-      <c r="UM11" s="34"/>
-      <c r="UN11" s="34"/>
-      <c r="UO11" s="34"/>
-      <c r="UP11" s="34"/>
-      <c r="UQ11" s="34"/>
-      <c r="UR11" s="34"/>
-      <c r="US11" s="34"/>
-      <c r="UT11" s="34"/>
-      <c r="UU11" s="34"/>
-      <c r="UV11" s="34"/>
-      <c r="UW11" s="34"/>
-      <c r="UX11" s="34"/>
-      <c r="UY11" s="34"/>
-      <c r="UZ11" s="34"/>
-      <c r="VA11" s="34"/>
-      <c r="VB11" s="34"/>
-      <c r="VC11" s="34"/>
-      <c r="VD11" s="34"/>
-      <c r="VE11" s="34"/>
-      <c r="VF11" s="34"/>
-      <c r="VG11" s="34"/>
-      <c r="VH11" s="34"/>
-      <c r="VI11" s="34"/>
-      <c r="VJ11" s="34"/>
-      <c r="VK11" s="34"/>
-      <c r="VL11" s="34"/>
-      <c r="VM11" s="34"/>
-      <c r="VN11" s="34"/>
-      <c r="VO11" s="34"/>
-      <c r="VP11" s="34"/>
-      <c r="VQ11" s="34"/>
-      <c r="VR11" s="34"/>
-      <c r="VS11" s="34"/>
-      <c r="VT11" s="34"/>
-      <c r="VU11" s="34"/>
-      <c r="VV11" s="34"/>
-      <c r="VW11" s="34"/>
-      <c r="VX11" s="34"/>
-      <c r="VY11" s="34"/>
-      <c r="VZ11" s="34"/>
-      <c r="WA11" s="34"/>
-      <c r="WB11" s="34"/>
-      <c r="WC11" s="34"/>
-      <c r="WD11" s="34"/>
-      <c r="WE11" s="34"/>
-      <c r="WF11" s="34"/>
-      <c r="WG11" s="34"/>
-      <c r="WH11" s="34"/>
-      <c r="WI11" s="34"/>
-      <c r="WJ11" s="34"/>
-      <c r="WK11" s="34"/>
-      <c r="WL11" s="34"/>
-      <c r="WM11" s="34"/>
-      <c r="WN11" s="34"/>
-      <c r="WO11" s="34"/>
-      <c r="WP11" s="34"/>
-      <c r="WQ11" s="34"/>
-      <c r="WR11" s="34"/>
-      <c r="WS11" s="34"/>
-      <c r="WT11" s="34"/>
-      <c r="WU11" s="34"/>
-      <c r="WV11" s="34"/>
-      <c r="WW11" s="34"/>
-      <c r="WX11" s="34"/>
-      <c r="WY11" s="34"/>
-      <c r="WZ11" s="34"/>
-      <c r="XA11" s="34"/>
-      <c r="XB11" s="34"/>
-      <c r="XC11" s="34"/>
-      <c r="XD11" s="34"/>
-      <c r="XE11" s="34"/>
-      <c r="XF11" s="34"/>
-      <c r="XG11" s="34"/>
-      <c r="XH11" s="34"/>
-      <c r="XI11" s="34"/>
-      <c r="XJ11" s="34"/>
-      <c r="XK11" s="34"/>
-      <c r="XL11" s="34"/>
-      <c r="XM11" s="34"/>
-      <c r="XN11" s="34"/>
-      <c r="XO11" s="34"/>
-      <c r="XP11" s="34"/>
-      <c r="XQ11" s="34"/>
-      <c r="XR11" s="34"/>
-      <c r="XS11" s="34"/>
-      <c r="XT11" s="34"/>
-      <c r="XU11" s="34"/>
-      <c r="XV11" s="34"/>
-      <c r="XW11" s="34"/>
-      <c r="XX11" s="34"/>
-      <c r="XY11" s="34"/>
-      <c r="XZ11" s="34"/>
-      <c r="YA11" s="34"/>
-      <c r="YB11" s="34"/>
-      <c r="YC11" s="34"/>
-      <c r="YD11" s="34"/>
-      <c r="YE11" s="34"/>
-      <c r="YF11" s="34"/>
-      <c r="YG11" s="34"/>
-      <c r="YH11" s="34"/>
-      <c r="YI11" s="34"/>
-      <c r="YJ11" s="34"/>
-      <c r="YK11" s="34"/>
-      <c r="YL11" s="34"/>
-      <c r="YM11" s="34"/>
-      <c r="YN11" s="34"/>
-      <c r="YO11" s="34"/>
-      <c r="YP11" s="34"/>
-      <c r="YQ11" s="34"/>
-      <c r="YR11" s="34"/>
-      <c r="YS11" s="34"/>
-      <c r="YT11" s="34"/>
-      <c r="YU11" s="34"/>
-      <c r="YV11" s="34"/>
-      <c r="YW11" s="34"/>
-      <c r="YX11" s="34"/>
-      <c r="YY11" s="34"/>
-      <c r="YZ11" s="34"/>
-      <c r="ZA11" s="34"/>
-      <c r="ZB11" s="34"/>
-      <c r="ZC11" s="34"/>
-      <c r="ZD11" s="34"/>
-      <c r="ZE11" s="34"/>
-      <c r="ZF11" s="34"/>
-      <c r="ZG11" s="34"/>
-      <c r="ZH11" s="34"/>
-      <c r="ZI11" s="34"/>
-      <c r="ZJ11" s="34"/>
-      <c r="ZK11" s="34"/>
-      <c r="ZL11" s="34"/>
-      <c r="ZM11" s="34"/>
-      <c r="ZN11" s="34"/>
-      <c r="ZO11" s="34"/>
-      <c r="ZP11" s="34"/>
-      <c r="ZQ11" s="34"/>
-      <c r="ZR11" s="34"/>
-      <c r="ZS11" s="34"/>
-      <c r="ZT11" s="34"/>
-      <c r="ZU11" s="34"/>
-      <c r="ZV11" s="34"/>
-      <c r="ZW11" s="34"/>
-      <c r="ZX11" s="34"/>
-      <c r="ZY11" s="34"/>
-      <c r="ZZ11" s="34"/>
-      <c r="AAA11" s="34"/>
-      <c r="AAB11" s="34"/>
-      <c r="AAC11" s="34"/>
-      <c r="AAD11" s="34"/>
-      <c r="AAE11" s="34"/>
-      <c r="AAF11" s="34"/>
-      <c r="AAG11" s="34"/>
-      <c r="AAH11" s="34"/>
-      <c r="AAI11" s="34"/>
-      <c r="AAJ11" s="34"/>
-      <c r="AAK11" s="34"/>
-      <c r="AAL11" s="34"/>
-      <c r="AAM11" s="34"/>
-      <c r="AAN11" s="34"/>
-      <c r="AAO11" s="34"/>
-      <c r="AAP11" s="34"/>
-      <c r="AAQ11" s="34"/>
-      <c r="AAR11" s="34"/>
-      <c r="AAS11" s="34"/>
-      <c r="AAT11" s="34"/>
-      <c r="AAU11" s="34"/>
-      <c r="AAV11" s="34"/>
-      <c r="AAW11" s="34"/>
-      <c r="AAX11" s="34"/>
-      <c r="AAY11" s="34"/>
-      <c r="AAZ11" s="34"/>
-      <c r="ABA11" s="34"/>
-      <c r="ABB11" s="34"/>
-      <c r="ABC11" s="34"/>
-      <c r="ABD11" s="34"/>
-      <c r="ABE11" s="34"/>
-      <c r="ABF11" s="34"/>
-      <c r="ABG11" s="34"/>
-      <c r="ABH11" s="34"/>
-      <c r="ABI11" s="34"/>
-      <c r="ABJ11" s="34"/>
-      <c r="ABK11" s="34"/>
-      <c r="ABL11" s="34"/>
-      <c r="ABM11" s="34"/>
-      <c r="ABN11" s="34"/>
-      <c r="ABO11" s="34"/>
-      <c r="ABP11" s="34"/>
-      <c r="ABQ11" s="34"/>
-      <c r="ABR11" s="34"/>
-      <c r="ABS11" s="34"/>
-      <c r="ABT11" s="34"/>
-      <c r="ABU11" s="34"/>
-      <c r="ABV11" s="34"/>
-      <c r="ABW11" s="34"/>
-      <c r="ABX11" s="34"/>
-      <c r="ABY11" s="34"/>
-      <c r="ABZ11" s="34"/>
-      <c r="ACA11" s="34"/>
-      <c r="ACB11" s="34"/>
-      <c r="ACC11" s="34"/>
-      <c r="ACD11" s="34"/>
-      <c r="ACE11" s="34"/>
-      <c r="ACF11" s="34"/>
-      <c r="ACG11" s="34"/>
-      <c r="ACH11" s="34"/>
-      <c r="ACI11" s="34"/>
-      <c r="ACJ11" s="34"/>
-      <c r="ACK11" s="34"/>
-      <c r="ACL11" s="34"/>
-      <c r="ACM11" s="34"/>
-      <c r="ACN11" s="34"/>
-      <c r="ACO11" s="34"/>
-      <c r="ACP11" s="34"/>
-      <c r="ACQ11" s="34"/>
-      <c r="ACR11" s="34"/>
-      <c r="ACS11" s="34"/>
-      <c r="ACT11" s="34"/>
-      <c r="ACU11" s="34"/>
-      <c r="ACV11" s="34"/>
-      <c r="ACW11" s="34"/>
-      <c r="ACX11" s="34"/>
-      <c r="ACY11" s="34"/>
-      <c r="ACZ11" s="34"/>
-      <c r="ADA11" s="34"/>
-      <c r="ADB11" s="34"/>
-      <c r="ADC11" s="34"/>
-      <c r="ADD11" s="34"/>
-      <c r="ADE11" s="34"/>
-      <c r="ADF11" s="34"/>
-      <c r="ADG11" s="34"/>
-      <c r="ADH11" s="34"/>
-      <c r="ADI11" s="34"/>
-      <c r="ADJ11" s="34"/>
-      <c r="ADK11" s="34"/>
-      <c r="ADL11" s="34"/>
-      <c r="ADM11" s="34"/>
-      <c r="ADN11" s="34"/>
-      <c r="ADO11" s="34"/>
-      <c r="ADP11" s="34"/>
-      <c r="ADQ11" s="34"/>
-      <c r="ADR11" s="34"/>
-      <c r="ADS11" s="34"/>
-      <c r="ADT11" s="34"/>
-      <c r="ADU11" s="34"/>
-      <c r="ADV11" s="34"/>
-      <c r="ADW11" s="34"/>
-      <c r="ADX11" s="34"/>
-      <c r="ADY11" s="34"/>
-      <c r="ADZ11" s="34"/>
-      <c r="AEA11" s="34"/>
-      <c r="AEB11" s="34"/>
-      <c r="AEC11" s="34"/>
-      <c r="AED11" s="34"/>
-      <c r="AEE11" s="34"/>
-      <c r="AEF11" s="34"/>
-      <c r="AEG11" s="34"/>
-      <c r="AEH11" s="34"/>
-      <c r="AEI11" s="34"/>
-      <c r="AEJ11" s="34"/>
-      <c r="AEK11" s="34"/>
-      <c r="AEL11" s="34"/>
-      <c r="AEM11" s="34"/>
-      <c r="AEN11" s="34"/>
-      <c r="AEO11" s="34"/>
-      <c r="AEP11" s="34"/>
-      <c r="AEQ11" s="34"/>
-      <c r="AER11" s="34"/>
-      <c r="AES11" s="34"/>
-      <c r="AET11" s="34"/>
-      <c r="AEU11" s="34"/>
-      <c r="AEV11" s="34"/>
-      <c r="AEW11" s="34"/>
-      <c r="AEX11" s="34"/>
-      <c r="AEY11" s="34"/>
-      <c r="AEZ11" s="34"/>
-      <c r="AFA11" s="34"/>
-      <c r="AFB11" s="34"/>
-      <c r="AFC11" s="34"/>
-      <c r="AFD11" s="34"/>
-      <c r="AFE11" s="34"/>
-      <c r="AFF11" s="34"/>
-      <c r="AFG11" s="34"/>
-      <c r="AFH11" s="34"/>
-      <c r="AFI11" s="34"/>
-      <c r="AFJ11" s="34"/>
-      <c r="AFK11" s="34"/>
-      <c r="AFL11" s="34"/>
-      <c r="AFM11" s="34"/>
-      <c r="AFN11" s="34"/>
-      <c r="AFO11" s="34"/>
-      <c r="AFP11" s="34"/>
-      <c r="AFQ11" s="34"/>
-      <c r="AFR11" s="34"/>
-      <c r="AFS11" s="34"/>
-      <c r="AFT11" s="34"/>
-      <c r="AFU11" s="34"/>
-      <c r="AFV11" s="34"/>
-      <c r="AFW11" s="34"/>
-      <c r="AFX11" s="34"/>
-      <c r="AFY11" s="34"/>
-      <c r="AFZ11" s="34"/>
-      <c r="AGA11" s="34"/>
-      <c r="AGB11" s="34"/>
-      <c r="AGC11" s="34"/>
-      <c r="AGD11" s="34"/>
-      <c r="AGE11" s="34"/>
-      <c r="AGF11" s="34"/>
-      <c r="AGG11" s="34"/>
-      <c r="AGH11" s="34"/>
-      <c r="AGI11" s="34"/>
-      <c r="AGJ11" s="34"/>
-      <c r="AGK11" s="34"/>
-      <c r="AGL11" s="34"/>
-      <c r="AGM11" s="34"/>
-      <c r="AGN11" s="34"/>
-      <c r="AGO11" s="34"/>
-      <c r="AGP11" s="34"/>
-      <c r="AGQ11" s="34"/>
-      <c r="AGR11" s="34"/>
-      <c r="AGS11" s="34"/>
-      <c r="AGT11" s="34"/>
-      <c r="AGU11" s="34"/>
-      <c r="AGV11" s="34"/>
-      <c r="AGW11" s="34"/>
-      <c r="AGX11" s="34"/>
-      <c r="AGY11" s="34"/>
-      <c r="AGZ11" s="34"/>
-      <c r="AHA11" s="34"/>
-      <c r="AHB11" s="34"/>
-      <c r="AHC11" s="34"/>
-      <c r="AHD11" s="34"/>
-      <c r="AHE11" s="34"/>
-      <c r="AHF11" s="34"/>
-      <c r="AHG11" s="34"/>
-      <c r="AHH11" s="34"/>
-      <c r="AHI11" s="34"/>
-      <c r="AHJ11" s="34"/>
-      <c r="AHK11" s="34"/>
-      <c r="AHL11" s="34"/>
-      <c r="AHM11" s="34"/>
-      <c r="AHN11" s="34"/>
-      <c r="AHO11" s="34"/>
-      <c r="AHP11" s="34"/>
-      <c r="AHQ11" s="34"/>
-      <c r="AHR11" s="34"/>
-      <c r="AHS11" s="34"/>
-      <c r="AHT11" s="34"/>
-      <c r="AHU11" s="34"/>
-      <c r="AHV11" s="34"/>
-      <c r="AHW11" s="34"/>
-      <c r="AHX11" s="34"/>
-      <c r="AHY11" s="34"/>
-      <c r="AHZ11" s="34"/>
-      <c r="AIA11" s="34"/>
-      <c r="AIB11" s="34"/>
-      <c r="AIC11" s="34"/>
-      <c r="AID11" s="34"/>
-      <c r="AIE11" s="34"/>
-      <c r="AIF11" s="34"/>
-      <c r="AIG11" s="34"/>
-      <c r="AIH11" s="34"/>
-      <c r="AII11" s="34"/>
-      <c r="AIJ11" s="34"/>
-      <c r="AIK11" s="34"/>
-      <c r="AIL11" s="34"/>
-      <c r="AIM11" s="34"/>
-      <c r="AIN11" s="34"/>
-      <c r="AIO11" s="34"/>
-      <c r="AIP11" s="34"/>
-      <c r="AIQ11" s="34"/>
-      <c r="AIR11" s="34"/>
-      <c r="AIS11" s="34"/>
-      <c r="AIT11" s="34"/>
-      <c r="AIU11" s="34"/>
-      <c r="AIV11" s="34"/>
-      <c r="AIW11" s="34"/>
-      <c r="AIX11" s="34"/>
-      <c r="AIY11" s="34"/>
-      <c r="AIZ11" s="34"/>
-      <c r="AJA11" s="34"/>
-      <c r="AJB11" s="34"/>
-      <c r="AJC11" s="34"/>
-      <c r="AJD11" s="34"/>
-      <c r="AJE11" s="34"/>
-      <c r="AJF11" s="34"/>
-      <c r="AJG11" s="34"/>
-      <c r="AJH11" s="34"/>
-      <c r="AJI11" s="34"/>
-      <c r="AJJ11" s="34"/>
-      <c r="AJK11" s="34"/>
-      <c r="AJL11" s="34"/>
-      <c r="AJM11" s="34"/>
-      <c r="AJN11" s="34"/>
-      <c r="AJO11" s="34"/>
-      <c r="AJP11" s="34"/>
-      <c r="AJQ11" s="34"/>
-      <c r="AJR11" s="34"/>
-      <c r="AJS11" s="34"/>
-      <c r="AJT11" s="34"/>
-      <c r="AJU11" s="34"/>
-      <c r="AJV11" s="34"/>
-      <c r="AJW11" s="34"/>
-      <c r="AJX11" s="34"/>
-      <c r="AJY11" s="34"/>
-      <c r="AJZ11" s="34"/>
-      <c r="AKA11" s="34"/>
-      <c r="AKB11" s="34"/>
-      <c r="AKC11" s="34"/>
-      <c r="AKD11" s="34"/>
-      <c r="AKE11" s="34"/>
-      <c r="AKF11" s="34"/>
-      <c r="AKG11" s="34"/>
-      <c r="AKH11" s="34"/>
-      <c r="AKI11" s="34"/>
-      <c r="AKJ11" s="34"/>
-      <c r="AKK11" s="34"/>
-      <c r="AKL11" s="34"/>
-      <c r="AKM11" s="34"/>
-      <c r="AKN11" s="34"/>
-      <c r="AKO11" s="34"/>
-      <c r="AKP11" s="34"/>
-      <c r="AKQ11" s="34"/>
-      <c r="AKR11" s="34"/>
-      <c r="AKS11" s="34"/>
-      <c r="AKT11" s="34"/>
-      <c r="AKU11" s="34"/>
-      <c r="AKV11" s="34"/>
-      <c r="AKW11" s="34"/>
-      <c r="AKX11" s="34"/>
-      <c r="AKY11" s="34"/>
-      <c r="AKZ11" s="34"/>
-      <c r="ALA11" s="34"/>
-      <c r="ALB11" s="34"/>
-      <c r="ALC11" s="34"/>
-      <c r="ALD11" s="34"/>
-      <c r="ALE11" s="34"/>
-      <c r="ALF11" s="34"/>
-      <c r="ALG11" s="34"/>
-      <c r="ALH11" s="34"/>
-      <c r="ALI11" s="34"/>
-      <c r="ALJ11" s="34"/>
-      <c r="ALK11" s="34"/>
-      <c r="ALL11" s="34"/>
-      <c r="ALM11" s="34"/>
-      <c r="ALN11" s="34"/>
-      <c r="ALO11" s="34"/>
-      <c r="ALP11" s="34"/>
-      <c r="ALQ11" s="34"/>
-      <c r="ALR11" s="34"/>
-      <c r="ALS11" s="34"/>
-      <c r="ALT11" s="34"/>
-      <c r="ALU11" s="34"/>
-      <c r="ALV11" s="34"/>
-      <c r="ALW11" s="34"/>
-      <c r="ALX11" s="34"/>
-      <c r="ALY11" s="34"/>
-      <c r="ALZ11" s="34"/>
-      <c r="AMA11" s="34"/>
-      <c r="AMB11" s="34"/>
-      <c r="AMC11" s="34"/>
-      <c r="AMD11" s="34"/>
-      <c r="AME11" s="34"/>
-      <c r="AMF11" s="34"/>
-      <c r="AMG11" s="34"/>
-      <c r="AMH11" s="34"/>
-      <c r="AMI11" s="34"/>
-      <c r="AMJ11" s="34"/>
-      <c r="AMK11" s="34"/>
-      <c r="AML11" s="34"/>
-      <c r="AMM11" s="34"/>
-      <c r="AMN11" s="34"/>
-      <c r="AMO11" s="34"/>
-      <c r="AMP11" s="34"/>
-      <c r="AMQ11" s="34"/>
-      <c r="AMR11" s="34"/>
-      <c r="AMS11" s="34"/>
-      <c r="AMT11" s="34"/>
-      <c r="AMU11" s="34"/>
-      <c r="AMV11" s="34"/>
-      <c r="AMW11" s="34"/>
-      <c r="AMX11" s="34"/>
-      <c r="AMY11" s="34"/>
-      <c r="AMZ11" s="34"/>
-      <c r="ANA11" s="34"/>
-      <c r="ANB11" s="34"/>
-      <c r="ANC11" s="34"/>
-      <c r="AND11" s="34"/>
-      <c r="ANE11" s="34"/>
-      <c r="ANF11" s="34"/>
-      <c r="ANG11" s="34"/>
-      <c r="ANH11" s="34"/>
-      <c r="ANI11" s="34"/>
-      <c r="ANJ11" s="34"/>
-      <c r="ANK11" s="34"/>
-      <c r="ANL11" s="34"/>
-      <c r="ANM11" s="34"/>
-      <c r="ANN11" s="34"/>
-      <c r="ANO11" s="34"/>
-      <c r="ANP11" s="34"/>
-      <c r="ANQ11" s="34"/>
-      <c r="ANR11" s="34"/>
-      <c r="ANS11" s="34"/>
-      <c r="ANT11" s="34"/>
-      <c r="ANU11" s="34"/>
-      <c r="ANV11" s="34"/>
-      <c r="ANW11" s="34"/>
-      <c r="ANX11" s="34"/>
-      <c r="ANY11" s="34"/>
-      <c r="ANZ11" s="34"/>
-      <c r="AOA11" s="34"/>
-      <c r="AOB11" s="34"/>
-      <c r="AOC11" s="34"/>
-      <c r="AOD11" s="34"/>
-      <c r="AOE11" s="34"/>
-      <c r="AOF11" s="34"/>
-      <c r="AOG11" s="34"/>
-      <c r="AOH11" s="34"/>
-      <c r="AOI11" s="34"/>
-      <c r="AOJ11" s="34"/>
-      <c r="AOK11" s="34"/>
-      <c r="AOL11" s="34"/>
-      <c r="AOM11" s="34"/>
-      <c r="AON11" s="34"/>
-      <c r="AOO11" s="34"/>
-      <c r="AOP11" s="34"/>
-      <c r="AOQ11" s="34"/>
-      <c r="AOR11" s="34"/>
-      <c r="AOS11" s="34"/>
-      <c r="AOT11" s="34"/>
-      <c r="AOU11" s="34"/>
-      <c r="AOV11" s="34"/>
-      <c r="AOW11" s="34"/>
-      <c r="AOX11" s="34"/>
-      <c r="AOY11" s="34"/>
-      <c r="AOZ11" s="34"/>
-      <c r="APA11" s="34"/>
-      <c r="APB11" s="34"/>
-      <c r="APC11" s="34"/>
-      <c r="APD11" s="34"/>
-      <c r="APE11" s="34"/>
-      <c r="APF11" s="34"/>
-      <c r="APG11" s="34"/>
-      <c r="APH11" s="34"/>
-      <c r="API11" s="34"/>
-      <c r="APJ11" s="34"/>
-      <c r="APK11" s="34"/>
-      <c r="APL11" s="34"/>
-      <c r="APM11" s="34"/>
-      <c r="APN11" s="34"/>
-      <c r="APO11" s="34"/>
-      <c r="APP11" s="34"/>
-      <c r="APQ11" s="34"/>
-      <c r="APR11" s="34"/>
-      <c r="APS11" s="34"/>
-      <c r="APT11" s="34"/>
-      <c r="APU11" s="34"/>
-      <c r="APV11" s="34"/>
-      <c r="APW11" s="34"/>
-      <c r="APX11" s="34"/>
-      <c r="APY11" s="34"/>
-      <c r="APZ11" s="34"/>
-      <c r="AQA11" s="34"/>
-      <c r="AQB11" s="34"/>
-      <c r="AQC11" s="34"/>
-      <c r="AQD11" s="34"/>
-      <c r="AQE11" s="34"/>
-      <c r="AQF11" s="34"/>
-      <c r="AQG11" s="34"/>
-      <c r="AQH11" s="34"/>
-      <c r="AQI11" s="34"/>
-      <c r="AQJ11" s="34"/>
-      <c r="AQK11" s="34"/>
-      <c r="AQL11" s="34"/>
-      <c r="AQM11" s="34"/>
-      <c r="AQN11" s="34"/>
-      <c r="AQO11" s="34"/>
-      <c r="AQP11" s="34"/>
-      <c r="AQQ11" s="34"/>
-      <c r="AQR11" s="34"/>
-      <c r="AQS11" s="34"/>
-      <c r="AQT11" s="34"/>
-      <c r="AQU11" s="34"/>
-      <c r="AQV11" s="34"/>
-      <c r="AQW11" s="34"/>
-      <c r="AQX11" s="34"/>
-      <c r="AQY11" s="34"/>
-      <c r="AQZ11" s="34"/>
-      <c r="ARA11" s="34"/>
-      <c r="ARB11" s="34"/>
-      <c r="ARC11" s="34"/>
-      <c r="ARD11" s="34"/>
-      <c r="ARE11" s="34"/>
-      <c r="ARF11" s="34"/>
-      <c r="ARG11" s="34"/>
-      <c r="ARH11" s="34"/>
-      <c r="ARI11" s="34"/>
-      <c r="ARJ11" s="34"/>
-      <c r="ARK11" s="34"/>
-      <c r="ARL11" s="34"/>
-      <c r="ARM11" s="34"/>
-      <c r="ARN11" s="34"/>
-      <c r="ARO11" s="34"/>
-      <c r="ARP11" s="34"/>
-      <c r="ARQ11" s="34"/>
-      <c r="ARR11" s="34"/>
-      <c r="ARS11" s="34"/>
-      <c r="ART11" s="34"/>
-      <c r="ARU11" s="34"/>
-      <c r="ARV11" s="34"/>
-      <c r="ARW11" s="34"/>
-      <c r="ARX11" s="34"/>
-      <c r="ARY11" s="34"/>
-      <c r="ARZ11" s="34"/>
-      <c r="ASA11" s="34"/>
-      <c r="ASB11" s="34"/>
-      <c r="ASC11" s="34"/>
-      <c r="ASD11" s="34"/>
-      <c r="ASE11" s="34"/>
-      <c r="ASF11" s="34"/>
-      <c r="ASG11" s="34"/>
-      <c r="ASH11" s="34"/>
-      <c r="ASI11" s="34"/>
-      <c r="ASJ11" s="34"/>
-      <c r="ASK11" s="34"/>
-      <c r="ASL11" s="34"/>
-      <c r="ASM11" s="34"/>
-      <c r="ASN11" s="34"/>
-      <c r="ASO11" s="34"/>
-      <c r="ASP11" s="34"/>
-      <c r="ASQ11" s="34"/>
-      <c r="ASR11" s="34"/>
-      <c r="ASS11" s="34"/>
-      <c r="AST11" s="34"/>
-      <c r="ASU11" s="34"/>
-      <c r="ASV11" s="34"/>
-      <c r="ASW11" s="34"/>
-      <c r="ASX11" s="34"/>
-      <c r="ASY11" s="34"/>
-      <c r="ASZ11" s="34"/>
-      <c r="ATA11" s="34"/>
-      <c r="ATB11" s="34"/>
-      <c r="ATC11" s="34"/>
-      <c r="ATD11" s="34"/>
-      <c r="ATE11" s="34"/>
-      <c r="ATF11" s="34"/>
-      <c r="ATG11" s="34"/>
-      <c r="ATH11" s="34"/>
-      <c r="ATI11" s="34"/>
-      <c r="ATJ11" s="34"/>
-      <c r="ATK11" s="34"/>
-      <c r="ATL11" s="34"/>
-      <c r="ATM11" s="34"/>
-      <c r="ATN11" s="34"/>
-      <c r="ATO11" s="34"/>
-      <c r="ATP11" s="34"/>
-      <c r="ATQ11" s="34"/>
-      <c r="ATR11" s="34"/>
-      <c r="ATS11" s="34"/>
-      <c r="ATT11" s="34"/>
-      <c r="ATU11" s="34"/>
-      <c r="ATV11" s="34"/>
-      <c r="ATW11" s="34"/>
-      <c r="ATX11" s="34"/>
-      <c r="ATY11" s="34"/>
-      <c r="ATZ11" s="34"/>
-      <c r="AUA11" s="34"/>
-      <c r="AUB11" s="34"/>
-      <c r="AUC11" s="34"/>
-      <c r="AUD11" s="34"/>
-      <c r="AUE11" s="34"/>
-      <c r="AUF11" s="34"/>
-      <c r="AUG11" s="34"/>
-      <c r="AUH11" s="34"/>
-      <c r="AUI11" s="34"/>
-      <c r="AUJ11" s="34"/>
-      <c r="AUK11" s="34"/>
-      <c r="AUL11" s="34"/>
-      <c r="AUM11" s="34"/>
-      <c r="AUN11" s="34"/>
-      <c r="AUO11" s="34"/>
-      <c r="AUP11" s="34"/>
-      <c r="AUQ11" s="34"/>
-      <c r="AUR11" s="34"/>
-      <c r="AUS11" s="34"/>
-      <c r="AUT11" s="34"/>
-      <c r="AUU11" s="34"/>
-      <c r="AUV11" s="34"/>
-      <c r="AUW11" s="34"/>
-      <c r="AUX11" s="34"/>
-      <c r="AUY11" s="34"/>
-      <c r="AUZ11" s="34"/>
-      <c r="AVA11" s="34"/>
-      <c r="AVB11" s="34"/>
-      <c r="AVC11" s="34"/>
-      <c r="AVD11" s="34"/>
-      <c r="AVE11" s="34"/>
-      <c r="AVF11" s="34"/>
-      <c r="AVG11" s="34"/>
-      <c r="AVH11" s="34"/>
-      <c r="AVI11" s="34"/>
-      <c r="AVJ11" s="34"/>
-      <c r="AVK11" s="34"/>
-      <c r="AVL11" s="34"/>
-      <c r="AVM11" s="34"/>
-      <c r="AVN11" s="34"/>
-      <c r="AVO11" s="34"/>
-      <c r="AVP11" s="34"/>
-      <c r="AVQ11" s="34"/>
-      <c r="AVR11" s="34"/>
-      <c r="AVS11" s="34"/>
-      <c r="AVT11" s="34"/>
-      <c r="AVU11" s="34"/>
-      <c r="AVV11" s="34"/>
-      <c r="AVW11" s="34"/>
-      <c r="AVX11" s="34"/>
-      <c r="AVY11" s="34"/>
-      <c r="AVZ11" s="34"/>
-      <c r="AWA11" s="34"/>
-      <c r="AWB11" s="34"/>
-      <c r="AWC11" s="34"/>
-      <c r="AWD11" s="34"/>
-      <c r="AWE11" s="34"/>
-      <c r="AWF11" s="34"/>
-      <c r="AWG11" s="34"/>
-      <c r="AWH11" s="34"/>
-      <c r="AWI11" s="34"/>
-      <c r="AWJ11" s="34"/>
-      <c r="AWK11" s="34"/>
-      <c r="AWL11" s="34"/>
-      <c r="AWM11" s="34"/>
-      <c r="AWN11" s="34"/>
-      <c r="AWO11" s="34"/>
-      <c r="AWP11" s="34"/>
-      <c r="AWQ11" s="34"/>
-      <c r="AWR11" s="34"/>
-      <c r="AWS11" s="34"/>
-      <c r="AWT11" s="34"/>
-      <c r="AWU11" s="34"/>
-      <c r="AWV11" s="34"/>
-      <c r="AWW11" s="34"/>
-      <c r="AWX11" s="34"/>
-      <c r="AWY11" s="34"/>
-      <c r="AWZ11" s="34"/>
-      <c r="AXA11" s="34"/>
-      <c r="AXB11" s="34"/>
-      <c r="AXC11" s="34"/>
-      <c r="AXD11" s="34"/>
-      <c r="AXE11" s="34"/>
-      <c r="AXF11" s="34"/>
-      <c r="AXG11" s="34"/>
-      <c r="AXH11" s="34"/>
-      <c r="AXI11" s="34"/>
-      <c r="AXJ11" s="34"/>
-      <c r="AXK11" s="34"/>
-      <c r="AXL11" s="34"/>
-      <c r="AXM11" s="34"/>
-      <c r="AXN11" s="34"/>
-      <c r="AXO11" s="34"/>
-      <c r="AXP11" s="34"/>
-      <c r="AXQ11" s="34"/>
-      <c r="AXR11" s="34"/>
-      <c r="AXS11" s="34"/>
-      <c r="AXT11" s="34"/>
-      <c r="AXU11" s="34"/>
-      <c r="AXV11" s="34"/>
-      <c r="AXW11" s="34"/>
-      <c r="AXX11" s="34"/>
-      <c r="AXY11" s="34"/>
-      <c r="AXZ11" s="34"/>
-      <c r="AYA11" s="34"/>
-      <c r="AYB11" s="34"/>
-      <c r="AYC11" s="34"/>
-      <c r="AYD11" s="34"/>
-      <c r="AYE11" s="34"/>
-      <c r="AYF11" s="34"/>
-      <c r="AYG11" s="34"/>
-      <c r="AYH11" s="34"/>
-      <c r="AYI11" s="34"/>
-      <c r="AYJ11" s="34"/>
-      <c r="AYK11" s="34"/>
-      <c r="AYL11" s="34"/>
-      <c r="AYM11" s="34"/>
-      <c r="AYN11" s="34"/>
-      <c r="AYO11" s="34"/>
-      <c r="AYP11" s="34"/>
-      <c r="AYQ11" s="34"/>
-      <c r="AYR11" s="34"/>
-      <c r="AYS11" s="34"/>
-      <c r="AYT11" s="34"/>
-      <c r="AYU11" s="34"/>
-      <c r="AYV11" s="34"/>
-      <c r="AYW11" s="34"/>
-      <c r="AYX11" s="34"/>
-      <c r="AYY11" s="34"/>
-      <c r="AYZ11" s="34"/>
-      <c r="AZA11" s="34"/>
-      <c r="AZB11" s="34"/>
-      <c r="AZC11" s="34"/>
-      <c r="AZD11" s="34"/>
-      <c r="AZE11" s="34"/>
-      <c r="AZF11" s="34"/>
-      <c r="AZG11" s="34"/>
-      <c r="AZH11" s="34"/>
-      <c r="AZI11" s="34"/>
-      <c r="AZJ11" s="34"/>
-      <c r="AZK11" s="34"/>
-      <c r="AZL11" s="34"/>
-      <c r="AZM11" s="34"/>
-      <c r="AZN11" s="34"/>
-      <c r="AZO11" s="34"/>
-      <c r="AZP11" s="34"/>
-      <c r="AZQ11" s="34"/>
-      <c r="AZR11" s="34"/>
-      <c r="AZS11" s="34"/>
-      <c r="AZT11" s="34"/>
-      <c r="AZU11" s="34"/>
-      <c r="AZV11" s="34"/>
-      <c r="AZW11" s="34"/>
-      <c r="AZX11" s="34"/>
-      <c r="AZY11" s="34"/>
-      <c r="AZZ11" s="34"/>
-      <c r="BAA11" s="34"/>
-      <c r="BAB11" s="34"/>
-      <c r="BAC11" s="34"/>
-      <c r="BAD11" s="34"/>
-      <c r="BAE11" s="34"/>
-      <c r="BAF11" s="34"/>
-      <c r="BAG11" s="34"/>
-      <c r="BAH11" s="34"/>
-      <c r="BAI11" s="34"/>
-      <c r="BAJ11" s="34"/>
-      <c r="BAK11" s="34"/>
-      <c r="BAL11" s="34"/>
-      <c r="BAM11" s="34"/>
-      <c r="BAN11" s="34"/>
-      <c r="BAO11" s="34"/>
-      <c r="BAP11" s="34"/>
-      <c r="BAQ11" s="34"/>
-      <c r="BAR11" s="34"/>
-      <c r="BAS11" s="34"/>
-      <c r="BAT11" s="34"/>
-      <c r="BAU11" s="34"/>
-      <c r="BAV11" s="34"/>
-      <c r="BAW11" s="34"/>
-      <c r="BAX11" s="34"/>
-      <c r="BAY11" s="34"/>
-      <c r="BAZ11" s="34"/>
-      <c r="BBA11" s="34"/>
-      <c r="BBB11" s="34"/>
-      <c r="BBC11" s="34"/>
-      <c r="BBD11" s="34"/>
-      <c r="BBE11" s="34"/>
-      <c r="BBF11" s="34"/>
-      <c r="BBG11" s="34"/>
-      <c r="BBH11" s="34"/>
-      <c r="BBI11" s="34"/>
-      <c r="BBJ11" s="34"/>
-      <c r="BBK11" s="34"/>
-      <c r="BBL11" s="34"/>
-      <c r="BBM11" s="34"/>
-      <c r="BBN11" s="34"/>
-      <c r="BBO11" s="34"/>
-      <c r="BBP11" s="34"/>
-      <c r="BBQ11" s="34"/>
-      <c r="BBR11" s="34"/>
-      <c r="BBS11" s="34"/>
-      <c r="BBT11" s="34"/>
-      <c r="BBU11" s="34"/>
-      <c r="BBV11" s="34"/>
-      <c r="BBW11" s="34"/>
-      <c r="BBX11" s="34"/>
-      <c r="BBY11" s="34"/>
-      <c r="BBZ11" s="34"/>
-      <c r="BCA11" s="34"/>
-      <c r="BCB11" s="34"/>
-      <c r="BCC11" s="34"/>
-      <c r="BCD11" s="34"/>
-      <c r="BCE11" s="34"/>
-      <c r="BCF11" s="34"/>
-      <c r="BCG11" s="34"/>
-      <c r="BCH11" s="34"/>
-      <c r="BCI11" s="34"/>
-      <c r="BCJ11" s="34"/>
-      <c r="BCK11" s="34"/>
-      <c r="BCL11" s="34"/>
-      <c r="BCM11" s="34"/>
-      <c r="BCN11" s="34"/>
-      <c r="BCO11" s="34"/>
-      <c r="BCP11" s="34"/>
-      <c r="BCQ11" s="34"/>
-      <c r="BCR11" s="34"/>
-      <c r="BCS11" s="34"/>
-      <c r="BCT11" s="34"/>
-      <c r="BCU11" s="34"/>
-      <c r="BCV11" s="34"/>
-      <c r="BCW11" s="34"/>
-      <c r="BCX11" s="34"/>
-      <c r="BCY11" s="34"/>
-      <c r="BCZ11" s="34"/>
-      <c r="BDA11" s="34"/>
-      <c r="BDB11" s="34"/>
-      <c r="BDC11" s="34"/>
-      <c r="BDD11" s="34"/>
-      <c r="BDE11" s="34"/>
-      <c r="BDF11" s="34"/>
-      <c r="BDG11" s="34"/>
-      <c r="BDH11" s="34"/>
-      <c r="BDI11" s="34"/>
-      <c r="BDJ11" s="34"/>
-      <c r="BDK11" s="34"/>
-      <c r="BDL11" s="34"/>
-      <c r="BDM11" s="34"/>
-      <c r="BDN11" s="34"/>
-      <c r="BDO11" s="34"/>
-      <c r="BDP11" s="34"/>
-      <c r="BDQ11" s="34"/>
-      <c r="BDR11" s="34"/>
-      <c r="BDS11" s="34"/>
-      <c r="BDT11" s="34"/>
-      <c r="BDU11" s="34"/>
-      <c r="BDV11" s="34"/>
-      <c r="BDW11" s="34"/>
-      <c r="BDX11" s="34"/>
-      <c r="BDY11" s="34"/>
-      <c r="BDZ11" s="34"/>
-      <c r="BEA11" s="34"/>
-      <c r="BEB11" s="34"/>
-      <c r="BEC11" s="34"/>
-      <c r="BED11" s="34"/>
-      <c r="BEE11" s="34"/>
-      <c r="BEF11" s="34"/>
-      <c r="BEG11" s="34"/>
-      <c r="BEH11" s="34"/>
-      <c r="BEI11" s="34"/>
-      <c r="BEJ11" s="34"/>
-      <c r="BEK11" s="34"/>
-      <c r="BEL11" s="34"/>
-      <c r="BEM11" s="34"/>
-      <c r="BEN11" s="34"/>
-      <c r="BEO11" s="34"/>
-      <c r="BEP11" s="34"/>
-      <c r="BEQ11" s="34"/>
-      <c r="BER11" s="34"/>
-      <c r="BES11" s="34"/>
-      <c r="BET11" s="34"/>
-      <c r="BEU11" s="34"/>
-      <c r="BEV11" s="34"/>
-      <c r="BEW11" s="34"/>
-      <c r="BEX11" s="34"/>
-      <c r="BEY11" s="34"/>
-      <c r="BEZ11" s="34"/>
-      <c r="BFA11" s="34"/>
-      <c r="BFB11" s="34"/>
-      <c r="BFC11" s="34"/>
-      <c r="BFD11" s="34"/>
-      <c r="BFE11" s="34"/>
-      <c r="BFF11" s="34"/>
-      <c r="BFG11" s="34"/>
-      <c r="BFH11" s="34"/>
-      <c r="BFI11" s="34"/>
-      <c r="BFJ11" s="34"/>
-      <c r="BFK11" s="34"/>
-      <c r="BFL11" s="34"/>
-      <c r="BFM11" s="34"/>
-      <c r="BFN11" s="34"/>
-      <c r="BFO11" s="34"/>
-      <c r="BFP11" s="34"/>
-      <c r="BFQ11" s="34"/>
-      <c r="BFR11" s="34"/>
-      <c r="BFS11" s="34"/>
-      <c r="BFT11" s="34"/>
-      <c r="BFU11" s="34"/>
-      <c r="BFV11" s="34"/>
-      <c r="BFW11" s="34"/>
-      <c r="BFX11" s="34"/>
-      <c r="BFY11" s="34"/>
-      <c r="BFZ11" s="34"/>
-      <c r="BGA11" s="34"/>
-      <c r="BGB11" s="34"/>
-      <c r="BGC11" s="34"/>
-      <c r="BGD11" s="34"/>
-      <c r="BGE11" s="34"/>
-      <c r="BGF11" s="34"/>
-      <c r="BGG11" s="34"/>
-      <c r="BGH11" s="34"/>
-      <c r="BGI11" s="34"/>
-      <c r="BGJ11" s="34"/>
-      <c r="BGK11" s="34"/>
-      <c r="BGL11" s="34"/>
-      <c r="BGM11" s="34"/>
-      <c r="BGN11" s="34"/>
-      <c r="BGO11" s="34"/>
-      <c r="BGP11" s="34"/>
-      <c r="BGQ11" s="34"/>
-      <c r="BGR11" s="34"/>
-      <c r="BGS11" s="34"/>
-      <c r="BGT11" s="34"/>
-      <c r="BGU11" s="34"/>
-      <c r="BGV11" s="34"/>
-      <c r="BGW11" s="34"/>
-      <c r="BGX11" s="34"/>
-      <c r="BGY11" s="34"/>
-      <c r="BGZ11" s="34"/>
-      <c r="BHA11" s="34"/>
-      <c r="BHB11" s="34"/>
-      <c r="BHC11" s="34"/>
-      <c r="BHD11" s="34"/>
-      <c r="BHE11" s="34"/>
-      <c r="BHF11" s="34"/>
-      <c r="BHG11" s="34"/>
-      <c r="BHH11" s="34"/>
-      <c r="BHI11" s="34"/>
-      <c r="BHJ11" s="34"/>
-      <c r="BHK11" s="34"/>
-      <c r="BHL11" s="34"/>
-      <c r="BHM11" s="34"/>
-      <c r="BHN11" s="34"/>
-      <c r="BHO11" s="34"/>
-      <c r="BHP11" s="34"/>
-      <c r="BHQ11" s="34"/>
-      <c r="BHR11" s="34"/>
-      <c r="BHS11" s="34"/>
-      <c r="BHT11" s="34"/>
-      <c r="BHU11" s="34"/>
-      <c r="BHV11" s="34"/>
-      <c r="BHW11" s="34"/>
-      <c r="BHX11" s="34"/>
-      <c r="BHY11" s="34"/>
-      <c r="BHZ11" s="34"/>
-      <c r="BIA11" s="34"/>
-      <c r="BIB11" s="34"/>
-      <c r="BIC11" s="34"/>
-      <c r="BID11" s="34"/>
-      <c r="BIE11" s="34"/>
-      <c r="BIF11" s="34"/>
-      <c r="BIG11" s="34"/>
-      <c r="BIH11" s="34"/>
-      <c r="BII11" s="34"/>
-      <c r="BIJ11" s="34"/>
-      <c r="BIK11" s="34"/>
-      <c r="BIL11" s="34"/>
-      <c r="BIM11" s="34"/>
-      <c r="BIN11" s="34"/>
-      <c r="BIO11" s="34"/>
-      <c r="BIP11" s="34"/>
-      <c r="BIQ11" s="34"/>
-      <c r="BIR11" s="34"/>
-      <c r="BIS11" s="34"/>
-      <c r="BIT11" s="34"/>
-      <c r="BIU11" s="34"/>
-      <c r="BIV11" s="34"/>
-      <c r="BIW11" s="34"/>
-      <c r="BIX11" s="34"/>
-      <c r="BIY11" s="34"/>
-      <c r="BIZ11" s="34"/>
-      <c r="BJA11" s="34"/>
-      <c r="BJB11" s="34"/>
-      <c r="BJC11" s="34"/>
-      <c r="BJD11" s="34"/>
-      <c r="BJE11" s="34"/>
-      <c r="BJF11" s="34"/>
-      <c r="BJG11" s="34"/>
-      <c r="BJH11" s="34"/>
-      <c r="BJI11" s="34"/>
-      <c r="BJJ11" s="34"/>
-      <c r="BJK11" s="34"/>
-      <c r="BJL11" s="34"/>
-      <c r="BJM11" s="34"/>
-      <c r="BJN11" s="34"/>
-      <c r="BJO11" s="34"/>
-      <c r="BJP11" s="34"/>
-      <c r="BJQ11" s="34"/>
-      <c r="BJR11" s="34"/>
-      <c r="BJS11" s="34"/>
-      <c r="BJT11" s="34"/>
-      <c r="BJU11" s="34"/>
-      <c r="BJV11" s="34"/>
-      <c r="BJW11" s="34"/>
-      <c r="BJX11" s="34"/>
-      <c r="BJY11" s="34"/>
-      <c r="BJZ11" s="34"/>
-      <c r="BKA11" s="34"/>
-      <c r="BKB11" s="34"/>
-      <c r="BKC11" s="34"/>
-      <c r="BKD11" s="34"/>
-      <c r="BKE11" s="34"/>
-      <c r="BKF11" s="34"/>
-      <c r="BKG11" s="34"/>
-      <c r="BKH11" s="34"/>
-      <c r="BKI11" s="34"/>
-      <c r="BKJ11" s="34"/>
-      <c r="BKK11" s="34"/>
-      <c r="BKL11" s="34"/>
-      <c r="BKM11" s="34"/>
-      <c r="BKN11" s="34"/>
-      <c r="BKO11" s="34"/>
-      <c r="BKP11" s="34"/>
-      <c r="BKQ11" s="34"/>
-      <c r="BKR11" s="34"/>
-      <c r="BKS11" s="34"/>
-      <c r="BKT11" s="34"/>
-      <c r="BKU11" s="34"/>
-      <c r="BKV11" s="34"/>
-      <c r="BKW11" s="34"/>
-      <c r="BKX11" s="34"/>
-      <c r="BKY11" s="34"/>
-      <c r="BKZ11" s="34"/>
-      <c r="BLA11" s="34"/>
-      <c r="BLB11" s="34"/>
-      <c r="BLC11" s="34"/>
-      <c r="BLD11" s="34"/>
-      <c r="BLE11" s="34"/>
-      <c r="BLF11" s="34"/>
-      <c r="BLG11" s="34"/>
-      <c r="BLH11" s="34"/>
-      <c r="BLI11" s="34"/>
-      <c r="BLJ11" s="34"/>
-      <c r="BLK11" s="34"/>
-      <c r="BLL11" s="34"/>
-      <c r="BLM11" s="34"/>
-      <c r="BLN11" s="34"/>
-      <c r="BLO11" s="34"/>
-      <c r="BLP11" s="34"/>
-      <c r="BLQ11" s="34"/>
-      <c r="BLR11" s="34"/>
-      <c r="BLS11" s="34"/>
-      <c r="BLT11" s="34"/>
-      <c r="BLU11" s="34"/>
-      <c r="BLV11" s="34"/>
-      <c r="BLW11" s="34"/>
-      <c r="BLX11" s="34"/>
-      <c r="BLY11" s="34"/>
-      <c r="BLZ11" s="34"/>
-      <c r="BMA11" s="34"/>
-      <c r="BMB11" s="34"/>
-      <c r="BMC11" s="34"/>
-      <c r="BMD11" s="34"/>
-      <c r="BME11" s="34"/>
-      <c r="BMF11" s="34"/>
-      <c r="BMG11" s="34"/>
-      <c r="BMH11" s="34"/>
-      <c r="BMI11" s="34"/>
-      <c r="BMJ11" s="34"/>
-      <c r="BMK11" s="34"/>
-      <c r="BML11" s="34"/>
-      <c r="BMM11" s="34"/>
-      <c r="BMN11" s="34"/>
-      <c r="BMO11" s="34"/>
-      <c r="BMP11" s="34"/>
-      <c r="BMQ11" s="34"/>
-      <c r="BMR11" s="34"/>
-      <c r="BMS11" s="34"/>
-      <c r="BMT11" s="34"/>
-      <c r="BMU11" s="34"/>
-      <c r="BMV11" s="34"/>
-      <c r="BMW11" s="34"/>
-      <c r="BMX11" s="34"/>
-      <c r="BMY11" s="34"/>
-      <c r="BMZ11" s="34"/>
-      <c r="BNA11" s="34"/>
-      <c r="BNB11" s="34"/>
-      <c r="BNC11" s="34"/>
-      <c r="BND11" s="34"/>
-      <c r="BNE11" s="34"/>
-      <c r="BNF11" s="34"/>
-      <c r="BNG11" s="34"/>
-      <c r="BNH11" s="34"/>
-      <c r="BNI11" s="34"/>
-      <c r="BNJ11" s="34"/>
-      <c r="BNK11" s="34"/>
-      <c r="BNL11" s="34"/>
-      <c r="BNM11" s="34"/>
-      <c r="BNN11" s="34"/>
-      <c r="BNO11" s="34"/>
-      <c r="BNP11" s="34"/>
-      <c r="BNQ11" s="34"/>
-      <c r="BNR11" s="34"/>
-      <c r="BNS11" s="34"/>
-      <c r="BNT11" s="34"/>
-      <c r="BNU11" s="34"/>
-      <c r="BNV11" s="34"/>
-      <c r="BNW11" s="34"/>
-      <c r="BNX11" s="34"/>
-      <c r="BNY11" s="34"/>
-      <c r="BNZ11" s="34"/>
-      <c r="BOA11" s="34"/>
-      <c r="BOB11" s="34"/>
-      <c r="BOC11" s="34"/>
-      <c r="BOD11" s="34"/>
-      <c r="BOE11" s="34"/>
-      <c r="BOF11" s="34"/>
-      <c r="BOG11" s="34"/>
-      <c r="BOH11" s="34"/>
-      <c r="BOI11" s="34"/>
-      <c r="BOJ11" s="34"/>
-      <c r="BOK11" s="34"/>
-      <c r="BOL11" s="34"/>
-      <c r="BOM11" s="34"/>
-      <c r="BON11" s="34"/>
-      <c r="BOO11" s="34"/>
-      <c r="BOP11" s="34"/>
-      <c r="BOQ11" s="34"/>
-      <c r="BOR11" s="34"/>
-      <c r="BOS11" s="34"/>
-      <c r="BOT11" s="34"/>
-      <c r="BOU11" s="34"/>
-      <c r="BOV11" s="34"/>
-      <c r="BOW11" s="34"/>
-      <c r="BOX11" s="34"/>
-      <c r="BOY11" s="34"/>
-      <c r="BOZ11" s="34"/>
-      <c r="BPA11" s="34"/>
-      <c r="BPB11" s="34"/>
-      <c r="BPC11" s="34"/>
-      <c r="BPD11" s="34"/>
-      <c r="BPE11" s="34"/>
-      <c r="BPF11" s="34"/>
-      <c r="BPG11" s="34"/>
-      <c r="BPH11" s="34"/>
-      <c r="BPI11" s="34"/>
-      <c r="BPJ11" s="34"/>
-      <c r="BPK11" s="34"/>
-      <c r="BPL11" s="34"/>
-      <c r="BPM11" s="34"/>
-      <c r="BPN11" s="34"/>
-      <c r="BPO11" s="34"/>
-      <c r="BPP11" s="34"/>
-      <c r="BPQ11" s="34"/>
-      <c r="BPR11" s="34"/>
-      <c r="BPS11" s="34"/>
-      <c r="BPT11" s="34"/>
-      <c r="BPU11" s="34"/>
-      <c r="BPV11" s="34"/>
-      <c r="BPW11" s="34"/>
-      <c r="BPX11" s="34"/>
-      <c r="BPY11" s="34"/>
-      <c r="BPZ11" s="34"/>
-      <c r="BQA11" s="34"/>
-      <c r="BQB11" s="34"/>
-      <c r="BQC11" s="34"/>
-      <c r="BQD11" s="34"/>
-      <c r="BQE11" s="34"/>
-      <c r="BQF11" s="34"/>
-      <c r="BQG11" s="34"/>
-      <c r="BQH11" s="34"/>
-      <c r="BQI11" s="34"/>
-      <c r="BQJ11" s="34"/>
-      <c r="BQK11" s="34"/>
-      <c r="BQL11" s="34"/>
-      <c r="BQM11" s="34"/>
-      <c r="BQN11" s="34"/>
-      <c r="BQO11" s="34"/>
-      <c r="BQP11" s="34"/>
-      <c r="BQQ11" s="34"/>
-      <c r="BQR11" s="34"/>
-      <c r="BQS11" s="34"/>
-      <c r="BQT11" s="34"/>
-      <c r="BQU11" s="34"/>
-      <c r="BQV11" s="34"/>
-      <c r="BQW11" s="34"/>
-      <c r="BQX11" s="34"/>
-      <c r="BQY11" s="34"/>
-      <c r="BQZ11" s="34"/>
-      <c r="BRA11" s="34"/>
-      <c r="BRB11" s="34"/>
-      <c r="BRC11" s="34"/>
-      <c r="BRD11" s="34"/>
-      <c r="BRE11" s="34"/>
-      <c r="BRF11" s="34"/>
-      <c r="BRG11" s="34"/>
-      <c r="BRH11" s="34"/>
-      <c r="BRI11" s="34"/>
-      <c r="BRJ11" s="34"/>
-      <c r="BRK11" s="34"/>
-      <c r="BRL11" s="34"/>
-      <c r="BRM11" s="34"/>
-      <c r="BRN11" s="34"/>
-      <c r="BRO11" s="34"/>
-      <c r="BRP11" s="34"/>
-      <c r="BRQ11" s="34"/>
-      <c r="BRR11" s="34"/>
-      <c r="BRS11" s="34"/>
-      <c r="BRT11" s="34"/>
-      <c r="BRU11" s="34"/>
-      <c r="BRV11" s="34"/>
-      <c r="BRW11" s="34"/>
-      <c r="BRX11" s="34"/>
-      <c r="BRY11" s="34"/>
-      <c r="BRZ11" s="34"/>
-      <c r="BSA11" s="34"/>
-      <c r="BSB11" s="34"/>
-      <c r="BSC11" s="34"/>
-      <c r="BSD11" s="34"/>
-      <c r="BSE11" s="34"/>
-      <c r="BSF11" s="34"/>
-      <c r="BSG11" s="34"/>
-      <c r="BSH11" s="34"/>
-      <c r="BSI11" s="34"/>
-      <c r="BSJ11" s="34"/>
-      <c r="BSK11" s="34"/>
-      <c r="BSL11" s="34"/>
-      <c r="BSM11" s="34"/>
-      <c r="BSN11" s="34"/>
-      <c r="BSO11" s="34"/>
-      <c r="BSP11" s="34"/>
-      <c r="BSQ11" s="34"/>
-      <c r="BSR11" s="34"/>
-      <c r="BSS11" s="34"/>
-      <c r="BST11" s="34"/>
-      <c r="BSU11" s="34"/>
-      <c r="BSV11" s="34"/>
-      <c r="BSW11" s="34"/>
-      <c r="BSX11" s="34"/>
-      <c r="BSY11" s="34"/>
-      <c r="BSZ11" s="34"/>
-      <c r="BTA11" s="34"/>
-      <c r="BTB11" s="34"/>
-      <c r="BTC11" s="34"/>
-      <c r="BTD11" s="34"/>
-      <c r="BTE11" s="34"/>
-      <c r="BTF11" s="34"/>
-      <c r="BTG11" s="34"/>
-      <c r="BTH11" s="34"/>
-      <c r="BTI11" s="34"/>
-      <c r="BTJ11" s="34"/>
-      <c r="BTK11" s="34"/>
-      <c r="BTL11" s="34"/>
-      <c r="BTM11" s="34"/>
-      <c r="BTN11" s="34"/>
-      <c r="BTO11" s="34"/>
-      <c r="BTP11" s="34"/>
-      <c r="BTQ11" s="34"/>
-      <c r="BTR11" s="34"/>
-      <c r="BTS11" s="34"/>
-      <c r="BTT11" s="34"/>
-      <c r="BTU11" s="34"/>
-      <c r="BTV11" s="34"/>
-      <c r="BTW11" s="34"/>
-      <c r="BTX11" s="34"/>
-      <c r="BTY11" s="34"/>
-      <c r="BTZ11" s="34"/>
-      <c r="BUA11" s="34"/>
-      <c r="BUB11" s="34"/>
-      <c r="BUC11" s="34"/>
-      <c r="BUD11" s="34"/>
-      <c r="BUE11" s="34"/>
-      <c r="BUF11" s="34"/>
-      <c r="BUG11" s="34"/>
-      <c r="BUH11" s="34"/>
-      <c r="BUI11" s="34"/>
-      <c r="BUJ11" s="34"/>
-      <c r="BUK11" s="34"/>
-      <c r="BUL11" s="34"/>
-      <c r="BUM11" s="34"/>
-      <c r="BUN11" s="34"/>
-      <c r="BUO11" s="34"/>
-      <c r="BUP11" s="34"/>
-      <c r="BUQ11" s="34"/>
-      <c r="BUR11" s="34"/>
-      <c r="BUS11" s="34"/>
-      <c r="BUT11" s="34"/>
-      <c r="BUU11" s="34"/>
-      <c r="BUV11" s="34"/>
-      <c r="BUW11" s="34"/>
-      <c r="BUX11" s="34"/>
-      <c r="BUY11" s="34"/>
-      <c r="BUZ11" s="34"/>
-      <c r="BVA11" s="34"/>
-      <c r="BVB11" s="34"/>
-      <c r="BVC11" s="34"/>
-      <c r="BVD11" s="34"/>
-      <c r="BVE11" s="34"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="39"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="39"/>
+      <c r="V11" s="33"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="38"/>
+      <c r="Y11" s="39"/>
+      <c r="Z11" s="33"/>
+      <c r="AA11" s="33"/>
+      <c r="AB11" s="33"/>
+      <c r="AC11" s="33"/>
+      <c r="AD11" s="38"/>
+      <c r="AE11" s="39"/>
+      <c r="AF11" s="38"/>
+      <c r="AG11" s="33"/>
+      <c r="AH11" s="33"/>
+      <c r="AI11" s="33"/>
+      <c r="AJ11" s="33"/>
+      <c r="AK11" s="40"/>
+      <c r="AL11" s="30"/>
+      <c r="AM11" s="29"/>
+      <c r="AN11" s="29"/>
+      <c r="AO11" s="29"/>
+      <c r="AP11" s="29"/>
+      <c r="AQ11" s="29"/>
+      <c r="AR11" s="29"/>
+      <c r="AS11" s="29"/>
+      <c r="AT11" s="29"/>
+      <c r="AU11" s="29"/>
+      <c r="AV11" s="29"/>
+      <c r="AW11" s="29"/>
+      <c r="AX11" s="29"/>
+      <c r="AY11" s="29"/>
+      <c r="AZ11" s="29"/>
+      <c r="BA11" s="29"/>
+      <c r="BB11" s="29"/>
+      <c r="BC11" s="29"/>
+      <c r="BD11" s="29"/>
+      <c r="BE11" s="29"/>
+      <c r="BF11" s="29"/>
+      <c r="BG11" s="29"/>
+      <c r="BH11" s="29"/>
+      <c r="BI11" s="29"/>
+      <c r="BJ11" s="29"/>
+      <c r="BK11" s="29"/>
+      <c r="BL11" s="29"/>
+      <c r="BM11" s="29"/>
+      <c r="BN11" s="29"/>
+      <c r="BO11" s="29"/>
+      <c r="BP11" s="29"/>
+      <c r="BQ11" s="29"/>
+      <c r="BR11" s="29"/>
+      <c r="BS11" s="29"/>
+      <c r="BT11" s="29"/>
+      <c r="BU11" s="29"/>
+      <c r="BV11" s="29"/>
+      <c r="BW11" s="29"/>
+      <c r="BX11" s="29"/>
+      <c r="BY11" s="29"/>
+      <c r="BZ11" s="29"/>
+      <c r="CA11" s="29"/>
+      <c r="CB11" s="29"/>
+      <c r="CC11" s="29"/>
+      <c r="CD11" s="29"/>
+      <c r="CE11" s="29"/>
+      <c r="CF11" s="29"/>
+      <c r="CG11" s="29"/>
+      <c r="CH11" s="29"/>
+      <c r="CI11" s="29"/>
+      <c r="CJ11" s="29"/>
+      <c r="CK11" s="29"/>
+      <c r="CL11" s="29"/>
+      <c r="CM11" s="29"/>
+      <c r="CN11" s="29"/>
+      <c r="CO11" s="29"/>
+      <c r="CP11" s="29"/>
+      <c r="CQ11" s="29"/>
+      <c r="CR11" s="29"/>
+      <c r="CS11" s="29"/>
+      <c r="CT11" s="29"/>
+      <c r="CU11" s="29"/>
+      <c r="CV11" s="29"/>
+      <c r="CW11" s="29"/>
+      <c r="CX11" s="29"/>
+      <c r="CY11" s="29"/>
+      <c r="CZ11" s="29"/>
+      <c r="DA11" s="29"/>
+      <c r="DB11" s="29"/>
+      <c r="DC11" s="29"/>
+      <c r="DD11" s="29"/>
+      <c r="DE11" s="29"/>
+      <c r="DF11" s="29"/>
+      <c r="DG11" s="29"/>
+      <c r="DH11" s="29"/>
+      <c r="DI11" s="29"/>
+      <c r="DJ11" s="29"/>
+      <c r="DK11" s="29"/>
+      <c r="DL11" s="29"/>
+      <c r="DM11" s="29"/>
+      <c r="DN11" s="29"/>
+      <c r="DO11" s="29"/>
+      <c r="DP11" s="29"/>
+      <c r="DQ11" s="29"/>
+      <c r="DR11" s="29"/>
+      <c r="DS11" s="29"/>
+      <c r="DT11" s="29"/>
+      <c r="DU11" s="29"/>
+      <c r="DV11" s="29"/>
+      <c r="DW11" s="29"/>
+      <c r="DX11" s="29"/>
+      <c r="DY11" s="29"/>
+      <c r="DZ11" s="29"/>
+      <c r="EA11" s="29"/>
+      <c r="EB11" s="29"/>
+      <c r="EC11" s="29"/>
+      <c r="ED11" s="29"/>
+      <c r="EE11" s="29"/>
+      <c r="EF11" s="29"/>
+      <c r="EG11" s="29"/>
+      <c r="EH11" s="29"/>
+      <c r="EI11" s="29"/>
+      <c r="EJ11" s="29"/>
+      <c r="EK11" s="29"/>
+      <c r="EL11" s="29"/>
+      <c r="EM11" s="29"/>
+      <c r="EN11" s="29"/>
+      <c r="EO11" s="29"/>
+      <c r="EP11" s="29"/>
+      <c r="EQ11" s="29"/>
+      <c r="ER11" s="29"/>
+      <c r="ES11" s="29"/>
+      <c r="ET11" s="29"/>
+      <c r="EU11" s="29"/>
+      <c r="EV11" s="29"/>
+      <c r="EW11" s="29"/>
+      <c r="EX11" s="29"/>
+      <c r="EY11" s="29"/>
+      <c r="EZ11" s="29"/>
+      <c r="FA11" s="29"/>
+      <c r="FB11" s="29"/>
+      <c r="FC11" s="29"/>
+      <c r="FD11" s="29"/>
+      <c r="FE11" s="29"/>
+      <c r="FF11" s="29"/>
+      <c r="FG11" s="29"/>
+      <c r="FH11" s="29"/>
+      <c r="FI11" s="29"/>
+      <c r="FJ11" s="29"/>
+      <c r="FK11" s="29"/>
+      <c r="FL11" s="29"/>
+      <c r="FM11" s="29"/>
+      <c r="FN11" s="29"/>
+      <c r="FO11" s="29"/>
+      <c r="FP11" s="29"/>
+      <c r="FQ11" s="29"/>
+      <c r="FR11" s="29"/>
+      <c r="FS11" s="29"/>
+      <c r="FT11" s="29"/>
+      <c r="FU11" s="29"/>
+      <c r="FV11" s="29"/>
+      <c r="FW11" s="29"/>
+      <c r="FX11" s="29"/>
+      <c r="FY11" s="29"/>
+      <c r="FZ11" s="29"/>
+      <c r="GA11" s="29"/>
+      <c r="GB11" s="29"/>
+      <c r="GC11" s="29"/>
+      <c r="GD11" s="29"/>
+      <c r="GE11" s="29"/>
+      <c r="GF11" s="29"/>
+      <c r="GG11" s="29"/>
+      <c r="GH11" s="29"/>
+      <c r="GI11" s="29"/>
+      <c r="GJ11" s="29"/>
+      <c r="GK11" s="29"/>
+      <c r="GL11" s="29"/>
+      <c r="GM11" s="29"/>
+      <c r="GN11" s="29"/>
+      <c r="GO11" s="29"/>
+      <c r="GP11" s="29"/>
+      <c r="GQ11" s="29"/>
+      <c r="GR11" s="29"/>
+      <c r="GS11" s="29"/>
+      <c r="GT11" s="29"/>
+      <c r="GU11" s="29"/>
+      <c r="GV11" s="29"/>
+      <c r="GW11" s="29"/>
+      <c r="GX11" s="29"/>
+      <c r="GY11" s="29"/>
+      <c r="GZ11" s="29"/>
+      <c r="HA11" s="29"/>
+      <c r="HB11" s="29"/>
+      <c r="HC11" s="29"/>
+      <c r="HD11" s="29"/>
+      <c r="HE11" s="29"/>
+      <c r="HF11" s="29"/>
+      <c r="HG11" s="29"/>
+      <c r="HH11" s="29"/>
+      <c r="HI11" s="29"/>
+      <c r="HJ11" s="29"/>
+      <c r="HK11" s="29"/>
+      <c r="HL11" s="29"/>
+      <c r="HM11" s="29"/>
+      <c r="HN11" s="29"/>
+      <c r="HO11" s="29"/>
+      <c r="HP11" s="29"/>
+      <c r="HQ11" s="29"/>
+      <c r="HR11" s="29"/>
+      <c r="HS11" s="29"/>
+      <c r="HT11" s="29"/>
+      <c r="HU11" s="29"/>
+      <c r="HV11" s="29"/>
+      <c r="HW11" s="29"/>
+      <c r="HX11" s="29"/>
+      <c r="HY11" s="29"/>
+      <c r="HZ11" s="29"/>
+      <c r="IA11" s="29"/>
+      <c r="IB11" s="29"/>
+      <c r="IC11" s="29"/>
+      <c r="ID11" s="29"/>
+      <c r="IE11" s="29"/>
+      <c r="IF11" s="29"/>
+      <c r="IG11" s="29"/>
+      <c r="IH11" s="29"/>
+      <c r="II11" s="29"/>
+      <c r="IJ11" s="29"/>
+      <c r="IK11" s="29"/>
+      <c r="IL11" s="29"/>
+      <c r="IM11" s="29"/>
+      <c r="IN11" s="29"/>
+      <c r="IO11" s="29"/>
+      <c r="IP11" s="29"/>
+      <c r="IQ11" s="29"/>
+      <c r="IR11" s="29"/>
+      <c r="IS11" s="29"/>
+      <c r="IT11" s="29"/>
+      <c r="IU11" s="29"/>
+      <c r="IV11" s="29"/>
+      <c r="IW11" s="29"/>
+      <c r="IX11" s="29"/>
+      <c r="IY11" s="29"/>
+      <c r="IZ11" s="29"/>
+      <c r="JA11" s="29"/>
+      <c r="JB11" s="29"/>
+      <c r="JC11" s="29"/>
+      <c r="JD11" s="29"/>
+      <c r="JE11" s="29"/>
+      <c r="JF11" s="29"/>
+      <c r="JG11" s="29"/>
+      <c r="JH11" s="29"/>
+      <c r="JI11" s="29"/>
+      <c r="JJ11" s="29"/>
+      <c r="JK11" s="29"/>
+      <c r="JL11" s="29"/>
+      <c r="JM11" s="29"/>
+      <c r="JN11" s="29"/>
+      <c r="JO11" s="29"/>
+      <c r="JP11" s="29"/>
+      <c r="JQ11" s="29"/>
+      <c r="JR11" s="29"/>
+      <c r="JS11" s="29"/>
+      <c r="JT11" s="29"/>
+      <c r="JU11" s="29"/>
+      <c r="JV11" s="29"/>
+      <c r="JW11" s="29"/>
+      <c r="JX11" s="29"/>
+      <c r="JY11" s="29"/>
+      <c r="JZ11" s="29"/>
+      <c r="KA11" s="29"/>
+      <c r="KB11" s="29"/>
+      <c r="KC11" s="29"/>
+      <c r="KD11" s="29"/>
+      <c r="KE11" s="29"/>
+      <c r="KF11" s="29"/>
+      <c r="KG11" s="29"/>
+      <c r="KH11" s="29"/>
+      <c r="KI11" s="29"/>
+      <c r="KJ11" s="29"/>
+      <c r="KK11" s="29"/>
+      <c r="KL11" s="29"/>
+      <c r="KM11" s="29"/>
+      <c r="KN11" s="29"/>
+      <c r="KO11" s="29"/>
+      <c r="KP11" s="29"/>
+      <c r="KQ11" s="29"/>
+      <c r="KR11" s="29"/>
+      <c r="KS11" s="29"/>
+      <c r="KT11" s="29"/>
+      <c r="KU11" s="29"/>
+      <c r="KV11" s="29"/>
+      <c r="KW11" s="29"/>
+      <c r="KX11" s="29"/>
+      <c r="KY11" s="29"/>
+      <c r="KZ11" s="29"/>
+      <c r="LA11" s="29"/>
+      <c r="LB11" s="29"/>
+      <c r="LC11" s="29"/>
+      <c r="LD11" s="29"/>
+      <c r="LE11" s="29"/>
+      <c r="LF11" s="29"/>
+      <c r="LG11" s="29"/>
+      <c r="LH11" s="29"/>
+      <c r="LI11" s="29"/>
+      <c r="LJ11" s="29"/>
+      <c r="LK11" s="29"/>
+      <c r="LL11" s="29"/>
+      <c r="LM11" s="29"/>
+      <c r="LN11" s="29"/>
+      <c r="LO11" s="29"/>
+      <c r="LP11" s="29"/>
+      <c r="LQ11" s="29"/>
+      <c r="LR11" s="29"/>
+      <c r="LS11" s="29"/>
+      <c r="LT11" s="29"/>
+      <c r="LU11" s="29"/>
+      <c r="LV11" s="29"/>
+      <c r="LW11" s="29"/>
+      <c r="LX11" s="29"/>
+      <c r="LY11" s="29"/>
+      <c r="LZ11" s="29"/>
+      <c r="MA11" s="29"/>
+      <c r="MB11" s="29"/>
+      <c r="MC11" s="29"/>
+      <c r="MD11" s="29"/>
+      <c r="ME11" s="29"/>
+      <c r="MF11" s="29"/>
+      <c r="MG11" s="29"/>
+      <c r="MH11" s="29"/>
+      <c r="MI11" s="29"/>
+      <c r="MJ11" s="29"/>
+      <c r="MK11" s="29"/>
+      <c r="ML11" s="29"/>
+      <c r="MM11" s="29"/>
+      <c r="MN11" s="29"/>
+      <c r="MO11" s="29"/>
+      <c r="MP11" s="29"/>
+      <c r="MQ11" s="29"/>
+      <c r="MR11" s="29"/>
+      <c r="MS11" s="29"/>
+      <c r="MT11" s="29"/>
+      <c r="MU11" s="29"/>
+      <c r="MV11" s="29"/>
+      <c r="MW11" s="29"/>
+      <c r="MX11" s="29"/>
+      <c r="MY11" s="29"/>
+      <c r="MZ11" s="29"/>
+      <c r="NA11" s="29"/>
+      <c r="NB11" s="29"/>
+      <c r="NC11" s="29"/>
+      <c r="ND11" s="29"/>
+      <c r="NE11" s="29"/>
+      <c r="NF11" s="29"/>
+      <c r="NG11" s="29"/>
+      <c r="NH11" s="29"/>
+      <c r="NI11" s="29"/>
+      <c r="NJ11" s="29"/>
+      <c r="NK11" s="29"/>
+      <c r="NL11" s="29"/>
+      <c r="NM11" s="29"/>
+      <c r="NN11" s="29"/>
+      <c r="NO11" s="29"/>
+      <c r="NP11" s="29"/>
+      <c r="NQ11" s="29"/>
+      <c r="NR11" s="29"/>
+      <c r="NS11" s="29"/>
+      <c r="NT11" s="29"/>
+      <c r="NU11" s="29"/>
+      <c r="NV11" s="29"/>
+      <c r="NW11" s="29"/>
+      <c r="NX11" s="29"/>
+      <c r="NY11" s="29"/>
+      <c r="NZ11" s="29"/>
+      <c r="OA11" s="29"/>
+      <c r="OB11" s="29"/>
+      <c r="OC11" s="29"/>
+      <c r="OD11" s="29"/>
+      <c r="OE11" s="29"/>
+      <c r="OF11" s="29"/>
+      <c r="OG11" s="29"/>
+      <c r="OH11" s="29"/>
+      <c r="OI11" s="29"/>
+      <c r="OJ11" s="29"/>
+      <c r="OK11" s="29"/>
+      <c r="OL11" s="29"/>
+      <c r="OM11" s="29"/>
+      <c r="ON11" s="29"/>
+      <c r="OO11" s="29"/>
+      <c r="OP11" s="29"/>
+      <c r="OQ11" s="29"/>
+      <c r="OR11" s="29"/>
+      <c r="OS11" s="29"/>
+      <c r="OT11" s="29"/>
+      <c r="OU11" s="29"/>
+      <c r="OV11" s="29"/>
+      <c r="OW11" s="29"/>
+      <c r="OX11" s="29"/>
+      <c r="OY11" s="29"/>
+      <c r="OZ11" s="29"/>
+      <c r="PA11" s="29"/>
+      <c r="PB11" s="29"/>
+      <c r="PC11" s="29"/>
+      <c r="PD11" s="29"/>
+      <c r="PE11" s="29"/>
+      <c r="PF11" s="29"/>
+      <c r="PG11" s="29"/>
+      <c r="PH11" s="29"/>
+      <c r="PI11" s="29"/>
+      <c r="PJ11" s="29"/>
+      <c r="PK11" s="29"/>
+      <c r="PL11" s="29"/>
+      <c r="PM11" s="29"/>
+      <c r="PN11" s="29"/>
+      <c r="PO11" s="29"/>
+      <c r="PP11" s="29"/>
+      <c r="PQ11" s="29"/>
+      <c r="PR11" s="29"/>
+      <c r="PS11" s="29"/>
+      <c r="PT11" s="29"/>
+      <c r="PU11" s="29"/>
+      <c r="PV11" s="29"/>
+      <c r="PW11" s="29"/>
+      <c r="PX11" s="29"/>
+      <c r="PY11" s="29"/>
+      <c r="PZ11" s="29"/>
+      <c r="QA11" s="29"/>
+      <c r="QB11" s="29"/>
+      <c r="QC11" s="29"/>
+      <c r="QD11" s="29"/>
+      <c r="QE11" s="29"/>
+      <c r="QF11" s="29"/>
+      <c r="QG11" s="29"/>
+      <c r="QH11" s="29"/>
+      <c r="QI11" s="29"/>
+      <c r="QJ11" s="29"/>
+      <c r="QK11" s="29"/>
+      <c r="QL11" s="29"/>
+      <c r="QM11" s="29"/>
+      <c r="QN11" s="29"/>
+      <c r="QO11" s="29"/>
+      <c r="QP11" s="29"/>
+      <c r="QQ11" s="29"/>
+      <c r="QR11" s="29"/>
+      <c r="QS11" s="29"/>
+      <c r="QT11" s="29"/>
+      <c r="QU11" s="29"/>
+      <c r="QV11" s="29"/>
+      <c r="QW11" s="29"/>
+      <c r="QX11" s="29"/>
+      <c r="QY11" s="29"/>
+      <c r="QZ11" s="29"/>
+      <c r="RA11" s="29"/>
+      <c r="RB11" s="29"/>
+      <c r="RC11" s="29"/>
+      <c r="RD11" s="29"/>
+      <c r="RE11" s="29"/>
+      <c r="RF11" s="29"/>
+      <c r="RG11" s="29"/>
+      <c r="RH11" s="29"/>
+      <c r="RI11" s="29"/>
+      <c r="RJ11" s="29"/>
+      <c r="RK11" s="29"/>
+      <c r="RL11" s="29"/>
+      <c r="RM11" s="29"/>
+      <c r="RN11" s="29"/>
+      <c r="RO11" s="29"/>
+      <c r="RP11" s="29"/>
+      <c r="RQ11" s="29"/>
+      <c r="RR11" s="29"/>
+      <c r="RS11" s="29"/>
+      <c r="RT11" s="29"/>
+      <c r="RU11" s="29"/>
+      <c r="RV11" s="29"/>
+      <c r="RW11" s="29"/>
+      <c r="RX11" s="29"/>
+      <c r="RY11" s="29"/>
+      <c r="RZ11" s="29"/>
+      <c r="SA11" s="29"/>
+      <c r="SB11" s="29"/>
+      <c r="SC11" s="29"/>
+      <c r="SD11" s="29"/>
+      <c r="SE11" s="29"/>
+      <c r="SF11" s="29"/>
+      <c r="SG11" s="29"/>
+      <c r="SH11" s="29"/>
+      <c r="SI11" s="29"/>
+      <c r="SJ11" s="29"/>
+      <c r="SK11" s="29"/>
+      <c r="SL11" s="29"/>
+      <c r="SM11" s="29"/>
+      <c r="SN11" s="29"/>
+      <c r="SO11" s="29"/>
+      <c r="SP11" s="29"/>
+      <c r="SQ11" s="29"/>
+      <c r="SR11" s="29"/>
+      <c r="SS11" s="29"/>
+      <c r="ST11" s="29"/>
+      <c r="SU11" s="29"/>
+      <c r="SV11" s="29"/>
+      <c r="SW11" s="29"/>
+      <c r="SX11" s="29"/>
+      <c r="SY11" s="29"/>
+      <c r="SZ11" s="29"/>
+      <c r="TA11" s="29"/>
+      <c r="TB11" s="29"/>
+      <c r="TC11" s="29"/>
+      <c r="TD11" s="29"/>
+      <c r="TE11" s="29"/>
+      <c r="TF11" s="29"/>
+      <c r="TG11" s="29"/>
+      <c r="TH11" s="29"/>
+      <c r="TI11" s="29"/>
+      <c r="TJ11" s="29"/>
+      <c r="TK11" s="29"/>
+      <c r="TL11" s="29"/>
+      <c r="TM11" s="29"/>
+      <c r="TN11" s="29"/>
+      <c r="TO11" s="29"/>
+      <c r="TP11" s="29"/>
+      <c r="TQ11" s="29"/>
+      <c r="TR11" s="29"/>
+      <c r="TS11" s="29"/>
+      <c r="TT11" s="29"/>
+      <c r="TU11" s="29"/>
+      <c r="TV11" s="29"/>
+      <c r="TW11" s="29"/>
+      <c r="TX11" s="29"/>
+      <c r="TY11" s="29"/>
+      <c r="TZ11" s="29"/>
+      <c r="UA11" s="29"/>
+      <c r="UB11" s="29"/>
+      <c r="UC11" s="29"/>
+      <c r="UD11" s="29"/>
+      <c r="UE11" s="29"/>
+      <c r="UF11" s="29"/>
+      <c r="UG11" s="29"/>
+      <c r="UH11" s="29"/>
+      <c r="UI11" s="29"/>
+      <c r="UJ11" s="29"/>
+      <c r="UK11" s="29"/>
+      <c r="UL11" s="29"/>
+      <c r="UM11" s="29"/>
+      <c r="UN11" s="29"/>
+      <c r="UO11" s="29"/>
+      <c r="UP11" s="29"/>
+      <c r="UQ11" s="29"/>
+      <c r="UR11" s="29"/>
+      <c r="US11" s="29"/>
+      <c r="UT11" s="29"/>
+      <c r="UU11" s="29"/>
+      <c r="UV11" s="29"/>
+      <c r="UW11" s="29"/>
+      <c r="UX11" s="29"/>
+      <c r="UY11" s="29"/>
+      <c r="UZ11" s="29"/>
+      <c r="VA11" s="29"/>
+      <c r="VB11" s="29"/>
+      <c r="VC11" s="29"/>
+      <c r="VD11" s="29"/>
+      <c r="VE11" s="29"/>
+      <c r="VF11" s="29"/>
+      <c r="VG11" s="29"/>
+      <c r="VH11" s="29"/>
+      <c r="VI11" s="29"/>
+      <c r="VJ11" s="29"/>
+      <c r="VK11" s="29"/>
+      <c r="VL11" s="29"/>
+      <c r="VM11" s="29"/>
+      <c r="VN11" s="29"/>
+      <c r="VO11" s="29"/>
+      <c r="VP11" s="29"/>
+      <c r="VQ11" s="29"/>
+      <c r="VR11" s="29"/>
+      <c r="VS11" s="29"/>
+      <c r="VT11" s="29"/>
+      <c r="VU11" s="29"/>
+      <c r="VV11" s="29"/>
+      <c r="VW11" s="29"/>
+      <c r="VX11" s="29"/>
+      <c r="VY11" s="29"/>
+      <c r="VZ11" s="29"/>
+      <c r="WA11" s="29"/>
+      <c r="WB11" s="29"/>
+      <c r="WC11" s="29"/>
+      <c r="WD11" s="29"/>
+      <c r="WE11" s="29"/>
+      <c r="WF11" s="29"/>
+      <c r="WG11" s="29"/>
+      <c r="WH11" s="29"/>
+      <c r="WI11" s="29"/>
+      <c r="WJ11" s="29"/>
+      <c r="WK11" s="29"/>
+      <c r="WL11" s="29"/>
+      <c r="WM11" s="29"/>
+      <c r="WN11" s="29"/>
+      <c r="WO11" s="29"/>
+      <c r="WP11" s="29"/>
+      <c r="WQ11" s="29"/>
+      <c r="WR11" s="29"/>
+      <c r="WS11" s="29"/>
+      <c r="WT11" s="29"/>
+      <c r="WU11" s="29"/>
+      <c r="WV11" s="29"/>
+      <c r="WW11" s="29"/>
+      <c r="WX11" s="29"/>
+      <c r="WY11" s="29"/>
+      <c r="WZ11" s="29"/>
+      <c r="XA11" s="29"/>
+      <c r="XB11" s="29"/>
+      <c r="XC11" s="29"/>
+      <c r="XD11" s="29"/>
+      <c r="XE11" s="29"/>
+      <c r="XF11" s="29"/>
+      <c r="XG11" s="29"/>
+      <c r="XH11" s="29"/>
+      <c r="XI11" s="29"/>
+      <c r="XJ11" s="29"/>
+      <c r="XK11" s="29"/>
+      <c r="XL11" s="29"/>
+      <c r="XM11" s="29"/>
+      <c r="XN11" s="29"/>
+      <c r="XO11" s="29"/>
+      <c r="XP11" s="29"/>
+      <c r="XQ11" s="29"/>
+      <c r="XR11" s="29"/>
+      <c r="XS11" s="29"/>
+      <c r="XT11" s="29"/>
+      <c r="XU11" s="29"/>
+      <c r="XV11" s="29"/>
+      <c r="XW11" s="29"/>
+      <c r="XX11" s="29"/>
+      <c r="XY11" s="29"/>
+      <c r="XZ11" s="29"/>
+      <c r="YA11" s="29"/>
+      <c r="YB11" s="29"/>
+      <c r="YC11" s="29"/>
+      <c r="YD11" s="29"/>
+      <c r="YE11" s="29"/>
+      <c r="YF11" s="29"/>
+      <c r="YG11" s="29"/>
+      <c r="YH11" s="29"/>
+      <c r="YI11" s="29"/>
+      <c r="YJ11" s="29"/>
+      <c r="YK11" s="29"/>
+      <c r="YL11" s="29"/>
+      <c r="YM11" s="29"/>
+      <c r="YN11" s="29"/>
+      <c r="YO11" s="29"/>
+      <c r="YP11" s="29"/>
+      <c r="YQ11" s="29"/>
+      <c r="YR11" s="29"/>
+      <c r="YS11" s="29"/>
+      <c r="YT11" s="29"/>
+      <c r="YU11" s="29"/>
+      <c r="YV11" s="29"/>
+      <c r="YW11" s="29"/>
+      <c r="YX11" s="29"/>
+      <c r="YY11" s="29"/>
+      <c r="YZ11" s="29"/>
+      <c r="ZA11" s="29"/>
+      <c r="ZB11" s="29"/>
+      <c r="ZC11" s="29"/>
+      <c r="ZD11" s="29"/>
+      <c r="ZE11" s="29"/>
+      <c r="ZF11" s="29"/>
+      <c r="ZG11" s="29"/>
+      <c r="ZH11" s="29"/>
+      <c r="ZI11" s="29"/>
+      <c r="ZJ11" s="29"/>
+      <c r="ZK11" s="29"/>
+      <c r="ZL11" s="29"/>
+      <c r="ZM11" s="29"/>
+      <c r="ZN11" s="29"/>
+      <c r="ZO11" s="29"/>
+      <c r="ZP11" s="29"/>
+      <c r="ZQ11" s="29"/>
+      <c r="ZR11" s="29"/>
+      <c r="ZS11" s="29"/>
+      <c r="ZT11" s="29"/>
+      <c r="ZU11" s="29"/>
+      <c r="ZV11" s="29"/>
+      <c r="ZW11" s="29"/>
+      <c r="ZX11" s="29"/>
+      <c r="ZY11" s="29"/>
+      <c r="ZZ11" s="29"/>
+      <c r="AAA11" s="29"/>
+      <c r="AAB11" s="29"/>
+      <c r="AAC11" s="29"/>
+      <c r="AAD11" s="29"/>
+      <c r="AAE11" s="29"/>
+      <c r="AAF11" s="29"/>
+      <c r="AAG11" s="29"/>
+      <c r="AAH11" s="29"/>
+      <c r="AAI11" s="29"/>
+      <c r="AAJ11" s="29"/>
+      <c r="AAK11" s="29"/>
+      <c r="AAL11" s="29"/>
+      <c r="AAM11" s="29"/>
+      <c r="AAN11" s="29"/>
+      <c r="AAO11" s="29"/>
+      <c r="AAP11" s="29"/>
+      <c r="AAQ11" s="29"/>
+      <c r="AAR11" s="29"/>
+      <c r="AAS11" s="29"/>
+      <c r="AAT11" s="29"/>
+      <c r="AAU11" s="29"/>
+      <c r="AAV11" s="29"/>
+      <c r="AAW11" s="29"/>
+      <c r="AAX11" s="29"/>
+      <c r="AAY11" s="29"/>
+      <c r="AAZ11" s="29"/>
+      <c r="ABA11" s="29"/>
+      <c r="ABB11" s="29"/>
+      <c r="ABC11" s="29"/>
+      <c r="ABD11" s="29"/>
+      <c r="ABE11" s="29"/>
+      <c r="ABF11" s="29"/>
+      <c r="ABG11" s="29"/>
+      <c r="ABH11" s="29"/>
+      <c r="ABI11" s="29"/>
+      <c r="ABJ11" s="29"/>
+      <c r="ABK11" s="29"/>
+      <c r="ABL11" s="29"/>
+      <c r="ABM11" s="29"/>
+      <c r="ABN11" s="29"/>
+      <c r="ABO11" s="29"/>
+      <c r="ABP11" s="29"/>
+      <c r="ABQ11" s="29"/>
+      <c r="ABR11" s="29"/>
+      <c r="ABS11" s="29"/>
+      <c r="ABT11" s="29"/>
+      <c r="ABU11" s="29"/>
+      <c r="ABV11" s="29"/>
+      <c r="ABW11" s="29"/>
+      <c r="ABX11" s="29"/>
+      <c r="ABY11" s="29"/>
+      <c r="ABZ11" s="29"/>
+      <c r="ACA11" s="29"/>
+      <c r="ACB11" s="29"/>
+      <c r="ACC11" s="29"/>
+      <c r="ACD11" s="29"/>
+      <c r="ACE11" s="29"/>
+      <c r="ACF11" s="29"/>
+      <c r="ACG11" s="29"/>
+      <c r="ACH11" s="29"/>
+      <c r="ACI11" s="29"/>
+      <c r="ACJ11" s="29"/>
+      <c r="ACK11" s="29"/>
+      <c r="ACL11" s="29"/>
+      <c r="ACM11" s="29"/>
+      <c r="ACN11" s="29"/>
+      <c r="ACO11" s="29"/>
+      <c r="ACP11" s="29"/>
+      <c r="ACQ11" s="29"/>
+      <c r="ACR11" s="29"/>
+      <c r="ACS11" s="29"/>
+      <c r="ACT11" s="29"/>
+      <c r="ACU11" s="29"/>
+      <c r="ACV11" s="29"/>
+      <c r="ACW11" s="29"/>
+      <c r="ACX11" s="29"/>
+      <c r="ACY11" s="29"/>
+      <c r="ACZ11" s="29"/>
+      <c r="ADA11" s="29"/>
+      <c r="ADB11" s="29"/>
+      <c r="ADC11" s="29"/>
+      <c r="ADD11" s="29"/>
+      <c r="ADE11" s="29"/>
+      <c r="ADF11" s="29"/>
+      <c r="ADG11" s="29"/>
+      <c r="ADH11" s="29"/>
+      <c r="ADI11" s="29"/>
+      <c r="ADJ11" s="29"/>
+      <c r="ADK11" s="29"/>
+      <c r="ADL11" s="29"/>
+      <c r="ADM11" s="29"/>
+      <c r="ADN11" s="29"/>
+      <c r="ADO11" s="29"/>
+      <c r="ADP11" s="29"/>
+      <c r="ADQ11" s="29"/>
+      <c r="ADR11" s="29"/>
+      <c r="ADS11" s="29"/>
+      <c r="ADT11" s="29"/>
+      <c r="ADU11" s="29"/>
+      <c r="ADV11" s="29"/>
+      <c r="ADW11" s="29"/>
+      <c r="ADX11" s="29"/>
+      <c r="ADY11" s="29"/>
+      <c r="ADZ11" s="29"/>
+      <c r="AEA11" s="29"/>
+      <c r="AEB11" s="29"/>
+      <c r="AEC11" s="29"/>
+      <c r="AED11" s="29"/>
+      <c r="AEE11" s="29"/>
+      <c r="AEF11" s="29"/>
+      <c r="AEG11" s="29"/>
+      <c r="AEH11" s="29"/>
+      <c r="AEI11" s="29"/>
+      <c r="AEJ11" s="29"/>
+      <c r="AEK11" s="29"/>
+      <c r="AEL11" s="29"/>
+      <c r="AEM11" s="29"/>
+      <c r="AEN11" s="29"/>
+      <c r="AEO11" s="29"/>
+      <c r="AEP11" s="29"/>
+      <c r="AEQ11" s="29"/>
+      <c r="AER11" s="29"/>
+      <c r="AES11" s="29"/>
+      <c r="AET11" s="29"/>
+      <c r="AEU11" s="29"/>
+      <c r="AEV11" s="29"/>
+      <c r="AEW11" s="29"/>
+      <c r="AEX11" s="29"/>
+      <c r="AEY11" s="29"/>
+      <c r="AEZ11" s="29"/>
+      <c r="AFA11" s="29"/>
+      <c r="AFB11" s="29"/>
+      <c r="AFC11" s="29"/>
+      <c r="AFD11" s="29"/>
+      <c r="AFE11" s="29"/>
+      <c r="AFF11" s="29"/>
+      <c r="AFG11" s="29"/>
+      <c r="AFH11" s="29"/>
+      <c r="AFI11" s="29"/>
+      <c r="AFJ11" s="29"/>
+      <c r="AFK11" s="29"/>
+      <c r="AFL11" s="29"/>
+      <c r="AFM11" s="29"/>
+      <c r="AFN11" s="29"/>
+      <c r="AFO11" s="29"/>
+      <c r="AFP11" s="29"/>
+      <c r="AFQ11" s="29"/>
+      <c r="AFR11" s="29"/>
+      <c r="AFS11" s="29"/>
+      <c r="AFT11" s="29"/>
+      <c r="AFU11" s="29"/>
+      <c r="AFV11" s="29"/>
+      <c r="AFW11" s="29"/>
+      <c r="AFX11" s="29"/>
+      <c r="AFY11" s="29"/>
+      <c r="AFZ11" s="29"/>
+      <c r="AGA11" s="29"/>
+      <c r="AGB11" s="29"/>
+      <c r="AGC11" s="29"/>
+      <c r="AGD11" s="29"/>
+      <c r="AGE11" s="29"/>
+      <c r="AGF11" s="29"/>
+      <c r="AGG11" s="29"/>
+      <c r="AGH11" s="29"/>
+      <c r="AGI11" s="29"/>
+      <c r="AGJ11" s="29"/>
+      <c r="AGK11" s="29"/>
+      <c r="AGL11" s="29"/>
+      <c r="AGM11" s="29"/>
+      <c r="AGN11" s="29"/>
+      <c r="AGO11" s="29"/>
+      <c r="AGP11" s="29"/>
+      <c r="AGQ11" s="29"/>
+      <c r="AGR11" s="29"/>
+      <c r="AGS11" s="29"/>
+      <c r="AGT11" s="29"/>
+      <c r="AGU11" s="29"/>
+      <c r="AGV11" s="29"/>
+      <c r="AGW11" s="29"/>
+      <c r="AGX11" s="29"/>
+      <c r="AGY11" s="29"/>
+      <c r="AGZ11" s="29"/>
+      <c r="AHA11" s="29"/>
+      <c r="AHB11" s="29"/>
+      <c r="AHC11" s="29"/>
+      <c r="AHD11" s="29"/>
+      <c r="AHE11" s="29"/>
+      <c r="AHF11" s="29"/>
+      <c r="AHG11" s="29"/>
+      <c r="AHH11" s="29"/>
+      <c r="AHI11" s="29"/>
+      <c r="AHJ11" s="29"/>
+      <c r="AHK11" s="29"/>
+      <c r="AHL11" s="29"/>
+      <c r="AHM11" s="29"/>
+      <c r="AHN11" s="29"/>
+      <c r="AHO11" s="29"/>
+      <c r="AHP11" s="29"/>
+      <c r="AHQ11" s="29"/>
+      <c r="AHR11" s="29"/>
+      <c r="AHS11" s="29"/>
+      <c r="AHT11" s="29"/>
+      <c r="AHU11" s="29"/>
+      <c r="AHV11" s="29"/>
+      <c r="AHW11" s="29"/>
+      <c r="AHX11" s="29"/>
+      <c r="AHY11" s="29"/>
+      <c r="AHZ11" s="29"/>
+      <c r="AIA11" s="29"/>
+      <c r="AIB11" s="29"/>
+      <c r="AIC11" s="29"/>
+      <c r="AID11" s="29"/>
+      <c r="AIE11" s="29"/>
+      <c r="AIF11" s="29"/>
+      <c r="AIG11" s="29"/>
+      <c r="AIH11" s="29"/>
+      <c r="AII11" s="29"/>
+      <c r="AIJ11" s="29"/>
+      <c r="AIK11" s="29"/>
+      <c r="AIL11" s="29"/>
+      <c r="AIM11" s="29"/>
+      <c r="AIN11" s="29"/>
+      <c r="AIO11" s="29"/>
+      <c r="AIP11" s="29"/>
+      <c r="AIQ11" s="29"/>
+      <c r="AIR11" s="29"/>
+      <c r="AIS11" s="29"/>
+      <c r="AIT11" s="29"/>
+      <c r="AIU11" s="29"/>
+      <c r="AIV11" s="29"/>
+      <c r="AIW11" s="29"/>
+      <c r="AIX11" s="29"/>
+      <c r="AIY11" s="29"/>
+      <c r="AIZ11" s="29"/>
+      <c r="AJA11" s="29"/>
+      <c r="AJB11" s="29"/>
+      <c r="AJC11" s="29"/>
+      <c r="AJD11" s="29"/>
+      <c r="AJE11" s="29"/>
+      <c r="AJF11" s="29"/>
+      <c r="AJG11" s="29"/>
+      <c r="AJH11" s="29"/>
+      <c r="AJI11" s="29"/>
+      <c r="AJJ11" s="29"/>
+      <c r="AJK11" s="29"/>
+      <c r="AJL11" s="29"/>
+      <c r="AJM11" s="29"/>
+      <c r="AJN11" s="29"/>
+      <c r="AJO11" s="29"/>
+      <c r="AJP11" s="29"/>
+      <c r="AJQ11" s="29"/>
+      <c r="AJR11" s="29"/>
+      <c r="AJS11" s="29"/>
+      <c r="AJT11" s="29"/>
+      <c r="AJU11" s="29"/>
+      <c r="AJV11" s="29"/>
+      <c r="AJW11" s="29"/>
+      <c r="AJX11" s="29"/>
+      <c r="AJY11" s="29"/>
+      <c r="AJZ11" s="29"/>
+      <c r="AKA11" s="29"/>
+      <c r="AKB11" s="29"/>
+      <c r="AKC11" s="29"/>
+      <c r="AKD11" s="29"/>
+      <c r="AKE11" s="29"/>
+      <c r="AKF11" s="29"/>
+      <c r="AKG11" s="29"/>
+      <c r="AKH11" s="29"/>
+      <c r="AKI11" s="29"/>
+      <c r="AKJ11" s="29"/>
+      <c r="AKK11" s="29"/>
+      <c r="AKL11" s="29"/>
+      <c r="AKM11" s="29"/>
+      <c r="AKN11" s="29"/>
+      <c r="AKO11" s="29"/>
+      <c r="AKP11" s="29"/>
+      <c r="AKQ11" s="29"/>
+      <c r="AKR11" s="29"/>
+      <c r="AKS11" s="29"/>
+      <c r="AKT11" s="29"/>
+      <c r="AKU11" s="29"/>
+      <c r="AKV11" s="29"/>
+      <c r="AKW11" s="29"/>
+      <c r="AKX11" s="29"/>
+      <c r="AKY11" s="29"/>
+      <c r="AKZ11" s="29"/>
+      <c r="ALA11" s="29"/>
+      <c r="ALB11" s="29"/>
+      <c r="ALC11" s="29"/>
+      <c r="ALD11" s="29"/>
+      <c r="ALE11" s="29"/>
+      <c r="ALF11" s="29"/>
+      <c r="ALG11" s="29"/>
+      <c r="ALH11" s="29"/>
+      <c r="ALI11" s="29"/>
+      <c r="ALJ11" s="29"/>
+      <c r="ALK11" s="29"/>
+      <c r="ALL11" s="29"/>
+      <c r="ALM11" s="29"/>
+      <c r="ALN11" s="29"/>
+      <c r="ALO11" s="29"/>
+      <c r="ALP11" s="29"/>
+      <c r="ALQ11" s="29"/>
+      <c r="ALR11" s="29"/>
+      <c r="ALS11" s="29"/>
+      <c r="ALT11" s="29"/>
+      <c r="ALU11" s="29"/>
+      <c r="ALV11" s="29"/>
+      <c r="ALW11" s="29"/>
+      <c r="ALX11" s="29"/>
+      <c r="ALY11" s="29"/>
+      <c r="ALZ11" s="29"/>
+      <c r="AMA11" s="29"/>
+      <c r="AMB11" s="29"/>
+      <c r="AMC11" s="29"/>
+      <c r="AMD11" s="29"/>
+      <c r="AME11" s="29"/>
+      <c r="AMF11" s="29"/>
+      <c r="AMG11" s="29"/>
+      <c r="AMH11" s="29"/>
+      <c r="AMI11" s="29"/>
+      <c r="AMJ11" s="29"/>
+      <c r="AMK11" s="29"/>
+      <c r="AML11" s="29"/>
+      <c r="AMM11" s="29"/>
+      <c r="AMN11" s="29"/>
+      <c r="AMO11" s="29"/>
+      <c r="AMP11" s="29"/>
+      <c r="AMQ11" s="29"/>
+      <c r="AMR11" s="29"/>
+      <c r="AMS11" s="29"/>
+      <c r="AMT11" s="29"/>
+      <c r="AMU11" s="29"/>
+      <c r="AMV11" s="29"/>
+      <c r="AMW11" s="29"/>
+      <c r="AMX11" s="29"/>
+      <c r="AMY11" s="29"/>
+      <c r="AMZ11" s="29"/>
+      <c r="ANA11" s="29"/>
+      <c r="ANB11" s="29"/>
+      <c r="ANC11" s="29"/>
+      <c r="AND11" s="29"/>
+      <c r="ANE11" s="29"/>
+      <c r="ANF11" s="29"/>
+      <c r="ANG11" s="29"/>
+      <c r="ANH11" s="29"/>
+      <c r="ANI11" s="29"/>
+      <c r="ANJ11" s="29"/>
+      <c r="ANK11" s="29"/>
+      <c r="ANL11" s="29"/>
+      <c r="ANM11" s="29"/>
+      <c r="ANN11" s="29"/>
+      <c r="ANO11" s="29"/>
+      <c r="ANP11" s="29"/>
+      <c r="ANQ11" s="29"/>
+      <c r="ANR11" s="29"/>
+      <c r="ANS11" s="29"/>
+      <c r="ANT11" s="29"/>
+      <c r="ANU11" s="29"/>
+      <c r="ANV11" s="29"/>
+      <c r="ANW11" s="29"/>
+      <c r="ANX11" s="29"/>
+      <c r="ANY11" s="29"/>
+      <c r="ANZ11" s="29"/>
+      <c r="AOA11" s="29"/>
+      <c r="AOB11" s="29"/>
+      <c r="AOC11" s="29"/>
+      <c r="AOD11" s="29"/>
+      <c r="AOE11" s="29"/>
+      <c r="AOF11" s="29"/>
+      <c r="AOG11" s="29"/>
+      <c r="AOH11" s="29"/>
+      <c r="AOI11" s="29"/>
+      <c r="AOJ11" s="29"/>
+      <c r="AOK11" s="29"/>
+      <c r="AOL11" s="29"/>
+      <c r="AOM11" s="29"/>
+      <c r="AON11" s="29"/>
+      <c r="AOO11" s="29"/>
+      <c r="AOP11" s="29"/>
+      <c r="AOQ11" s="29"/>
+      <c r="AOR11" s="29"/>
+      <c r="AOS11" s="29"/>
+      <c r="AOT11" s="29"/>
+      <c r="AOU11" s="29"/>
+      <c r="AOV11" s="29"/>
+      <c r="AOW11" s="29"/>
+      <c r="AOX11" s="29"/>
+      <c r="AOY11" s="29"/>
+      <c r="AOZ11" s="29"/>
+      <c r="APA11" s="29"/>
+      <c r="APB11" s="29"/>
+      <c r="APC11" s="29"/>
+      <c r="APD11" s="29"/>
+      <c r="APE11" s="29"/>
+      <c r="APF11" s="29"/>
+      <c r="APG11" s="29"/>
+      <c r="APH11" s="29"/>
+      <c r="API11" s="29"/>
+      <c r="APJ11" s="29"/>
+      <c r="APK11" s="29"/>
+      <c r="APL11" s="29"/>
+      <c r="APM11" s="29"/>
+      <c r="APN11" s="29"/>
+      <c r="APO11" s="29"/>
+      <c r="APP11" s="29"/>
+      <c r="APQ11" s="29"/>
+      <c r="APR11" s="29"/>
+      <c r="APS11" s="29"/>
+      <c r="APT11" s="29"/>
+      <c r="APU11" s="29"/>
+      <c r="APV11" s="29"/>
+      <c r="APW11" s="29"/>
+      <c r="APX11" s="29"/>
+      <c r="APY11" s="29"/>
+      <c r="APZ11" s="29"/>
+      <c r="AQA11" s="29"/>
+      <c r="AQB11" s="29"/>
+      <c r="AQC11" s="29"/>
+      <c r="AQD11" s="29"/>
+      <c r="AQE11" s="29"/>
+      <c r="AQF11" s="29"/>
+      <c r="AQG11" s="29"/>
+      <c r="AQH11" s="29"/>
+      <c r="AQI11" s="29"/>
+      <c r="AQJ11" s="29"/>
+      <c r="AQK11" s="29"/>
+      <c r="AQL11" s="29"/>
+      <c r="AQM11" s="29"/>
+      <c r="AQN11" s="29"/>
+      <c r="AQO11" s="29"/>
+      <c r="AQP11" s="29"/>
+      <c r="AQQ11" s="29"/>
+      <c r="AQR11" s="29"/>
+      <c r="AQS11" s="29"/>
+      <c r="AQT11" s="29"/>
+      <c r="AQU11" s="29"/>
+      <c r="AQV11" s="29"/>
+      <c r="AQW11" s="29"/>
+      <c r="AQX11" s="29"/>
+      <c r="AQY11" s="29"/>
+      <c r="AQZ11" s="29"/>
+      <c r="ARA11" s="29"/>
+      <c r="ARB11" s="29"/>
+      <c r="ARC11" s="29"/>
+      <c r="ARD11" s="29"/>
+      <c r="ARE11" s="29"/>
+      <c r="ARF11" s="29"/>
+      <c r="ARG11" s="29"/>
+      <c r="ARH11" s="29"/>
+      <c r="ARI11" s="29"/>
+      <c r="ARJ11" s="29"/>
+      <c r="ARK11" s="29"/>
+      <c r="ARL11" s="29"/>
+      <c r="ARM11" s="29"/>
+      <c r="ARN11" s="29"/>
+      <c r="ARO11" s="29"/>
+      <c r="ARP11" s="29"/>
+      <c r="ARQ11" s="29"/>
+      <c r="ARR11" s="29"/>
+      <c r="ARS11" s="29"/>
+      <c r="ART11" s="29"/>
+      <c r="ARU11" s="29"/>
+      <c r="ARV11" s="29"/>
+      <c r="ARW11" s="29"/>
+      <c r="ARX11" s="29"/>
+      <c r="ARY11" s="29"/>
+      <c r="ARZ11" s="29"/>
+      <c r="ASA11" s="29"/>
+      <c r="ASB11" s="29"/>
+      <c r="ASC11" s="29"/>
+      <c r="ASD11" s="29"/>
+      <c r="ASE11" s="29"/>
+      <c r="ASF11" s="29"/>
+      <c r="ASG11" s="29"/>
+      <c r="ASH11" s="29"/>
+      <c r="ASI11" s="29"/>
+      <c r="ASJ11" s="29"/>
+      <c r="ASK11" s="29"/>
+      <c r="ASL11" s="29"/>
+      <c r="ASM11" s="29"/>
+      <c r="ASN11" s="29"/>
+      <c r="ASO11" s="29"/>
+      <c r="ASP11" s="29"/>
+      <c r="ASQ11" s="29"/>
+      <c r="ASR11" s="29"/>
+      <c r="ASS11" s="29"/>
+      <c r="AST11" s="29"/>
+      <c r="ASU11" s="29"/>
+      <c r="ASV11" s="29"/>
+      <c r="ASW11" s="29"/>
+      <c r="ASX11" s="29"/>
+      <c r="ASY11" s="29"/>
+      <c r="ASZ11" s="29"/>
+      <c r="ATA11" s="29"/>
+      <c r="ATB11" s="29"/>
+      <c r="ATC11" s="29"/>
+      <c r="ATD11" s="29"/>
+      <c r="ATE11" s="29"/>
+      <c r="ATF11" s="29"/>
+      <c r="ATG11" s="29"/>
+      <c r="ATH11" s="29"/>
+      <c r="ATI11" s="29"/>
+      <c r="ATJ11" s="29"/>
+      <c r="ATK11" s="29"/>
+      <c r="ATL11" s="29"/>
+      <c r="ATM11" s="29"/>
+      <c r="ATN11" s="29"/>
+      <c r="ATO11" s="29"/>
+      <c r="ATP11" s="29"/>
+      <c r="ATQ11" s="29"/>
+      <c r="ATR11" s="29"/>
+      <c r="ATS11" s="29"/>
+      <c r="ATT11" s="29"/>
+      <c r="ATU11" s="29"/>
+      <c r="ATV11" s="29"/>
+      <c r="ATW11" s="29"/>
+      <c r="ATX11" s="29"/>
+      <c r="ATY11" s="29"/>
+      <c r="ATZ11" s="29"/>
+      <c r="AUA11" s="29"/>
+      <c r="AUB11" s="29"/>
+      <c r="AUC11" s="29"/>
+      <c r="AUD11" s="29"/>
+      <c r="AUE11" s="29"/>
+      <c r="AUF11" s="29"/>
+      <c r="AUG11" s="29"/>
+      <c r="AUH11" s="29"/>
+      <c r="AUI11" s="29"/>
+      <c r="AUJ11" s="29"/>
+      <c r="AUK11" s="29"/>
+      <c r="AUL11" s="29"/>
+      <c r="AUM11" s="29"/>
+      <c r="AUN11" s="29"/>
+      <c r="AUO11" s="29"/>
+      <c r="AUP11" s="29"/>
+      <c r="AUQ11" s="29"/>
+      <c r="AUR11" s="29"/>
+      <c r="AUS11" s="29"/>
+      <c r="AUT11" s="29"/>
+      <c r="AUU11" s="29"/>
+      <c r="AUV11" s="29"/>
+      <c r="AUW11" s="29"/>
+      <c r="AUX11" s="29"/>
+      <c r="AUY11" s="29"/>
+      <c r="AUZ11" s="29"/>
+      <c r="AVA11" s="29"/>
+      <c r="AVB11" s="29"/>
+      <c r="AVC11" s="29"/>
+      <c r="AVD11" s="29"/>
+      <c r="AVE11" s="29"/>
+      <c r="AVF11" s="29"/>
+      <c r="AVG11" s="29"/>
+      <c r="AVH11" s="29"/>
+      <c r="AVI11" s="29"/>
+      <c r="AVJ11" s="29"/>
+      <c r="AVK11" s="29"/>
+      <c r="AVL11" s="29"/>
+      <c r="AVM11" s="29"/>
+      <c r="AVN11" s="29"/>
+      <c r="AVO11" s="29"/>
+      <c r="AVP11" s="29"/>
+      <c r="AVQ11" s="29"/>
+      <c r="AVR11" s="29"/>
+      <c r="AVS11" s="29"/>
+      <c r="AVT11" s="29"/>
+      <c r="AVU11" s="29"/>
+      <c r="AVV11" s="29"/>
+      <c r="AVW11" s="29"/>
+      <c r="AVX11" s="29"/>
+      <c r="AVY11" s="29"/>
+      <c r="AVZ11" s="29"/>
+      <c r="AWA11" s="29"/>
+      <c r="AWB11" s="29"/>
+      <c r="AWC11" s="29"/>
+      <c r="AWD11" s="29"/>
+      <c r="AWE11" s="29"/>
+      <c r="AWF11" s="29"/>
+      <c r="AWG11" s="29"/>
+      <c r="AWH11" s="29"/>
+      <c r="AWI11" s="29"/>
+      <c r="AWJ11" s="29"/>
+      <c r="AWK11" s="29"/>
+      <c r="AWL11" s="29"/>
+      <c r="AWM11" s="29"/>
+      <c r="AWN11" s="29"/>
+      <c r="AWO11" s="29"/>
+      <c r="AWP11" s="29"/>
+      <c r="AWQ11" s="29"/>
+      <c r="AWR11" s="29"/>
+      <c r="AWS11" s="29"/>
+      <c r="AWT11" s="29"/>
+      <c r="AWU11" s="29"/>
+      <c r="AWV11" s="29"/>
+      <c r="AWW11" s="29"/>
+      <c r="AWX11" s="29"/>
+      <c r="AWY11" s="29"/>
+      <c r="AWZ11" s="29"/>
+      <c r="AXA11" s="29"/>
+      <c r="AXB11" s="29"/>
+      <c r="AXC11" s="29"/>
+      <c r="AXD11" s="29"/>
+      <c r="AXE11" s="29"/>
+      <c r="AXF11" s="29"/>
+      <c r="AXG11" s="29"/>
+      <c r="AXH11" s="29"/>
+      <c r="AXI11" s="29"/>
+      <c r="AXJ11" s="29"/>
+      <c r="AXK11" s="29"/>
+      <c r="AXL11" s="29"/>
+      <c r="AXM11" s="29"/>
+      <c r="AXN11" s="29"/>
+      <c r="AXO11" s="29"/>
+      <c r="AXP11" s="29"/>
+      <c r="AXQ11" s="29"/>
+      <c r="AXR11" s="29"/>
+      <c r="AXS11" s="29"/>
+      <c r="AXT11" s="29"/>
+      <c r="AXU11" s="29"/>
+      <c r="AXV11" s="29"/>
+      <c r="AXW11" s="29"/>
+      <c r="AXX11" s="29"/>
+      <c r="AXY11" s="29"/>
+      <c r="AXZ11" s="29"/>
+      <c r="AYA11" s="29"/>
+      <c r="AYB11" s="29"/>
+      <c r="AYC11" s="29"/>
+      <c r="AYD11" s="29"/>
+      <c r="AYE11" s="29"/>
+      <c r="AYF11" s="29"/>
+      <c r="AYG11" s="29"/>
+      <c r="AYH11" s="29"/>
+      <c r="AYI11" s="29"/>
+      <c r="AYJ11" s="29"/>
+      <c r="AYK11" s="29"/>
+      <c r="AYL11" s="29"/>
+      <c r="AYM11" s="29"/>
+      <c r="AYN11" s="29"/>
+      <c r="AYO11" s="29"/>
+      <c r="AYP11" s="29"/>
+      <c r="AYQ11" s="29"/>
+      <c r="AYR11" s="29"/>
+      <c r="AYS11" s="29"/>
+      <c r="AYT11" s="29"/>
+      <c r="AYU11" s="29"/>
+      <c r="AYV11" s="29"/>
+      <c r="AYW11" s="29"/>
+      <c r="AYX11" s="29"/>
+      <c r="AYY11" s="29"/>
+      <c r="AYZ11" s="29"/>
+      <c r="AZA11" s="29"/>
+      <c r="AZB11" s="29"/>
+      <c r="AZC11" s="29"/>
+      <c r="AZD11" s="29"/>
+      <c r="AZE11" s="29"/>
+      <c r="AZF11" s="29"/>
+      <c r="AZG11" s="29"/>
+      <c r="AZH11" s="29"/>
+      <c r="AZI11" s="29"/>
+      <c r="AZJ11" s="29"/>
+      <c r="AZK11" s="29"/>
+      <c r="AZL11" s="29"/>
+      <c r="AZM11" s="29"/>
+      <c r="AZN11" s="29"/>
+      <c r="AZO11" s="29"/>
+      <c r="AZP11" s="29"/>
+      <c r="AZQ11" s="29"/>
+      <c r="AZR11" s="29"/>
+      <c r="AZS11" s="29"/>
+      <c r="AZT11" s="29"/>
+      <c r="AZU11" s="29"/>
+      <c r="AZV11" s="29"/>
+      <c r="AZW11" s="29"/>
+      <c r="AZX11" s="29"/>
+      <c r="AZY11" s="29"/>
+      <c r="AZZ11" s="29"/>
+      <c r="BAA11" s="29"/>
+      <c r="BAB11" s="29"/>
+      <c r="BAC11" s="29"/>
+      <c r="BAD11" s="29"/>
+      <c r="BAE11" s="29"/>
+      <c r="BAF11" s="29"/>
+      <c r="BAG11" s="29"/>
+      <c r="BAH11" s="29"/>
+      <c r="BAI11" s="29"/>
+      <c r="BAJ11" s="29"/>
+      <c r="BAK11" s="29"/>
+      <c r="BAL11" s="29"/>
+      <c r="BAM11" s="29"/>
+      <c r="BAN11" s="29"/>
+      <c r="BAO11" s="29"/>
+      <c r="BAP11" s="29"/>
+      <c r="BAQ11" s="29"/>
+      <c r="BAR11" s="29"/>
+      <c r="BAS11" s="29"/>
+      <c r="BAT11" s="29"/>
+      <c r="BAU11" s="29"/>
+      <c r="BAV11" s="29"/>
+      <c r="BAW11" s="29"/>
+      <c r="BAX11" s="29"/>
+      <c r="BAY11" s="29"/>
+      <c r="BAZ11" s="29"/>
+      <c r="BBA11" s="29"/>
+      <c r="BBB11" s="29"/>
+      <c r="BBC11" s="29"/>
+      <c r="BBD11" s="29"/>
+      <c r="BBE11" s="29"/>
+      <c r="BBF11" s="29"/>
+      <c r="BBG11" s="29"/>
+      <c r="BBH11" s="29"/>
+      <c r="BBI11" s="29"/>
+      <c r="BBJ11" s="29"/>
+      <c r="BBK11" s="29"/>
+      <c r="BBL11" s="29"/>
+      <c r="BBM11" s="29"/>
+      <c r="BBN11" s="29"/>
+      <c r="BBO11" s="29"/>
+      <c r="BBP11" s="29"/>
+      <c r="BBQ11" s="29"/>
+      <c r="BBR11" s="29"/>
+      <c r="BBS11" s="29"/>
+      <c r="BBT11" s="29"/>
+      <c r="BBU11" s="29"/>
+      <c r="BBV11" s="29"/>
+      <c r="BBW11" s="29"/>
+      <c r="BBX11" s="29"/>
+      <c r="BBY11" s="29"/>
+      <c r="BBZ11" s="29"/>
+      <c r="BCA11" s="29"/>
+      <c r="BCB11" s="29"/>
+      <c r="BCC11" s="29"/>
+      <c r="BCD11" s="29"/>
+      <c r="BCE11" s="29"/>
+      <c r="BCF11" s="29"/>
+      <c r="BCG11" s="29"/>
+      <c r="BCH11" s="29"/>
+      <c r="BCI11" s="29"/>
+      <c r="BCJ11" s="29"/>
+      <c r="BCK11" s="29"/>
+      <c r="BCL11" s="29"/>
+      <c r="BCM11" s="29"/>
+      <c r="BCN11" s="29"/>
+      <c r="BCO11" s="29"/>
+      <c r="BCP11" s="29"/>
+      <c r="BCQ11" s="29"/>
+      <c r="BCR11" s="29"/>
+      <c r="BCS11" s="29"/>
+      <c r="BCT11" s="29"/>
+      <c r="BCU11" s="29"/>
+      <c r="BCV11" s="29"/>
+      <c r="BCW11" s="29"/>
+      <c r="BCX11" s="29"/>
+      <c r="BCY11" s="29"/>
+      <c r="BCZ11" s="29"/>
+      <c r="BDA11" s="29"/>
+      <c r="BDB11" s="29"/>
+      <c r="BDC11" s="29"/>
+      <c r="BDD11" s="29"/>
+      <c r="BDE11" s="29"/>
+      <c r="BDF11" s="29"/>
+      <c r="BDG11" s="29"/>
+      <c r="BDH11" s="29"/>
+      <c r="BDI11" s="29"/>
+      <c r="BDJ11" s="29"/>
+      <c r="BDK11" s="29"/>
+      <c r="BDL11" s="29"/>
+      <c r="BDM11" s="29"/>
+      <c r="BDN11" s="29"/>
+      <c r="BDO11" s="29"/>
+      <c r="BDP11" s="29"/>
+      <c r="BDQ11" s="29"/>
+      <c r="BDR11" s="29"/>
+      <c r="BDS11" s="29"/>
+      <c r="BDT11" s="29"/>
+      <c r="BDU11" s="29"/>
+      <c r="BDV11" s="29"/>
+      <c r="BDW11" s="29"/>
+      <c r="BDX11" s="29"/>
+      <c r="BDY11" s="29"/>
+      <c r="BDZ11" s="29"/>
+      <c r="BEA11" s="29"/>
+      <c r="BEB11" s="29"/>
+      <c r="BEC11" s="29"/>
+      <c r="BED11" s="29"/>
+      <c r="BEE11" s="29"/>
+      <c r="BEF11" s="29"/>
+      <c r="BEG11" s="29"/>
+      <c r="BEH11" s="29"/>
+      <c r="BEI11" s="29"/>
+      <c r="BEJ11" s="29"/>
+      <c r="BEK11" s="29"/>
+      <c r="BEL11" s="29"/>
+      <c r="BEM11" s="29"/>
+      <c r="BEN11" s="29"/>
+      <c r="BEO11" s="29"/>
+      <c r="BEP11" s="29"/>
+      <c r="BEQ11" s="29"/>
+      <c r="BER11" s="29"/>
+      <c r="BES11" s="29"/>
+      <c r="BET11" s="29"/>
+      <c r="BEU11" s="29"/>
+      <c r="BEV11" s="29"/>
+      <c r="BEW11" s="29"/>
+      <c r="BEX11" s="29"/>
+      <c r="BEY11" s="29"/>
+      <c r="BEZ11" s="29"/>
+      <c r="BFA11" s="29"/>
+      <c r="BFB11" s="29"/>
+      <c r="BFC11" s="29"/>
+      <c r="BFD11" s="29"/>
+      <c r="BFE11" s="29"/>
+      <c r="BFF11" s="29"/>
+      <c r="BFG11" s="29"/>
+      <c r="BFH11" s="29"/>
+      <c r="BFI11" s="29"/>
+      <c r="BFJ11" s="29"/>
+      <c r="BFK11" s="29"/>
+      <c r="BFL11" s="29"/>
+      <c r="BFM11" s="29"/>
+      <c r="BFN11" s="29"/>
+      <c r="BFO11" s="29"/>
+      <c r="BFP11" s="29"/>
+      <c r="BFQ11" s="29"/>
+      <c r="BFR11" s="29"/>
+      <c r="BFS11" s="29"/>
+      <c r="BFT11" s="29"/>
+      <c r="BFU11" s="29"/>
+      <c r="BFV11" s="29"/>
+      <c r="BFW11" s="29"/>
+      <c r="BFX11" s="29"/>
+      <c r="BFY11" s="29"/>
+      <c r="BFZ11" s="29"/>
+      <c r="BGA11" s="29"/>
+      <c r="BGB11" s="29"/>
+      <c r="BGC11" s="29"/>
+      <c r="BGD11" s="29"/>
+      <c r="BGE11" s="29"/>
+      <c r="BGF11" s="29"/>
+      <c r="BGG11" s="29"/>
+      <c r="BGH11" s="29"/>
+      <c r="BGI11" s="29"/>
+      <c r="BGJ11" s="29"/>
+      <c r="BGK11" s="29"/>
+      <c r="BGL11" s="29"/>
+      <c r="BGM11" s="29"/>
+      <c r="BGN11" s="29"/>
+      <c r="BGO11" s="29"/>
+      <c r="BGP11" s="29"/>
+      <c r="BGQ11" s="29"/>
+      <c r="BGR11" s="29"/>
+      <c r="BGS11" s="29"/>
+      <c r="BGT11" s="29"/>
+      <c r="BGU11" s="29"/>
+      <c r="BGV11" s="29"/>
+      <c r="BGW11" s="29"/>
+      <c r="BGX11" s="29"/>
+      <c r="BGY11" s="29"/>
+      <c r="BGZ11" s="29"/>
+      <c r="BHA11" s="29"/>
+      <c r="BHB11" s="29"/>
+      <c r="BHC11" s="29"/>
+      <c r="BHD11" s="29"/>
+      <c r="BHE11" s="29"/>
+      <c r="BHF11" s="29"/>
+      <c r="BHG11" s="29"/>
+      <c r="BHH11" s="29"/>
+      <c r="BHI11" s="29"/>
+      <c r="BHJ11" s="29"/>
+      <c r="BHK11" s="29"/>
+      <c r="BHL11" s="29"/>
+      <c r="BHM11" s="29"/>
+      <c r="BHN11" s="29"/>
+      <c r="BHO11" s="29"/>
+      <c r="BHP11" s="29"/>
+      <c r="BHQ11" s="29"/>
+      <c r="BHR11" s="29"/>
+      <c r="BHS11" s="29"/>
+      <c r="BHT11" s="29"/>
+      <c r="BHU11" s="29"/>
+      <c r="BHV11" s="29"/>
+      <c r="BHW11" s="29"/>
+      <c r="BHX11" s="29"/>
+      <c r="BHY11" s="29"/>
+      <c r="BHZ11" s="29"/>
+      <c r="BIA11" s="29"/>
+      <c r="BIB11" s="29"/>
+      <c r="BIC11" s="29"/>
+      <c r="BID11" s="29"/>
+      <c r="BIE11" s="29"/>
+      <c r="BIF11" s="29"/>
+      <c r="BIG11" s="29"/>
+      <c r="BIH11" s="29"/>
+      <c r="BII11" s="29"/>
+      <c r="BIJ11" s="29"/>
+      <c r="BIK11" s="29"/>
+      <c r="BIL11" s="29"/>
+      <c r="BIM11" s="29"/>
+      <c r="BIN11" s="29"/>
+      <c r="BIO11" s="29"/>
+      <c r="BIP11" s="29"/>
+      <c r="BIQ11" s="29"/>
+      <c r="BIR11" s="29"/>
+      <c r="BIS11" s="29"/>
+      <c r="BIT11" s="29"/>
+      <c r="BIU11" s="29"/>
+      <c r="BIV11" s="29"/>
+      <c r="BIW11" s="29"/>
+      <c r="BIX11" s="29"/>
+      <c r="BIY11" s="29"/>
+      <c r="BIZ11" s="29"/>
+      <c r="BJA11" s="29"/>
+      <c r="BJB11" s="29"/>
+      <c r="BJC11" s="29"/>
+      <c r="BJD11" s="29"/>
+      <c r="BJE11" s="29"/>
+      <c r="BJF11" s="29"/>
+      <c r="BJG11" s="29"/>
+      <c r="BJH11" s="29"/>
+      <c r="BJI11" s="29"/>
+      <c r="BJJ11" s="29"/>
+      <c r="BJK11" s="29"/>
+      <c r="BJL11" s="29"/>
+      <c r="BJM11" s="29"/>
+      <c r="BJN11" s="29"/>
+      <c r="BJO11" s="29"/>
+      <c r="BJP11" s="29"/>
+      <c r="BJQ11" s="29"/>
+      <c r="BJR11" s="29"/>
+      <c r="BJS11" s="29"/>
+      <c r="BJT11" s="29"/>
+      <c r="BJU11" s="29"/>
+      <c r="BJV11" s="29"/>
+      <c r="BJW11" s="29"/>
+      <c r="BJX11" s="29"/>
+      <c r="BJY11" s="29"/>
+      <c r="BJZ11" s="29"/>
+      <c r="BKA11" s="29"/>
+      <c r="BKB11" s="29"/>
+      <c r="BKC11" s="29"/>
+      <c r="BKD11" s="29"/>
+      <c r="BKE11" s="29"/>
+      <c r="BKF11" s="29"/>
+      <c r="BKG11" s="29"/>
+      <c r="BKH11" s="29"/>
+      <c r="BKI11" s="29"/>
+      <c r="BKJ11" s="29"/>
+      <c r="BKK11" s="29"/>
+      <c r="BKL11" s="29"/>
+      <c r="BKM11" s="29"/>
+      <c r="BKN11" s="29"/>
+      <c r="BKO11" s="29"/>
+      <c r="BKP11" s="29"/>
+      <c r="BKQ11" s="29"/>
+      <c r="BKR11" s="29"/>
+      <c r="BKS11" s="29"/>
+      <c r="BKT11" s="29"/>
+      <c r="BKU11" s="29"/>
+      <c r="BKV11" s="29"/>
+      <c r="BKW11" s="29"/>
+      <c r="BKX11" s="29"/>
+      <c r="BKY11" s="29"/>
+      <c r="BKZ11" s="29"/>
+      <c r="BLA11" s="29"/>
+      <c r="BLB11" s="29"/>
+      <c r="BLC11" s="29"/>
+      <c r="BLD11" s="29"/>
+      <c r="BLE11" s="29"/>
+      <c r="BLF11" s="29"/>
+      <c r="BLG11" s="29"/>
+      <c r="BLH11" s="29"/>
+      <c r="BLI11" s="29"/>
+      <c r="BLJ11" s="29"/>
+      <c r="BLK11" s="29"/>
+      <c r="BLL11" s="29"/>
+      <c r="BLM11" s="29"/>
+      <c r="BLN11" s="29"/>
+      <c r="BLO11" s="29"/>
+      <c r="BLP11" s="29"/>
+      <c r="BLQ11" s="29"/>
+      <c r="BLR11" s="29"/>
+      <c r="BLS11" s="29"/>
+      <c r="BLT11" s="29"/>
+      <c r="BLU11" s="29"/>
+      <c r="BLV11" s="29"/>
+      <c r="BLW11" s="29"/>
+      <c r="BLX11" s="29"/>
+      <c r="BLY11" s="29"/>
+      <c r="BLZ11" s="29"/>
+      <c r="BMA11" s="29"/>
+      <c r="BMB11" s="29"/>
+      <c r="BMC11" s="29"/>
+      <c r="BMD11" s="29"/>
+      <c r="BME11" s="29"/>
+      <c r="BMF11" s="29"/>
+      <c r="BMG11" s="29"/>
+      <c r="BMH11" s="29"/>
+      <c r="BMI11" s="29"/>
+      <c r="BMJ11" s="29"/>
+      <c r="BMK11" s="29"/>
+      <c r="BML11" s="29"/>
+      <c r="BMM11" s="29"/>
+      <c r="BMN11" s="29"/>
+      <c r="BMO11" s="29"/>
+      <c r="BMP11" s="29"/>
+      <c r="BMQ11" s="29"/>
+      <c r="BMR11" s="29"/>
+      <c r="BMS11" s="29"/>
+      <c r="BMT11" s="29"/>
+      <c r="BMU11" s="29"/>
+      <c r="BMV11" s="29"/>
+      <c r="BMW11" s="29"/>
+      <c r="BMX11" s="29"/>
+      <c r="BMY11" s="29"/>
+      <c r="BMZ11" s="29"/>
+      <c r="BNA11" s="29"/>
+      <c r="BNB11" s="29"/>
+      <c r="BNC11" s="29"/>
+      <c r="BND11" s="29"/>
+      <c r="BNE11" s="29"/>
+      <c r="BNF11" s="29"/>
+      <c r="BNG11" s="29"/>
+      <c r="BNH11" s="29"/>
+      <c r="BNI11" s="29"/>
+      <c r="BNJ11" s="29"/>
+      <c r="BNK11" s="29"/>
+      <c r="BNL11" s="29"/>
+      <c r="BNM11" s="29"/>
+      <c r="BNN11" s="29"/>
+      <c r="BNO11" s="29"/>
+      <c r="BNP11" s="29"/>
+      <c r="BNQ11" s="29"/>
+      <c r="BNR11" s="29"/>
+      <c r="BNS11" s="29"/>
+      <c r="BNT11" s="29"/>
+      <c r="BNU11" s="29"/>
+      <c r="BNV11" s="29"/>
+      <c r="BNW11" s="29"/>
+      <c r="BNX11" s="29"/>
+      <c r="BNY11" s="29"/>
+      <c r="BNZ11" s="29"/>
+      <c r="BOA11" s="29"/>
+      <c r="BOB11" s="29"/>
+      <c r="BOC11" s="29"/>
+      <c r="BOD11" s="29"/>
+      <c r="BOE11" s="29"/>
+      <c r="BOF11" s="29"/>
+      <c r="BOG11" s="29"/>
+      <c r="BOH11" s="29"/>
+      <c r="BOI11" s="29"/>
+      <c r="BOJ11" s="29"/>
+      <c r="BOK11" s="29"/>
+      <c r="BOL11" s="29"/>
+      <c r="BOM11" s="29"/>
+      <c r="BON11" s="29"/>
+      <c r="BOO11" s="29"/>
+      <c r="BOP11" s="29"/>
+      <c r="BOQ11" s="29"/>
+      <c r="BOR11" s="29"/>
+      <c r="BOS11" s="29"/>
+      <c r="BOT11" s="29"/>
+      <c r="BOU11" s="29"/>
+      <c r="BOV11" s="29"/>
+      <c r="BOW11" s="29"/>
+      <c r="BOX11" s="29"/>
+      <c r="BOY11" s="29"/>
+      <c r="BOZ11" s="29"/>
+      <c r="BPA11" s="29"/>
+      <c r="BPB11" s="29"/>
+      <c r="BPC11" s="29"/>
+      <c r="BPD11" s="29"/>
+      <c r="BPE11" s="29"/>
+      <c r="BPF11" s="29"/>
+      <c r="BPG11" s="29"/>
+      <c r="BPH11" s="29"/>
+      <c r="BPI11" s="29"/>
+      <c r="BPJ11" s="29"/>
+      <c r="BPK11" s="29"/>
+      <c r="BPL11" s="29"/>
+      <c r="BPM11" s="29"/>
+      <c r="BPN11" s="29"/>
+      <c r="BPO11" s="29"/>
+      <c r="BPP11" s="29"/>
+      <c r="BPQ11" s="29"/>
+      <c r="BPR11" s="29"/>
+      <c r="BPS11" s="29"/>
+      <c r="BPT11" s="29"/>
+      <c r="BPU11" s="29"/>
+      <c r="BPV11" s="29"/>
+      <c r="BPW11" s="29"/>
+      <c r="BPX11" s="29"/>
+      <c r="BPY11" s="29"/>
+      <c r="BPZ11" s="29"/>
+      <c r="BQA11" s="29"/>
+      <c r="BQB11" s="29"/>
+      <c r="BQC11" s="29"/>
+      <c r="BQD11" s="29"/>
+      <c r="BQE11" s="29"/>
+      <c r="BQF11" s="29"/>
+      <c r="BQG11" s="29"/>
+      <c r="BQH11" s="29"/>
+      <c r="BQI11" s="29"/>
+      <c r="BQJ11" s="29"/>
+      <c r="BQK11" s="29"/>
+      <c r="BQL11" s="29"/>
+      <c r="BQM11" s="29"/>
+      <c r="BQN11" s="29"/>
+      <c r="BQO11" s="29"/>
+      <c r="BQP11" s="29"/>
+      <c r="BQQ11" s="29"/>
+      <c r="BQR11" s="29"/>
+      <c r="BQS11" s="29"/>
+      <c r="BQT11" s="29"/>
+      <c r="BQU11" s="29"/>
+      <c r="BQV11" s="29"/>
+      <c r="BQW11" s="29"/>
+      <c r="BQX11" s="29"/>
+      <c r="BQY11" s="29"/>
+      <c r="BQZ11" s="29"/>
+      <c r="BRA11" s="29"/>
+      <c r="BRB11" s="29"/>
+      <c r="BRC11" s="29"/>
+      <c r="BRD11" s="29"/>
+      <c r="BRE11" s="29"/>
+      <c r="BRF11" s="29"/>
+      <c r="BRG11" s="29"/>
+      <c r="BRH11" s="29"/>
+      <c r="BRI11" s="29"/>
+      <c r="BRJ11" s="29"/>
+      <c r="BRK11" s="29"/>
+      <c r="BRL11" s="29"/>
+      <c r="BRM11" s="29"/>
+      <c r="BRN11" s="29"/>
+      <c r="BRO11" s="29"/>
+      <c r="BRP11" s="29"/>
+      <c r="BRQ11" s="29"/>
+      <c r="BRR11" s="29"/>
+      <c r="BRS11" s="29"/>
+      <c r="BRT11" s="29"/>
+      <c r="BRU11" s="29"/>
+      <c r="BRV11" s="29"/>
+      <c r="BRW11" s="29"/>
+      <c r="BRX11" s="29"/>
+      <c r="BRY11" s="29"/>
+      <c r="BRZ11" s="29"/>
+      <c r="BSA11" s="29"/>
+      <c r="BSB11" s="29"/>
+      <c r="BSC11" s="29"/>
+      <c r="BSD11" s="29"/>
+      <c r="BSE11" s="29"/>
+      <c r="BSF11" s="29"/>
+      <c r="BSG11" s="29"/>
+      <c r="BSH11" s="29"/>
+      <c r="BSI11" s="29"/>
+      <c r="BSJ11" s="29"/>
+      <c r="BSK11" s="29"/>
+      <c r="BSL11" s="29"/>
+      <c r="BSM11" s="29"/>
+      <c r="BSN11" s="29"/>
+      <c r="BSO11" s="29"/>
+      <c r="BSP11" s="29"/>
+      <c r="BSQ11" s="29"/>
+      <c r="BSR11" s="29"/>
+      <c r="BSS11" s="29"/>
+      <c r="BST11" s="29"/>
+      <c r="BSU11" s="29"/>
+      <c r="BSV11" s="29"/>
+      <c r="BSW11" s="29"/>
+      <c r="BSX11" s="29"/>
+      <c r="BSY11" s="29"/>
+      <c r="BSZ11" s="29"/>
+      <c r="BTA11" s="29"/>
+      <c r="BTB11" s="29"/>
+      <c r="BTC11" s="29"/>
+      <c r="BTD11" s="29"/>
+      <c r="BTE11" s="29"/>
+      <c r="BTF11" s="29"/>
+      <c r="BTG11" s="29"/>
+      <c r="BTH11" s="29"/>
+      <c r="BTI11" s="29"/>
+      <c r="BTJ11" s="29"/>
+      <c r="BTK11" s="29"/>
+      <c r="BTL11" s="29"/>
+      <c r="BTM11" s="29"/>
+      <c r="BTN11" s="29"/>
+      <c r="BTO11" s="29"/>
+      <c r="BTP11" s="29"/>
+      <c r="BTQ11" s="29"/>
+      <c r="BTR11" s="29"/>
+      <c r="BTS11" s="29"/>
+      <c r="BTT11" s="29"/>
+      <c r="BTU11" s="29"/>
+      <c r="BTV11" s="29"/>
+      <c r="BTW11" s="29"/>
+      <c r="BTX11" s="29"/>
+      <c r="BTY11" s="29"/>
+      <c r="BTZ11" s="29"/>
+      <c r="BUA11" s="29"/>
+      <c r="BUB11" s="29"/>
+      <c r="BUC11" s="29"/>
+      <c r="BUD11" s="29"/>
+      <c r="BUE11" s="29"/>
+      <c r="BUF11" s="29"/>
+      <c r="BUG11" s="29"/>
+      <c r="BUH11" s="29"/>
+      <c r="BUI11" s="29"/>
+      <c r="BUJ11" s="29"/>
+      <c r="BUK11" s="29"/>
+      <c r="BUL11" s="29"/>
+      <c r="BUM11" s="29"/>
+      <c r="BUN11" s="29"/>
+      <c r="BUO11" s="29"/>
+      <c r="BUP11" s="29"/>
+      <c r="BUQ11" s="29"/>
+      <c r="BUR11" s="29"/>
+      <c r="BUS11" s="29"/>
+      <c r="BUT11" s="29"/>
+      <c r="BUU11" s="29"/>
+      <c r="BUV11" s="29"/>
+      <c r="BUW11" s="29"/>
+      <c r="BUX11" s="29"/>
+      <c r="BUY11" s="29"/>
+      <c r="BUZ11" s="29"/>
+      <c r="BVA11" s="29"/>
+      <c r="BVB11" s="29"/>
+      <c r="BVC11" s="29"/>
+      <c r="BVD11" s="29"/>
+      <c r="BVE11" s="29"/>
     </row>
     <row r="12" spans="1:2322" x14ac:dyDescent="0.2">
       <c r="A12" s="3"/>
@@ -8370,17 +8366,17 @@
       <c r="G12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="31" t="s">
+      <c r="H12" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="32" t="s">
+      <c r="I12" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="42"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="37"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -8415,24 +8411,24 @@
       <c r="D13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="42">
         <v>46096</v>
       </c>
-      <c r="F13" s="49">
+      <c r="F13" s="42">
         <v>46103</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="31" t="s">
+      <c r="H13" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
-      <c r="L13" s="73"/>
+      <c r="L13" s="55"/>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
@@ -8478,15 +8474,15 @@
       <c r="G14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="31" t="s">
+      <c r="H14" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="25" t="s">
+      <c r="I14" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="72"/>
+      <c r="L14" s="54"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
@@ -8517,10 +8513,10 @@
       <c r="B15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="43" t="s">
         <v>39</v>
       </c>
       <c r="E15" s="5">
@@ -8532,15 +8528,15 @@
       <c r="G15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="31" t="s">
+      <c r="H15" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="28" t="s">
+      <c r="I15" s="24" t="s">
         <v>49</v>
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
-      <c r="L15" s="73"/>
+      <c r="L15" s="55"/>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -8574,7 +8570,7 @@
       <c r="C16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E16" s="8">
@@ -8586,16 +8582,16 @@
       <c r="G16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="24" t="s">
         <v>49</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-      <c r="M16" s="72"/>
+      <c r="M16" s="54"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -8625,7 +8621,7 @@
       <c r="B17" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="43" t="s">
         <v>57</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -8640,16 +8636,16 @@
       <c r="G17" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="31" t="s">
+      <c r="H17" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="28" t="s">
+      <c r="I17" s="24" t="s">
         <v>49</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="73"/>
+      <c r="M17" s="55"/>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
@@ -8694,17 +8690,17 @@
       <c r="G18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="31" t="s">
+      <c r="H18" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I18" s="37" t="s">
+      <c r="I18" s="32" t="s">
         <v>49</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
-      <c r="N18" s="72"/>
+      <c r="N18" s="54"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
@@ -8729,44 +8725,44 @@
       <c r="AJ18" s="3"/>
     </row>
     <row r="19" spans="1:36" s="6" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="47"/>
-      <c r="R19" s="47"/>
-      <c r="S19" s="47"/>
-      <c r="T19" s="47"/>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
-      <c r="W19" s="47"/>
-      <c r="X19" s="47"/>
-      <c r="Y19" s="47"/>
-      <c r="Z19" s="47"/>
-      <c r="AA19" s="47"/>
-      <c r="AB19" s="47"/>
-      <c r="AC19" s="47"/>
-      <c r="AD19" s="47"/>
-      <c r="AE19" s="47"/>
-      <c r="AF19" s="47"/>
-      <c r="AG19" s="47"/>
-      <c r="AH19" s="47"/>
-      <c r="AI19" s="47"/>
-      <c r="AJ19" s="47"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="77"/>
+      <c r="K19" s="77"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="77"/>
+      <c r="N19" s="77"/>
+      <c r="O19" s="77"/>
+      <c r="P19" s="77"/>
+      <c r="Q19" s="77"/>
+      <c r="R19" s="77"/>
+      <c r="S19" s="77"/>
+      <c r="T19" s="77"/>
+      <c r="U19" s="77"/>
+      <c r="V19" s="77"/>
+      <c r="W19" s="77"/>
+      <c r="X19" s="77"/>
+      <c r="Y19" s="77"/>
+      <c r="Z19" s="77"/>
+      <c r="AA19" s="77"/>
+      <c r="AB19" s="77"/>
+      <c r="AC19" s="77"/>
+      <c r="AD19" s="77"/>
+      <c r="AE19" s="77"/>
+      <c r="AF19" s="77"/>
+      <c r="AG19" s="77"/>
+      <c r="AH19" s="77"/>
+      <c r="AI19" s="77"/>
+      <c r="AJ19" s="77"/>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
@@ -8788,16 +8784,16 @@
       <c r="G20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H20" s="31" t="s">
+      <c r="H20" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I20" s="32" t="s">
+      <c r="I20" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
-      <c r="M20" s="72"/>
+      <c r="M20" s="54"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -8842,16 +8838,16 @@
       <c r="G21" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H21" s="31" t="s">
+      <c r="H21" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I21" s="32" t="s">
+      <c r="I21" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
-      <c r="M21" s="73"/>
+      <c r="M21" s="55"/>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
@@ -8878,7 +8874,7 @@
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="41" t="s">
         <v>67</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -8896,17 +8892,17 @@
       <c r="G22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="31" t="s">
+      <c r="H22" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I22" s="32" t="s">
+      <c r="I22" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
-      <c r="N22" s="72"/>
+      <c r="N22" s="54"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
@@ -8950,17 +8946,17 @@
       <c r="G23" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H23" s="31" t="s">
+      <c r="H23" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I23" s="32" t="s">
+      <c r="I23" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
       <c r="M23" s="7"/>
-      <c r="N23" s="73"/>
+      <c r="N23" s="55"/>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
       <c r="Q23" s="4"/>
@@ -9004,17 +9000,17 @@
       <c r="G24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H24" s="31" t="s">
+      <c r="H24" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I24" s="32" t="s">
+      <c r="I24" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
-      <c r="N24" s="72"/>
+      <c r="N24" s="54"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
@@ -9058,10 +9054,10 @@
       <c r="G25" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H25" s="31" t="s">
+      <c r="H25" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I25" s="32" t="s">
+      <c r="I25" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J25" s="7"/>
@@ -9069,7 +9065,7 @@
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
-      <c r="O25" s="73"/>
+      <c r="O25" s="55"/>
       <c r="P25" s="7"/>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
@@ -9095,7 +9091,7 @@
     <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>62</v>
@@ -9112,10 +9108,10 @@
       <c r="G26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H26" s="31" t="s">
+      <c r="H26" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I26" s="32" t="s">
+      <c r="I26" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J26" s="3"/>
@@ -9124,7 +9120,7 @@
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
-      <c r="P26" s="74"/>
+      <c r="P26" s="56"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
@@ -9166,10 +9162,10 @@
       <c r="G27" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H27" s="31" t="s">
+      <c r="H27" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I27" s="28" t="s">
+      <c r="I27" s="24" t="s">
         <v>49</v>
       </c>
       <c r="J27" s="7"/>
@@ -9178,7 +9174,7 @@
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
-      <c r="P27" s="73"/>
+      <c r="P27" s="55"/>
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
       <c r="S27" s="4"/>
@@ -9220,10 +9216,10 @@
       <c r="G28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H28" s="31" t="s">
+      <c r="H28" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I28" s="32" t="s">
+      <c r="I28" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J28" s="3"/>
@@ -9232,7 +9228,7 @@
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
-      <c r="P28" s="74"/>
+      <c r="P28" s="56"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
@@ -9274,10 +9270,10 @@
       <c r="G29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H29" s="31" t="s">
+      <c r="H29" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I29" s="28" t="s">
+      <c r="I29" s="24" t="s">
         <v>49</v>
       </c>
       <c r="J29" s="7"/>
@@ -9286,7 +9282,7 @@
       <c r="M29" s="7"/>
       <c r="N29" s="7"/>
       <c r="O29" s="7"/>
-      <c r="P29" s="73"/>
+      <c r="P29" s="55"/>
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
       <c r="S29" s="4"/>
@@ -9328,18 +9324,18 @@
       <c r="G30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H30" s="31" t="s">
+      <c r="H30" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I30" s="32" t="s">
+      <c r="I30" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
-      <c r="N30" s="74"/>
-      <c r="O30" s="74"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="56"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
@@ -9365,7 +9361,7 @@
     <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>62</v>
@@ -9382,10 +9378,10 @@
       <c r="G31" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H31" s="31" t="s">
+      <c r="H31" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I31" s="32" t="s">
+      <c r="I31" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J31" s="7"/>
@@ -9395,7 +9391,7 @@
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
-      <c r="Q31" s="73"/>
+      <c r="Q31" s="55"/>
       <c r="R31" s="4"/>
       <c r="S31" s="4"/>
       <c r="T31" s="4"/>
@@ -9436,10 +9432,10 @@
       <c r="G32" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H32" s="31" t="s">
+      <c r="H32" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I32" s="32" t="s">
+      <c r="I32" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J32" s="3"/>
@@ -9449,7 +9445,7 @@
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
-      <c r="Q32" s="74"/>
+      <c r="Q32" s="56"/>
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
@@ -9490,10 +9486,10 @@
       <c r="G33" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H33" s="31" t="s">
+      <c r="H33" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I33" s="32" t="s">
+      <c r="I33" s="28" t="s">
         <v>42</v>
       </c>
       <c r="J33" s="7"/>
@@ -9503,7 +9499,7 @@
       <c r="N33" s="7"/>
       <c r="O33" s="7"/>
       <c r="P33" s="7"/>
-      <c r="Q33" s="73"/>
+      <c r="Q33" s="55"/>
       <c r="R33" s="4"/>
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
@@ -9544,10 +9540,10 @@
       <c r="G34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H34" s="31" t="s">
+      <c r="H34" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I34" s="28" t="s">
+      <c r="I34" s="24" t="s">
         <v>49</v>
       </c>
       <c r="J34" s="3"/>
@@ -9558,7 +9554,7 @@
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
-      <c r="R34" s="74"/>
+      <c r="R34" s="56"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
@@ -9578,407 +9574,407 @@
       <c r="AI34" s="3"/>
       <c r="AJ34" s="3"/>
     </row>
-    <row r="35" spans="1:393" s="55" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="52" t="s">
+    <row r="35" spans="1:393" s="45" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="53"/>
-      <c r="C35" s="53"/>
-      <c r="D35" s="53"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="53"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="53"/>
-      <c r="N35" s="53"/>
-      <c r="O35" s="53"/>
-      <c r="P35" s="53"/>
-      <c r="Q35" s="53"/>
-      <c r="R35" s="53"/>
-      <c r="S35" s="53"/>
-      <c r="T35" s="53"/>
-      <c r="U35" s="53"/>
-      <c r="V35" s="53"/>
-      <c r="W35" s="53"/>
-      <c r="X35" s="53"/>
-      <c r="Y35" s="53"/>
-      <c r="Z35" s="53"/>
-      <c r="AA35" s="53"/>
-      <c r="AB35" s="53"/>
-      <c r="AC35" s="53"/>
-      <c r="AD35" s="53"/>
-      <c r="AE35" s="53"/>
-      <c r="AF35" s="53"/>
-      <c r="AG35" s="53"/>
-      <c r="AH35" s="53"/>
-      <c r="AI35" s="53"/>
-      <c r="AJ35" s="54"/>
-      <c r="AK35" s="56"/>
-      <c r="AL35" s="56"/>
-      <c r="AM35" s="56"/>
-      <c r="AN35" s="56"/>
-      <c r="AO35" s="56"/>
-      <c r="AP35" s="56"/>
-      <c r="AQ35" s="56"/>
-      <c r="AR35" s="56"/>
-      <c r="AS35" s="56"/>
-      <c r="AT35" s="56"/>
-      <c r="AU35" s="56"/>
-      <c r="AV35" s="56"/>
-      <c r="AW35" s="56"/>
-      <c r="AX35" s="56"/>
-      <c r="AY35" s="56"/>
-      <c r="AZ35" s="56"/>
-      <c r="BA35" s="56"/>
-      <c r="BB35" s="56"/>
-      <c r="BC35" s="56"/>
-      <c r="BD35" s="56"/>
-      <c r="BE35" s="56"/>
-      <c r="BF35" s="56"/>
-      <c r="BG35" s="56"/>
-      <c r="BH35" s="56"/>
-      <c r="BI35" s="56"/>
-      <c r="BJ35" s="56"/>
-      <c r="BK35" s="56"/>
-      <c r="BL35" s="56"/>
-      <c r="BM35" s="56"/>
-      <c r="BN35" s="56"/>
-      <c r="BO35" s="56"/>
-      <c r="BP35" s="56"/>
-      <c r="BQ35" s="56"/>
-      <c r="BR35" s="56"/>
-      <c r="BS35" s="56"/>
-      <c r="BT35" s="56"/>
-      <c r="BU35" s="56"/>
-      <c r="BV35" s="56"/>
-      <c r="BW35" s="56"/>
-      <c r="BX35" s="56"/>
-      <c r="BY35" s="56"/>
-      <c r="BZ35" s="56"/>
-      <c r="CA35" s="56"/>
-      <c r="CB35" s="56"/>
-      <c r="CC35" s="56"/>
-      <c r="CD35" s="56"/>
-      <c r="CE35" s="56"/>
-      <c r="CF35" s="56"/>
-      <c r="CG35" s="56"/>
-      <c r="CH35" s="56"/>
-      <c r="CI35" s="56"/>
-      <c r="CJ35" s="56"/>
-      <c r="CK35" s="56"/>
-      <c r="CL35" s="56"/>
-      <c r="CM35" s="56"/>
-      <c r="CN35" s="56"/>
-      <c r="CO35" s="56"/>
-      <c r="CP35" s="56"/>
-      <c r="CQ35" s="56"/>
-      <c r="CR35" s="56"/>
-      <c r="CS35" s="56"/>
-      <c r="CT35" s="56"/>
-      <c r="CU35" s="56"/>
-      <c r="CV35" s="56"/>
-      <c r="CW35" s="56"/>
-      <c r="CX35" s="56"/>
-      <c r="CY35" s="56"/>
-      <c r="CZ35" s="56"/>
-      <c r="DA35" s="56"/>
-      <c r="DB35" s="56"/>
-      <c r="DC35" s="56"/>
-      <c r="DD35" s="56"/>
-      <c r="DE35" s="56"/>
-      <c r="DF35" s="56"/>
-      <c r="DG35" s="56"/>
-      <c r="DH35" s="56"/>
-      <c r="DI35" s="56"/>
-      <c r="DJ35" s="56"/>
-      <c r="DK35" s="56"/>
-      <c r="DL35" s="56"/>
-      <c r="DM35" s="56"/>
-      <c r="DN35" s="56"/>
-      <c r="DO35" s="56"/>
-      <c r="DP35" s="56"/>
-      <c r="DQ35" s="56"/>
-      <c r="DR35" s="56"/>
-      <c r="DS35" s="56"/>
-      <c r="DT35" s="56"/>
-      <c r="DU35" s="56"/>
-      <c r="DV35" s="56"/>
-      <c r="DW35" s="56"/>
-      <c r="DX35" s="56"/>
-      <c r="DY35" s="56"/>
-      <c r="DZ35" s="56"/>
-      <c r="EA35" s="56"/>
-      <c r="EB35" s="56"/>
-      <c r="EC35" s="56"/>
-      <c r="ED35" s="56"/>
-      <c r="EE35" s="56"/>
-      <c r="EF35" s="56"/>
-      <c r="EG35" s="56"/>
-      <c r="EH35" s="56"/>
-      <c r="EI35" s="56"/>
-      <c r="EJ35" s="56"/>
-      <c r="EK35" s="56"/>
-      <c r="EL35" s="56"/>
-      <c r="EM35" s="56"/>
-      <c r="EN35" s="56"/>
-      <c r="EO35" s="56"/>
-      <c r="EP35" s="56"/>
-      <c r="EQ35" s="56"/>
-      <c r="ER35" s="56"/>
-      <c r="ES35" s="56"/>
-      <c r="ET35" s="56"/>
-      <c r="EU35" s="56"/>
-      <c r="EV35" s="56"/>
-      <c r="EW35" s="56"/>
-      <c r="EX35" s="56"/>
-      <c r="EY35" s="56"/>
-      <c r="EZ35" s="56"/>
-      <c r="FA35" s="56"/>
-      <c r="FB35" s="56"/>
-      <c r="FC35" s="56"/>
-      <c r="FD35" s="56"/>
-      <c r="FE35" s="56"/>
-      <c r="FF35" s="56"/>
-      <c r="FG35" s="56"/>
-      <c r="FH35" s="56"/>
-      <c r="FI35" s="56"/>
-      <c r="FJ35" s="56"/>
-      <c r="FK35" s="56"/>
-      <c r="FL35" s="56"/>
-      <c r="FM35" s="56"/>
-      <c r="FN35" s="56"/>
-      <c r="FO35" s="56"/>
-      <c r="FP35" s="56"/>
-      <c r="FQ35" s="56"/>
-      <c r="FR35" s="56"/>
-      <c r="FS35" s="56"/>
-      <c r="FT35" s="56"/>
-      <c r="FU35" s="56"/>
-      <c r="FV35" s="56"/>
-      <c r="FW35" s="56"/>
-      <c r="FX35" s="56"/>
-      <c r="FY35" s="56"/>
-      <c r="FZ35" s="56"/>
-      <c r="GA35" s="56"/>
-      <c r="GB35" s="56"/>
-      <c r="GC35" s="56"/>
-      <c r="GD35" s="56"/>
-      <c r="GE35" s="56"/>
-      <c r="GF35" s="56"/>
-      <c r="GG35" s="56"/>
-      <c r="GH35" s="56"/>
-      <c r="GI35" s="56"/>
-      <c r="GJ35" s="56"/>
-      <c r="GK35" s="56"/>
-      <c r="GL35" s="56"/>
-      <c r="GM35" s="56"/>
-      <c r="GN35" s="56"/>
-      <c r="GO35" s="56"/>
-      <c r="GP35" s="56"/>
-      <c r="GQ35" s="56"/>
-      <c r="GR35" s="56"/>
-      <c r="GS35" s="56"/>
-      <c r="GT35" s="56"/>
-      <c r="GU35" s="56"/>
-      <c r="GV35" s="56"/>
-      <c r="GW35" s="56"/>
-      <c r="GX35" s="56"/>
-      <c r="GY35" s="56"/>
-      <c r="GZ35" s="56"/>
-      <c r="HA35" s="56"/>
-      <c r="HB35" s="56"/>
-      <c r="HC35" s="56"/>
-      <c r="HD35" s="56"/>
-      <c r="HE35" s="56"/>
-      <c r="HF35" s="56"/>
-      <c r="HG35" s="56"/>
-      <c r="HH35" s="56"/>
-      <c r="HI35" s="56"/>
-      <c r="HJ35" s="56"/>
-      <c r="HK35" s="56"/>
-      <c r="HL35" s="56"/>
-      <c r="HM35" s="56"/>
-      <c r="HN35" s="56"/>
-      <c r="HO35" s="56"/>
-      <c r="HP35" s="56"/>
-      <c r="HQ35" s="56"/>
-      <c r="HR35" s="56"/>
-      <c r="HS35" s="56"/>
-      <c r="HT35" s="56"/>
-      <c r="HU35" s="56"/>
-      <c r="HV35" s="56"/>
-      <c r="HW35" s="56"/>
-      <c r="HX35" s="56"/>
-      <c r="HY35" s="56"/>
-      <c r="HZ35" s="56"/>
-      <c r="IA35" s="56"/>
-      <c r="IB35" s="56"/>
-      <c r="IC35" s="56"/>
-      <c r="ID35" s="56"/>
-      <c r="IE35" s="56"/>
-      <c r="IF35" s="56"/>
-      <c r="IG35" s="56"/>
-      <c r="IH35" s="56"/>
-      <c r="II35" s="56"/>
-      <c r="IJ35" s="56"/>
-      <c r="IK35" s="56"/>
-      <c r="IL35" s="56"/>
-      <c r="IM35" s="56"/>
-      <c r="IN35" s="56"/>
-      <c r="IO35" s="56"/>
-      <c r="IP35" s="56"/>
-      <c r="IQ35" s="56"/>
-      <c r="IR35" s="56"/>
-      <c r="IS35" s="56"/>
-      <c r="IT35" s="56"/>
-      <c r="IU35" s="56"/>
-      <c r="IV35" s="56"/>
-      <c r="IW35" s="56"/>
-      <c r="IX35" s="56"/>
-      <c r="IY35" s="56"/>
-      <c r="IZ35" s="56"/>
-      <c r="JA35" s="56"/>
-      <c r="JB35" s="56"/>
-      <c r="JC35" s="56"/>
-      <c r="JD35" s="56"/>
-      <c r="JE35" s="56"/>
-      <c r="JF35" s="56"/>
-      <c r="JG35" s="56"/>
-      <c r="JH35" s="56"/>
-      <c r="JI35" s="56"/>
-      <c r="JJ35" s="56"/>
-      <c r="JK35" s="56"/>
-      <c r="JL35" s="56"/>
-      <c r="JM35" s="56"/>
-      <c r="JN35" s="56"/>
-      <c r="JO35" s="56"/>
-      <c r="JP35" s="56"/>
-      <c r="JQ35" s="56"/>
-      <c r="JR35" s="56"/>
-      <c r="JS35" s="56"/>
-      <c r="JT35" s="56"/>
-      <c r="JU35" s="56"/>
-      <c r="JV35" s="56"/>
-      <c r="JW35" s="56"/>
-      <c r="JX35" s="56"/>
-      <c r="JY35" s="56"/>
-      <c r="JZ35" s="56"/>
-      <c r="KA35" s="56"/>
-      <c r="KB35" s="56"/>
-      <c r="KC35" s="56"/>
-      <c r="KD35" s="56"/>
-      <c r="KE35" s="56"/>
-      <c r="KF35" s="56"/>
-      <c r="KG35" s="56"/>
-      <c r="KH35" s="56"/>
-      <c r="KI35" s="56"/>
-      <c r="KJ35" s="56"/>
-      <c r="KK35" s="56"/>
-      <c r="KL35" s="56"/>
-      <c r="KM35" s="56"/>
-      <c r="KN35" s="56"/>
-      <c r="KO35" s="56"/>
-      <c r="KP35" s="56"/>
-      <c r="KQ35" s="56"/>
-      <c r="KR35" s="56"/>
-      <c r="KS35" s="56"/>
-      <c r="KT35" s="56"/>
-      <c r="KU35" s="56"/>
-      <c r="KV35" s="56"/>
-      <c r="KW35" s="56"/>
-      <c r="KX35" s="56"/>
-      <c r="KY35" s="56"/>
-      <c r="KZ35" s="56"/>
-      <c r="LA35" s="56"/>
-      <c r="LB35" s="56"/>
-      <c r="LC35" s="56"/>
-      <c r="LD35" s="56"/>
-      <c r="LE35" s="56"/>
-      <c r="LF35" s="56"/>
-      <c r="LG35" s="56"/>
-      <c r="LH35" s="56"/>
-      <c r="LI35" s="56"/>
-      <c r="LJ35" s="56"/>
-      <c r="LK35" s="56"/>
-      <c r="LL35" s="56"/>
-      <c r="LM35" s="56"/>
-      <c r="LN35" s="56"/>
-      <c r="LO35" s="56"/>
-      <c r="LP35" s="56"/>
-      <c r="LQ35" s="56"/>
-      <c r="LR35" s="56"/>
-      <c r="LS35" s="56"/>
-      <c r="LT35" s="56"/>
-      <c r="LU35" s="56"/>
-      <c r="LV35" s="56"/>
-      <c r="LW35" s="56"/>
-      <c r="LX35" s="56"/>
-      <c r="LY35" s="56"/>
-      <c r="LZ35" s="56"/>
-      <c r="MA35" s="56"/>
-      <c r="MB35" s="56"/>
-      <c r="MC35" s="56"/>
-      <c r="MD35" s="56"/>
-      <c r="ME35" s="56"/>
-      <c r="MF35" s="56"/>
-      <c r="MG35" s="56"/>
-      <c r="MH35" s="56"/>
-      <c r="MI35" s="56"/>
-      <c r="MJ35" s="56"/>
-      <c r="MK35" s="56"/>
-      <c r="ML35" s="56"/>
-      <c r="MM35" s="56"/>
-      <c r="MN35" s="56"/>
-      <c r="MO35" s="56"/>
-      <c r="MP35" s="56"/>
-      <c r="MQ35" s="56"/>
-      <c r="MR35" s="56"/>
-      <c r="MS35" s="56"/>
-      <c r="MT35" s="56"/>
-      <c r="MU35" s="56"/>
-      <c r="MV35" s="56"/>
-      <c r="MW35" s="56"/>
-      <c r="MX35" s="56"/>
-      <c r="MY35" s="56"/>
-      <c r="MZ35" s="56"/>
-      <c r="NA35" s="56"/>
-      <c r="NB35" s="56"/>
-      <c r="NC35" s="56"/>
-      <c r="ND35" s="56"/>
-      <c r="NE35" s="56"/>
-      <c r="NF35" s="56"/>
-      <c r="NG35" s="56"/>
-      <c r="NH35" s="56"/>
-      <c r="NI35" s="56"/>
-      <c r="NJ35" s="56"/>
-      <c r="NK35" s="56"/>
-      <c r="NL35" s="56"/>
-      <c r="NM35" s="56"/>
-      <c r="NN35" s="56"/>
-      <c r="NO35" s="56"/>
-      <c r="NP35" s="56"/>
-      <c r="NQ35" s="56"/>
-      <c r="NR35" s="56"/>
-      <c r="NS35" s="56"/>
-      <c r="NT35" s="56"/>
-      <c r="NU35" s="56"/>
-      <c r="NV35" s="56"/>
-      <c r="NW35" s="56"/>
-      <c r="NX35" s="56"/>
-      <c r="NY35" s="56"/>
-      <c r="NZ35" s="56"/>
-      <c r="OA35" s="56"/>
-      <c r="OB35" s="56"/>
-      <c r="OC35" s="56"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="63"/>
+      <c r="P35" s="63"/>
+      <c r="Q35" s="63"/>
+      <c r="R35" s="63"/>
+      <c r="S35" s="63"/>
+      <c r="T35" s="63"/>
+      <c r="U35" s="63"/>
+      <c r="V35" s="63"/>
+      <c r="W35" s="63"/>
+      <c r="X35" s="63"/>
+      <c r="Y35" s="63"/>
+      <c r="Z35" s="63"/>
+      <c r="AA35" s="63"/>
+      <c r="AB35" s="63"/>
+      <c r="AC35" s="63"/>
+      <c r="AD35" s="63"/>
+      <c r="AE35" s="63"/>
+      <c r="AF35" s="63"/>
+      <c r="AG35" s="63"/>
+      <c r="AH35" s="63"/>
+      <c r="AI35" s="63"/>
+      <c r="AJ35" s="64"/>
+      <c r="AK35" s="46"/>
+      <c r="AL35" s="46"/>
+      <c r="AM35" s="46"/>
+      <c r="AN35" s="46"/>
+      <c r="AO35" s="46"/>
+      <c r="AP35" s="46"/>
+      <c r="AQ35" s="46"/>
+      <c r="AR35" s="46"/>
+      <c r="AS35" s="46"/>
+      <c r="AT35" s="46"/>
+      <c r="AU35" s="46"/>
+      <c r="AV35" s="46"/>
+      <c r="AW35" s="46"/>
+      <c r="AX35" s="46"/>
+      <c r="AY35" s="46"/>
+      <c r="AZ35" s="46"/>
+      <c r="BA35" s="46"/>
+      <c r="BB35" s="46"/>
+      <c r="BC35" s="46"/>
+      <c r="BD35" s="46"/>
+      <c r="BE35" s="46"/>
+      <c r="BF35" s="46"/>
+      <c r="BG35" s="46"/>
+      <c r="BH35" s="46"/>
+      <c r="BI35" s="46"/>
+      <c r="BJ35" s="46"/>
+      <c r="BK35" s="46"/>
+      <c r="BL35" s="46"/>
+      <c r="BM35" s="46"/>
+      <c r="BN35" s="46"/>
+      <c r="BO35" s="46"/>
+      <c r="BP35" s="46"/>
+      <c r="BQ35" s="46"/>
+      <c r="BR35" s="46"/>
+      <c r="BS35" s="46"/>
+      <c r="BT35" s="46"/>
+      <c r="BU35" s="46"/>
+      <c r="BV35" s="46"/>
+      <c r="BW35" s="46"/>
+      <c r="BX35" s="46"/>
+      <c r="BY35" s="46"/>
+      <c r="BZ35" s="46"/>
+      <c r="CA35" s="46"/>
+      <c r="CB35" s="46"/>
+      <c r="CC35" s="46"/>
+      <c r="CD35" s="46"/>
+      <c r="CE35" s="46"/>
+      <c r="CF35" s="46"/>
+      <c r="CG35" s="46"/>
+      <c r="CH35" s="46"/>
+      <c r="CI35" s="46"/>
+      <c r="CJ35" s="46"/>
+      <c r="CK35" s="46"/>
+      <c r="CL35" s="46"/>
+      <c r="CM35" s="46"/>
+      <c r="CN35" s="46"/>
+      <c r="CO35" s="46"/>
+      <c r="CP35" s="46"/>
+      <c r="CQ35" s="46"/>
+      <c r="CR35" s="46"/>
+      <c r="CS35" s="46"/>
+      <c r="CT35" s="46"/>
+      <c r="CU35" s="46"/>
+      <c r="CV35" s="46"/>
+      <c r="CW35" s="46"/>
+      <c r="CX35" s="46"/>
+      <c r="CY35" s="46"/>
+      <c r="CZ35" s="46"/>
+      <c r="DA35" s="46"/>
+      <c r="DB35" s="46"/>
+      <c r="DC35" s="46"/>
+      <c r="DD35" s="46"/>
+      <c r="DE35" s="46"/>
+      <c r="DF35" s="46"/>
+      <c r="DG35" s="46"/>
+      <c r="DH35" s="46"/>
+      <c r="DI35" s="46"/>
+      <c r="DJ35" s="46"/>
+      <c r="DK35" s="46"/>
+      <c r="DL35" s="46"/>
+      <c r="DM35" s="46"/>
+      <c r="DN35" s="46"/>
+      <c r="DO35" s="46"/>
+      <c r="DP35" s="46"/>
+      <c r="DQ35" s="46"/>
+      <c r="DR35" s="46"/>
+      <c r="DS35" s="46"/>
+      <c r="DT35" s="46"/>
+      <c r="DU35" s="46"/>
+      <c r="DV35" s="46"/>
+      <c r="DW35" s="46"/>
+      <c r="DX35" s="46"/>
+      <c r="DY35" s="46"/>
+      <c r="DZ35" s="46"/>
+      <c r="EA35" s="46"/>
+      <c r="EB35" s="46"/>
+      <c r="EC35" s="46"/>
+      <c r="ED35" s="46"/>
+      <c r="EE35" s="46"/>
+      <c r="EF35" s="46"/>
+      <c r="EG35" s="46"/>
+      <c r="EH35" s="46"/>
+      <c r="EI35" s="46"/>
+      <c r="EJ35" s="46"/>
+      <c r="EK35" s="46"/>
+      <c r="EL35" s="46"/>
+      <c r="EM35" s="46"/>
+      <c r="EN35" s="46"/>
+      <c r="EO35" s="46"/>
+      <c r="EP35" s="46"/>
+      <c r="EQ35" s="46"/>
+      <c r="ER35" s="46"/>
+      <c r="ES35" s="46"/>
+      <c r="ET35" s="46"/>
+      <c r="EU35" s="46"/>
+      <c r="EV35" s="46"/>
+      <c r="EW35" s="46"/>
+      <c r="EX35" s="46"/>
+      <c r="EY35" s="46"/>
+      <c r="EZ35" s="46"/>
+      <c r="FA35" s="46"/>
+      <c r="FB35" s="46"/>
+      <c r="FC35" s="46"/>
+      <c r="FD35" s="46"/>
+      <c r="FE35" s="46"/>
+      <c r="FF35" s="46"/>
+      <c r="FG35" s="46"/>
+      <c r="FH35" s="46"/>
+      <c r="FI35" s="46"/>
+      <c r="FJ35" s="46"/>
+      <c r="FK35" s="46"/>
+      <c r="FL35" s="46"/>
+      <c r="FM35" s="46"/>
+      <c r="FN35" s="46"/>
+      <c r="FO35" s="46"/>
+      <c r="FP35" s="46"/>
+      <c r="FQ35" s="46"/>
+      <c r="FR35" s="46"/>
+      <c r="FS35" s="46"/>
+      <c r="FT35" s="46"/>
+      <c r="FU35" s="46"/>
+      <c r="FV35" s="46"/>
+      <c r="FW35" s="46"/>
+      <c r="FX35" s="46"/>
+      <c r="FY35" s="46"/>
+      <c r="FZ35" s="46"/>
+      <c r="GA35" s="46"/>
+      <c r="GB35" s="46"/>
+      <c r="GC35" s="46"/>
+      <c r="GD35" s="46"/>
+      <c r="GE35" s="46"/>
+      <c r="GF35" s="46"/>
+      <c r="GG35" s="46"/>
+      <c r="GH35" s="46"/>
+      <c r="GI35" s="46"/>
+      <c r="GJ35" s="46"/>
+      <c r="GK35" s="46"/>
+      <c r="GL35" s="46"/>
+      <c r="GM35" s="46"/>
+      <c r="GN35" s="46"/>
+      <c r="GO35" s="46"/>
+      <c r="GP35" s="46"/>
+      <c r="GQ35" s="46"/>
+      <c r="GR35" s="46"/>
+      <c r="GS35" s="46"/>
+      <c r="GT35" s="46"/>
+      <c r="GU35" s="46"/>
+      <c r="GV35" s="46"/>
+      <c r="GW35" s="46"/>
+      <c r="GX35" s="46"/>
+      <c r="GY35" s="46"/>
+      <c r="GZ35" s="46"/>
+      <c r="HA35" s="46"/>
+      <c r="HB35" s="46"/>
+      <c r="HC35" s="46"/>
+      <c r="HD35" s="46"/>
+      <c r="HE35" s="46"/>
+      <c r="HF35" s="46"/>
+      <c r="HG35" s="46"/>
+      <c r="HH35" s="46"/>
+      <c r="HI35" s="46"/>
+      <c r="HJ35" s="46"/>
+      <c r="HK35" s="46"/>
+      <c r="HL35" s="46"/>
+      <c r="HM35" s="46"/>
+      <c r="HN35" s="46"/>
+      <c r="HO35" s="46"/>
+      <c r="HP35" s="46"/>
+      <c r="HQ35" s="46"/>
+      <c r="HR35" s="46"/>
+      <c r="HS35" s="46"/>
+      <c r="HT35" s="46"/>
+      <c r="HU35" s="46"/>
+      <c r="HV35" s="46"/>
+      <c r="HW35" s="46"/>
+      <c r="HX35" s="46"/>
+      <c r="HY35" s="46"/>
+      <c r="HZ35" s="46"/>
+      <c r="IA35" s="46"/>
+      <c r="IB35" s="46"/>
+      <c r="IC35" s="46"/>
+      <c r="ID35" s="46"/>
+      <c r="IE35" s="46"/>
+      <c r="IF35" s="46"/>
+      <c r="IG35" s="46"/>
+      <c r="IH35" s="46"/>
+      <c r="II35" s="46"/>
+      <c r="IJ35" s="46"/>
+      <c r="IK35" s="46"/>
+      <c r="IL35" s="46"/>
+      <c r="IM35" s="46"/>
+      <c r="IN35" s="46"/>
+      <c r="IO35" s="46"/>
+      <c r="IP35" s="46"/>
+      <c r="IQ35" s="46"/>
+      <c r="IR35" s="46"/>
+      <c r="IS35" s="46"/>
+      <c r="IT35" s="46"/>
+      <c r="IU35" s="46"/>
+      <c r="IV35" s="46"/>
+      <c r="IW35" s="46"/>
+      <c r="IX35" s="46"/>
+      <c r="IY35" s="46"/>
+      <c r="IZ35" s="46"/>
+      <c r="JA35" s="46"/>
+      <c r="JB35" s="46"/>
+      <c r="JC35" s="46"/>
+      <c r="JD35" s="46"/>
+      <c r="JE35" s="46"/>
+      <c r="JF35" s="46"/>
+      <c r="JG35" s="46"/>
+      <c r="JH35" s="46"/>
+      <c r="JI35" s="46"/>
+      <c r="JJ35" s="46"/>
+      <c r="JK35" s="46"/>
+      <c r="JL35" s="46"/>
+      <c r="JM35" s="46"/>
+      <c r="JN35" s="46"/>
+      <c r="JO35" s="46"/>
+      <c r="JP35" s="46"/>
+      <c r="JQ35" s="46"/>
+      <c r="JR35" s="46"/>
+      <c r="JS35" s="46"/>
+      <c r="JT35" s="46"/>
+      <c r="JU35" s="46"/>
+      <c r="JV35" s="46"/>
+      <c r="JW35" s="46"/>
+      <c r="JX35" s="46"/>
+      <c r="JY35" s="46"/>
+      <c r="JZ35" s="46"/>
+      <c r="KA35" s="46"/>
+      <c r="KB35" s="46"/>
+      <c r="KC35" s="46"/>
+      <c r="KD35" s="46"/>
+      <c r="KE35" s="46"/>
+      <c r="KF35" s="46"/>
+      <c r="KG35" s="46"/>
+      <c r="KH35" s="46"/>
+      <c r="KI35" s="46"/>
+      <c r="KJ35" s="46"/>
+      <c r="KK35" s="46"/>
+      <c r="KL35" s="46"/>
+      <c r="KM35" s="46"/>
+      <c r="KN35" s="46"/>
+      <c r="KO35" s="46"/>
+      <c r="KP35" s="46"/>
+      <c r="KQ35" s="46"/>
+      <c r="KR35" s="46"/>
+      <c r="KS35" s="46"/>
+      <c r="KT35" s="46"/>
+      <c r="KU35" s="46"/>
+      <c r="KV35" s="46"/>
+      <c r="KW35" s="46"/>
+      <c r="KX35" s="46"/>
+      <c r="KY35" s="46"/>
+      <c r="KZ35" s="46"/>
+      <c r="LA35" s="46"/>
+      <c r="LB35" s="46"/>
+      <c r="LC35" s="46"/>
+      <c r="LD35" s="46"/>
+      <c r="LE35" s="46"/>
+      <c r="LF35" s="46"/>
+      <c r="LG35" s="46"/>
+      <c r="LH35" s="46"/>
+      <c r="LI35" s="46"/>
+      <c r="LJ35" s="46"/>
+      <c r="LK35" s="46"/>
+      <c r="LL35" s="46"/>
+      <c r="LM35" s="46"/>
+      <c r="LN35" s="46"/>
+      <c r="LO35" s="46"/>
+      <c r="LP35" s="46"/>
+      <c r="LQ35" s="46"/>
+      <c r="LR35" s="46"/>
+      <c r="LS35" s="46"/>
+      <c r="LT35" s="46"/>
+      <c r="LU35" s="46"/>
+      <c r="LV35" s="46"/>
+      <c r="LW35" s="46"/>
+      <c r="LX35" s="46"/>
+      <c r="LY35" s="46"/>
+      <c r="LZ35" s="46"/>
+      <c r="MA35" s="46"/>
+      <c r="MB35" s="46"/>
+      <c r="MC35" s="46"/>
+      <c r="MD35" s="46"/>
+      <c r="ME35" s="46"/>
+      <c r="MF35" s="46"/>
+      <c r="MG35" s="46"/>
+      <c r="MH35" s="46"/>
+      <c r="MI35" s="46"/>
+      <c r="MJ35" s="46"/>
+      <c r="MK35" s="46"/>
+      <c r="ML35" s="46"/>
+      <c r="MM35" s="46"/>
+      <c r="MN35" s="46"/>
+      <c r="MO35" s="46"/>
+      <c r="MP35" s="46"/>
+      <c r="MQ35" s="46"/>
+      <c r="MR35" s="46"/>
+      <c r="MS35" s="46"/>
+      <c r="MT35" s="46"/>
+      <c r="MU35" s="46"/>
+      <c r="MV35" s="46"/>
+      <c r="MW35" s="46"/>
+      <c r="MX35" s="46"/>
+      <c r="MY35" s="46"/>
+      <c r="MZ35" s="46"/>
+      <c r="NA35" s="46"/>
+      <c r="NB35" s="46"/>
+      <c r="NC35" s="46"/>
+      <c r="ND35" s="46"/>
+      <c r="NE35" s="46"/>
+      <c r="NF35" s="46"/>
+      <c r="NG35" s="46"/>
+      <c r="NH35" s="46"/>
+      <c r="NI35" s="46"/>
+      <c r="NJ35" s="46"/>
+      <c r="NK35" s="46"/>
+      <c r="NL35" s="46"/>
+      <c r="NM35" s="46"/>
+      <c r="NN35" s="46"/>
+      <c r="NO35" s="46"/>
+      <c r="NP35" s="46"/>
+      <c r="NQ35" s="46"/>
+      <c r="NR35" s="46"/>
+      <c r="NS35" s="46"/>
+      <c r="NT35" s="46"/>
+      <c r="NU35" s="46"/>
+      <c r="NV35" s="46"/>
+      <c r="NW35" s="46"/>
+      <c r="NX35" s="46"/>
+      <c r="NY35" s="46"/>
+      <c r="NZ35" s="46"/>
+      <c r="OA35" s="46"/>
+      <c r="OB35" s="46"/>
+      <c r="OC35" s="46"/>
     </row>
     <row r="36" spans="1:393" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>84</v>
@@ -9995,10 +9991,10 @@
       <c r="G36" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H36" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="I36" s="25" t="s">
+      <c r="H36" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I36" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J36" s="3"/>
@@ -10009,8 +10005,8 @@
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
-      <c r="R36" s="75"/>
-      <c r="S36" s="75"/>
+      <c r="R36" s="78"/>
+      <c r="S36" s="78"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
@@ -10049,10 +10045,10 @@
       <c r="G37" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H37" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="I37" s="25" t="s">
+      <c r="H37" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I37" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J37" s="7"/>
@@ -10063,7 +10059,7 @@
       <c r="O37" s="7"/>
       <c r="P37" s="7"/>
       <c r="Q37" s="4"/>
-      <c r="R37" s="76"/>
+      <c r="R37" s="79"/>
       <c r="S37" s="4"/>
       <c r="T37" s="4"/>
       <c r="U37" s="4"/>
@@ -10103,10 +10099,10 @@
       <c r="G38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H38" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="I38" s="25" t="s">
+      <c r="H38" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I38" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J38" s="3"/>
@@ -10117,7 +10113,7 @@
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
-      <c r="R38" s="75"/>
+      <c r="R38" s="78"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
@@ -10157,10 +10153,10 @@
       <c r="G39" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H39" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I39" s="25" t="s">
+      <c r="H39" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I39" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J39" s="7"/>
@@ -10171,7 +10167,7 @@
       <c r="O39" s="7"/>
       <c r="P39" s="7"/>
       <c r="Q39" s="4"/>
-      <c r="R39" s="77"/>
+      <c r="R39" s="79"/>
       <c r="S39" s="4"/>
       <c r="T39" s="4"/>
       <c r="U39" s="4"/>
@@ -10211,10 +10207,10 @@
       <c r="G40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H40" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="I40" s="37" t="s">
+      <c r="H40" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I40" s="32" t="s">
         <v>49</v>
       </c>
       <c r="J40" s="3"/>
@@ -10248,7 +10244,7 @@
     <row r="41" spans="1:393" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>84</v>
@@ -10265,10 +10261,10 @@
       <c r="G41" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H41" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I41" s="37" t="s">
+      <c r="H41" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I41" s="32" t="s">
         <v>49</v>
       </c>
       <c r="J41" s="7"/>
@@ -10280,7 +10276,7 @@
       <c r="P41" s="7"/>
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
-      <c r="S41" s="77"/>
+      <c r="S41" s="79"/>
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
       <c r="V41" s="4"/>
@@ -10319,11 +10315,11 @@
       <c r="G42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H42" s="57" t="s">
+      <c r="H42" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I42" s="48" t="s">
         <v>86</v>
-      </c>
-      <c r="I42" s="59" t="s">
-        <v>87</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -10354,49 +10350,49 @@
       <c r="AJ42" s="3"/>
     </row>
     <row r="43" spans="1:393" x14ac:dyDescent="0.2">
-      <c r="A43" s="60" t="s">
-        <v>120</v>
-      </c>
-      <c r="B43" s="61"/>
-      <c r="C43" s="61"/>
-      <c r="D43" s="61"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="61"/>
-      <c r="G43" s="61"/>
-      <c r="H43" s="61"/>
-      <c r="I43" s="61"/>
-      <c r="J43" s="61"/>
-      <c r="K43" s="61"/>
-      <c r="L43" s="61"/>
-      <c r="M43" s="61"/>
-      <c r="N43" s="61"/>
-      <c r="O43" s="61"/>
-      <c r="P43" s="61"/>
-      <c r="Q43" s="61"/>
-      <c r="R43" s="61"/>
-      <c r="S43" s="61"/>
-      <c r="T43" s="61"/>
-      <c r="U43" s="61"/>
-      <c r="V43" s="61"/>
-      <c r="W43" s="61"/>
-      <c r="X43" s="61"/>
-      <c r="Y43" s="61"/>
-      <c r="Z43" s="61"/>
-      <c r="AA43" s="61"/>
-      <c r="AB43" s="61"/>
-      <c r="AC43" s="61"/>
-      <c r="AD43" s="61"/>
-      <c r="AE43" s="61"/>
-      <c r="AF43" s="61"/>
-      <c r="AG43" s="61"/>
-      <c r="AH43" s="61"/>
-      <c r="AI43" s="61"/>
-      <c r="AJ43" s="62"/>
+      <c r="A43" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" s="66"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="66"/>
+      <c r="L43" s="66"/>
+      <c r="M43" s="66"/>
+      <c r="N43" s="66"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="66"/>
+      <c r="Q43" s="66"/>
+      <c r="R43" s="66"/>
+      <c r="S43" s="66"/>
+      <c r="T43" s="66"/>
+      <c r="U43" s="66"/>
+      <c r="V43" s="66"/>
+      <c r="W43" s="66"/>
+      <c r="X43" s="66"/>
+      <c r="Y43" s="66"/>
+      <c r="Z43" s="66"/>
+      <c r="AA43" s="66"/>
+      <c r="AB43" s="66"/>
+      <c r="AC43" s="66"/>
+      <c r="AD43" s="66"/>
+      <c r="AE43" s="66"/>
+      <c r="AF43" s="66"/>
+      <c r="AG43" s="66"/>
+      <c r="AH43" s="66"/>
+      <c r="AI43" s="66"/>
+      <c r="AJ43" s="67"/>
     </row>
     <row r="44" spans="1:393" x14ac:dyDescent="0.2">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>62</v>
@@ -10413,10 +10409,10 @@
       <c r="G44" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H44" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I44" s="25" t="s">
+      <c r="H44" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I44" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J44" s="3"/>
@@ -10429,7 +10425,7 @@
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
-      <c r="T44" s="78"/>
+      <c r="T44" s="57"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -10450,7 +10446,7 @@
     <row r="45" spans="1:393" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>62</v>
@@ -10467,10 +10463,10 @@
       <c r="G45" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H45" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I45" s="25" t="s">
+      <c r="H45" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I45" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J45" s="7"/>
@@ -10483,7 +10479,7 @@
       <c r="Q45" s="4"/>
       <c r="R45" s="4"/>
       <c r="S45" s="4"/>
-      <c r="T45" s="77"/>
+      <c r="T45" s="58"/>
       <c r="U45" s="4"/>
       <c r="V45" s="4"/>
       <c r="W45" s="4"/>
@@ -10504,7 +10500,7 @@
     <row r="46" spans="1:393" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>62</v>
@@ -10521,10 +10517,10 @@
       <c r="G46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H46" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I46" s="25" t="s">
+      <c r="H46" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I46" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J46" s="3"/>
@@ -10537,7 +10533,7 @@
       <c r="Q46" s="3"/>
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
-      <c r="T46" s="78"/>
+      <c r="T46" s="59"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -10558,7 +10554,7 @@
     <row r="47" spans="1:393" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>62</v>
@@ -10575,10 +10571,10 @@
       <c r="G47" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H47" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I47" s="25" t="s">
+      <c r="H47" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I47" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J47" s="7"/>
@@ -10592,7 +10588,7 @@
       <c r="R47" s="4"/>
       <c r="S47" s="4"/>
       <c r="T47" s="4"/>
-      <c r="U47" s="77"/>
+      <c r="U47" s="58"/>
       <c r="V47" s="4"/>
       <c r="W47" s="4"/>
       <c r="X47" s="4"/>
@@ -10612,7 +10608,7 @@
     <row r="48" spans="1:393" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>62</v>
@@ -10629,10 +10625,10 @@
       <c r="G48" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H48" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I48" s="25" t="s">
+      <c r="H48" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I48" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J48" s="3"/>
@@ -10646,7 +10642,7 @@
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
-      <c r="U48" s="78"/>
+      <c r="U48" s="59"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
@@ -10666,7 +10662,7 @@
     <row r="49" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>62</v>
@@ -10683,10 +10679,10 @@
       <c r="G49" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H49" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I49" s="25" t="s">
+      <c r="H49" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I49" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J49" s="7"/>
@@ -10700,7 +10696,7 @@
       <c r="R49" s="4"/>
       <c r="S49" s="4"/>
       <c r="T49" s="4"/>
-      <c r="U49" s="77"/>
+      <c r="U49" s="58"/>
       <c r="V49" s="4"/>
       <c r="W49" s="4"/>
       <c r="X49" s="4"/>
@@ -10720,7 +10716,7 @@
     <row r="50" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>62</v>
@@ -10737,10 +10733,10 @@
       <c r="G50" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H50" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I50" s="25" t="s">
+      <c r="H50" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I50" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J50" s="3"/>
@@ -10755,7 +10751,7 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
-      <c r="V50" s="78"/>
+      <c r="V50" s="59"/>
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
@@ -10774,7 +10770,7 @@
     <row r="51" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>62</v>
@@ -10791,10 +10787,10 @@
       <c r="G51" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H51" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I51" s="37" t="s">
+      <c r="H51" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I51" s="32" t="s">
         <v>49</v>
       </c>
       <c r="J51" s="7"/>
@@ -10809,7 +10805,7 @@
       <c r="S51" s="4"/>
       <c r="T51" s="4"/>
       <c r="U51" s="4"/>
-      <c r="V51" s="77"/>
+      <c r="V51" s="58"/>
       <c r="W51" s="4"/>
       <c r="X51" s="4"/>
       <c r="Y51" s="4"/>
@@ -10828,7 +10824,7 @@
     <row r="52" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>62</v>
@@ -10845,10 +10841,10 @@
       <c r="G52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H52" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I52" s="25" t="s">
+      <c r="H52" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I52" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J52" s="3"/>
@@ -10864,7 +10860,7 @@
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
-      <c r="W52" s="78"/>
+      <c r="W52" s="59"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
@@ -10882,7 +10878,7 @@
     <row r="53" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>62</v>
@@ -10899,10 +10895,10 @@
       <c r="G53" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H53" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I53" s="25" t="s">
+      <c r="H53" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I53" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J53" s="7"/>
@@ -10919,7 +10915,7 @@
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
       <c r="W53" s="4"/>
-      <c r="X53" s="77"/>
+      <c r="X53" s="58"/>
       <c r="Y53" s="4"/>
       <c r="Z53" s="4"/>
       <c r="AA53" s="4"/>
@@ -10936,7 +10932,7 @@
     <row r="54" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>62</v>
@@ -10953,10 +10949,10 @@
       <c r="G54" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H54" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I54" s="25" t="s">
+      <c r="H54" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I54" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J54" s="3"/>
@@ -10973,7 +10969,7 @@
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
-      <c r="X54" s="78"/>
+      <c r="X54" s="59"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
       <c r="AA54" s="3"/>
@@ -10990,7 +10986,7 @@
     <row r="55" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>62</v>
@@ -11007,10 +11003,10 @@
       <c r="G55" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H55" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I55" s="37" t="s">
+      <c r="H55" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I55" s="32" t="s">
         <v>49</v>
       </c>
       <c r="J55" s="7"/>
@@ -11028,8 +11024,8 @@
       <c r="V55" s="4"/>
       <c r="W55" s="4"/>
       <c r="X55" s="4"/>
-      <c r="Y55" s="77"/>
-      <c r="Z55" s="77"/>
+      <c r="Y55" s="58"/>
+      <c r="Z55" s="58"/>
       <c r="AA55" s="4"/>
       <c r="AB55" s="4"/>
       <c r="AC55" s="4"/>
@@ -11042,52 +11038,52 @@
       <c r="AJ55" s="4"/>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A56" s="63" t="s">
-        <v>100</v>
-      </c>
-      <c r="B56" s="64"/>
-      <c r="C56" s="64"/>
-      <c r="D56" s="64"/>
-      <c r="E56" s="64"/>
-      <c r="F56" s="64"/>
-      <c r="G56" s="64"/>
-      <c r="H56" s="64"/>
-      <c r="I56" s="64"/>
-      <c r="J56" s="64"/>
-      <c r="K56" s="64"/>
-      <c r="L56" s="64"/>
-      <c r="M56" s="64"/>
-      <c r="N56" s="64"/>
-      <c r="O56" s="64"/>
-      <c r="P56" s="64"/>
-      <c r="Q56" s="64"/>
-      <c r="R56" s="64"/>
-      <c r="S56" s="64"/>
-      <c r="T56" s="64"/>
-      <c r="U56" s="64"/>
-      <c r="V56" s="64"/>
-      <c r="W56" s="64"/>
-      <c r="X56" s="64"/>
-      <c r="Y56" s="64"/>
-      <c r="Z56" s="64"/>
-      <c r="AA56" s="64"/>
-      <c r="AB56" s="64"/>
-      <c r="AC56" s="64"/>
-      <c r="AD56" s="64"/>
-      <c r="AE56" s="64"/>
-      <c r="AF56" s="64"/>
-      <c r="AG56" s="64"/>
-      <c r="AH56" s="64"/>
-      <c r="AI56" s="64"/>
-      <c r="AJ56" s="64"/>
+      <c r="A56" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B56" s="69"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
+      <c r="E56" s="69"/>
+      <c r="F56" s="69"/>
+      <c r="G56" s="69"/>
+      <c r="H56" s="69"/>
+      <c r="I56" s="69"/>
+      <c r="J56" s="69"/>
+      <c r="K56" s="69"/>
+      <c r="L56" s="69"/>
+      <c r="M56" s="69"/>
+      <c r="N56" s="69"/>
+      <c r="O56" s="69"/>
+      <c r="P56" s="69"/>
+      <c r="Q56" s="69"/>
+      <c r="R56" s="69"/>
+      <c r="S56" s="69"/>
+      <c r="T56" s="69"/>
+      <c r="U56" s="69"/>
+      <c r="V56" s="69"/>
+      <c r="W56" s="69"/>
+      <c r="X56" s="69"/>
+      <c r="Y56" s="69"/>
+      <c r="Z56" s="69"/>
+      <c r="AA56" s="69"/>
+      <c r="AB56" s="69"/>
+      <c r="AC56" s="69"/>
+      <c r="AD56" s="69"/>
+      <c r="AE56" s="69"/>
+      <c r="AF56" s="69"/>
+      <c r="AG56" s="69"/>
+      <c r="AH56" s="69"/>
+      <c r="AI56" s="69"/>
+      <c r="AJ56" s="69"/>
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>39</v>
@@ -11101,10 +11097,10 @@
       <c r="G57" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H57" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I57" s="25" t="s">
+      <c r="H57" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I57" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J57" s="7"/>
@@ -11123,8 +11119,8 @@
       <c r="W57" s="4"/>
       <c r="X57" s="4"/>
       <c r="Y57" s="4"/>
-      <c r="Z57" s="77"/>
-      <c r="AA57" s="77"/>
+      <c r="Z57" s="58"/>
+      <c r="AA57" s="58"/>
       <c r="AB57" s="4"/>
       <c r="AC57" s="4"/>
       <c r="AD57" s="4"/>
@@ -11137,39 +11133,39 @@
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D58" t="s">
         <v>39</v>
       </c>
-      <c r="E58" s="65">
+      <c r="E58" s="49">
         <v>46194</v>
       </c>
-      <c r="F58" s="65">
+      <c r="F58" s="49">
         <v>46208</v>
       </c>
       <c r="G58" t="s">
         <v>40</v>
       </c>
-      <c r="H58" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I58" s="25" t="s">
+      <c r="H58" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I58" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="Z58" s="79"/>
-      <c r="AA58" s="79"/>
+      <c r="Z58" s="60"/>
+      <c r="AA58" s="60"/>
     </row>
     <row r="59" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>39</v>
@@ -11183,10 +11179,10 @@
       <c r="G59" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H59" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I59" s="25" t="s">
+      <c r="H59" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I59" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J59" s="7"/>
@@ -11206,7 +11202,7 @@
       <c r="X59" s="4"/>
       <c r="Y59" s="4"/>
       <c r="Z59" s="4"/>
-      <c r="AA59" s="77"/>
+      <c r="AA59" s="58"/>
       <c r="AB59" s="4"/>
       <c r="AC59" s="4"/>
       <c r="AD59" s="4"/>
@@ -11219,39 +11215,39 @@
     </row>
     <row r="60" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C60" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D60" t="s">
         <v>39</v>
       </c>
-      <c r="E60" s="65">
+      <c r="E60" s="49">
         <v>46201</v>
       </c>
-      <c r="F60" s="65">
+      <c r="F60" s="49">
         <v>46208</v>
       </c>
       <c r="G60" t="s">
         <v>40</v>
       </c>
-      <c r="H60" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I60" s="25" t="s">
+      <c r="H60" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I60" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="AB60" s="79"/>
-      <c r="AC60" s="79"/>
+      <c r="AB60" s="60"/>
+      <c r="AC60" s="60"/>
     </row>
     <row r="61" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>39</v>
@@ -11265,10 +11261,10 @@
       <c r="G61" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H61" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I61" s="25" t="s">
+      <c r="H61" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I61" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J61" s="7"/>
@@ -11289,8 +11285,8 @@
       <c r="Y61" s="4"/>
       <c r="Z61" s="4"/>
       <c r="AA61" s="4"/>
-      <c r="AB61" s="77"/>
-      <c r="AC61" s="77"/>
+      <c r="AB61" s="58"/>
+      <c r="AC61" s="58"/>
       <c r="AD61" s="4"/>
       <c r="AE61" s="4"/>
       <c r="AF61" s="4"/>
@@ -11299,53 +11295,53 @@
       <c r="AI61" s="4"/>
       <c r="AJ61" s="4"/>
     </row>
-    <row r="62" spans="1:36" s="51" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="66" t="s">
-        <v>107</v>
-      </c>
-      <c r="B62" s="67"/>
-      <c r="C62" s="67"/>
-      <c r="D62" s="67"/>
-      <c r="E62" s="67"/>
-      <c r="F62" s="67"/>
-      <c r="G62" s="67"/>
-      <c r="H62" s="67"/>
-      <c r="I62" s="67"/>
-      <c r="J62" s="67"/>
-      <c r="K62" s="67"/>
-      <c r="L62" s="67"/>
-      <c r="M62" s="67"/>
-      <c r="N62" s="67"/>
-      <c r="O62" s="67"/>
-      <c r="P62" s="67"/>
-      <c r="Q62" s="67"/>
-      <c r="R62" s="67"/>
-      <c r="S62" s="67"/>
-      <c r="T62" s="67"/>
-      <c r="U62" s="67"/>
-      <c r="V62" s="67"/>
-      <c r="W62" s="67"/>
-      <c r="X62" s="67"/>
-      <c r="Y62" s="67"/>
-      <c r="Z62" s="67"/>
-      <c r="AA62" s="67"/>
-      <c r="AB62" s="67"/>
-      <c r="AC62" s="67"/>
-      <c r="AD62" s="67"/>
-      <c r="AE62" s="67"/>
-      <c r="AF62" s="67"/>
-      <c r="AG62" s="67"/>
-      <c r="AH62" s="67"/>
-      <c r="AI62" s="67"/>
-      <c r="AJ62" s="67"/>
+    <row r="62" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="70" t="s">
+        <v>106</v>
+      </c>
+      <c r="B62" s="71"/>
+      <c r="C62" s="71"/>
+      <c r="D62" s="71"/>
+      <c r="E62" s="71"/>
+      <c r="F62" s="71"/>
+      <c r="G62" s="71"/>
+      <c r="H62" s="71"/>
+      <c r="I62" s="71"/>
+      <c r="J62" s="71"/>
+      <c r="K62" s="71"/>
+      <c r="L62" s="71"/>
+      <c r="M62" s="71"/>
+      <c r="N62" s="71"/>
+      <c r="O62" s="71"/>
+      <c r="P62" s="71"/>
+      <c r="Q62" s="71"/>
+      <c r="R62" s="71"/>
+      <c r="S62" s="71"/>
+      <c r="T62" s="71"/>
+      <c r="U62" s="71"/>
+      <c r="V62" s="71"/>
+      <c r="W62" s="71"/>
+      <c r="X62" s="71"/>
+      <c r="Y62" s="71"/>
+      <c r="Z62" s="71"/>
+      <c r="AA62" s="71"/>
+      <c r="AB62" s="71"/>
+      <c r="AC62" s="71"/>
+      <c r="AD62" s="71"/>
+      <c r="AE62" s="71"/>
+      <c r="AF62" s="71"/>
+      <c r="AG62" s="71"/>
+      <c r="AH62" s="71"/>
+      <c r="AI62" s="71"/>
+      <c r="AJ62" s="71"/>
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>58</v>
@@ -11359,10 +11355,10 @@
       <c r="G63" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H63" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I63" s="37" t="s">
+      <c r="H63" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I63" s="32" t="s">
         <v>49</v>
       </c>
       <c r="J63" s="7"/>
@@ -11384,8 +11380,8 @@
       <c r="Z63" s="4"/>
       <c r="AA63" s="4"/>
       <c r="AB63" s="4"/>
-      <c r="AC63" s="77"/>
-      <c r="AD63" s="77"/>
+      <c r="AC63" s="58"/>
+      <c r="AD63" s="58"/>
       <c r="AE63" s="4"/>
       <c r="AF63" s="4"/>
       <c r="AG63" s="4"/>
@@ -11395,39 +11391,39 @@
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C64" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D64" t="s">
         <v>63</v>
       </c>
-      <c r="E64" s="65">
+      <c r="E64" s="49">
         <v>46215</v>
       </c>
-      <c r="F64" s="65">
+      <c r="F64" s="49">
         <v>46229</v>
       </c>
       <c r="G64" t="s">
         <v>40</v>
       </c>
-      <c r="H64" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I64" s="37" t="s">
+      <c r="H64" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I64" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="AC64" s="79"/>
-      <c r="AD64" s="79"/>
+      <c r="AC64" s="60"/>
+      <c r="AD64" s="60"/>
     </row>
     <row r="65" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>63</v>
@@ -11441,10 +11437,10 @@
       <c r="G65" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H65" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="I65" s="25" t="s">
+      <c r="H65" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I65" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J65" s="7"/>
@@ -11468,50 +11464,50 @@
       <c r="AB65" s="4"/>
       <c r="AC65" s="4"/>
       <c r="AD65" s="4"/>
-      <c r="AE65" s="77"/>
-      <c r="AF65" s="77"/>
-      <c r="AG65" s="77"/>
-      <c r="AH65" s="77"/>
+      <c r="AE65" s="58"/>
+      <c r="AF65" s="58"/>
+      <c r="AG65" s="58"/>
+      <c r="AH65" s="58"/>
       <c r="AI65" s="4"/>
       <c r="AJ65" s="4"/>
     </row>
     <row r="66" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C66" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D66" t="s">
         <v>39</v>
       </c>
-      <c r="E66" s="65">
+      <c r="E66" s="49">
         <v>46243</v>
       </c>
-      <c r="F66" s="65">
+      <c r="F66" s="49">
         <v>46271</v>
       </c>
       <c r="G66" t="s">
         <v>40</v>
       </c>
-      <c r="H66" s="58" t="s">
+      <c r="H66" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I66" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="I66" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG66" s="79"/>
-      <c r="AH66" s="79"/>
-      <c r="AI66" s="79"/>
-      <c r="AJ66" s="79"/>
+      <c r="AG66" s="60"/>
+      <c r="AH66" s="60"/>
+      <c r="AI66" s="60"/>
+      <c r="AJ66" s="60"/>
     </row>
     <row r="67" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>58</v>
@@ -11525,11 +11521,11 @@
       <c r="G67" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H67" s="58" t="s">
+      <c r="H67" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="I67" s="48" t="s">
         <v>86</v>
-      </c>
-      <c r="I67" s="59" t="s">
-        <v>87</v>
       </c>
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
@@ -11550,8 +11546,8 @@
       <c r="Z67" s="4"/>
       <c r="AA67" s="4"/>
       <c r="AB67" s="4"/>
-      <c r="AC67" s="77"/>
-      <c r="AD67" s="77"/>
+      <c r="AC67" s="58"/>
+      <c r="AD67" s="58"/>
       <c r="AE67" s="4"/>
       <c r="AF67" s="4"/>
       <c r="AG67" s="4"/>
@@ -11560,36 +11556,36 @@
       <c r="AJ67" s="4"/>
     </row>
     <row r="69" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="B69" s="68" t="s">
-        <v>113</v>
+      <c r="B69" s="50" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="B70" s="69" t="s">
-        <v>115</v>
+      <c r="B70" s="51" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="B71" s="80" t="s">
-        <v>117</v>
+      <c r="B71" s="61" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="B72" s="70" t="s">
-        <v>114</v>
+      <c r="B72" s="52" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="A2:AJ2"/>
+    <mergeCell ref="A19:AJ19"/>
     <mergeCell ref="A35:AJ35"/>
     <mergeCell ref="A43:AJ43"/>
     <mergeCell ref="A56:AJ56"/>
     <mergeCell ref="A62:AJ62"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A1:AJ1"/>
-    <mergeCell ref="A2:AJ2"/>
-    <mergeCell ref="A19:AJ19"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="BF5:KL5">
